--- a/data/sports/dota2/gated.xlsx
+++ b/data/sports/dota2/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ116" headerRowCount="1">
-  <autoFilter ref="A1:DQ116"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ119" headerRowCount="1">
+  <autoFilter ref="A1:DQ119"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$116)</f>
+        <f>COUNTA('Picks'!$A$2:$A$119)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$116,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$119,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$116,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$119,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"win")+COUNTIFS('Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")+COUNTIFS('Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$116,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$119,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$116,"&gt;0",'Picks'!$V$2:$V$116,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$116,"&gt;0",'Picks'!$V$2:$V$116,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$116,"&gt;0",'Picks'!$V$2:$V$116,"win")/(COUNTIFS('Picks'!$BX$2:$BX$116,"&gt;0",'Picks'!$V$2:$V$116,"win")+COUNTIFS('Picks'!$BX$2:$BX$116,"&gt;0",'Picks'!$V$2:$V$116,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")/(COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")+COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$116)/SUM('Picks'!$BX$2:$BX$116),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$119)/SUM('Picks'!$BX$2:$BX$119),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$116)</f>
+        <f>SUM('Picks'!$BY$2:$BY$119)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$116,"&lt;&gt;",'Picks'!$AB$2:$AB$116),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$119,"&lt;&gt;",'Picks'!$AB$2:$AB$119),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$116,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$116,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$119,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$119,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$116,'Picks'!$AM$2:$AM$116,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$119,'Picks'!$AM$2:$AM$119,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A14,'Picks'!$U$2:$U$116,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A14,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A14,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$116,'Picks'!$H$2:$H$116,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$116,'Picks'!$H$2:$H$116,$A14,'Picks'!$U$2:$U$116,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A15,'Picks'!$U$2:$U$116,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A15,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A15,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$116,'Picks'!$H$2:$H$116,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$116,'Picks'!$H$2:$H$116,$A15,'Picks'!$U$2:$U$116,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A16,'Picks'!$U$2:$U$116,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A16,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$116,$A16,'Picks'!$U$2:$U$116,"settled",'Picks'!$V$2:$V$116,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$116,'Picks'!$H$2:$H$116,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$116,'Picks'!$H$2:$H$116,$A16,'Picks'!$U$2:$U$116,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ116"/>
+  <dimension ref="A1:DQ119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37608,18 +37608,38 @@
       </c>
       <c r="U114" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V114" s="24" t="n"/>
-      <c r="W114" s="26" t="n"/>
-      <c r="X114" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V114" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W114" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X114" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y114" s="25" t="n"/>
-      <c r="Z114" s="26" t="n"/>
-      <c r="AA114" s="28" t="n"/>
-      <c r="AB114" s="28" t="n"/>
-      <c r="AC114" s="30" t="n"/>
-      <c r="AD114" s="24" t="n"/>
+      <c r="Z114" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA114" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB114" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC114" s="30" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AD114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T10:03:05.704498Z</t>
+        </is>
+      </c>
       <c r="AE114" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-yg-iac-2026-10-06).</t>
@@ -37762,8 +37782,12 @@
       <c r="BN114" s="28" t="n"/>
       <c r="BO114" s="28" t="n"/>
       <c r="BP114" s="25" t="n"/>
-      <c r="BQ114" s="27" t="n"/>
-      <c r="BR114" s="28" t="n"/>
+      <c r="BQ114" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR114" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS114" s="28" t="n"/>
       <c r="BT114" s="28" t="n"/>
       <c r="BU114" s="25" t="n"/>
@@ -37905,18 +37929,38 @@
       </c>
       <c r="U115" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V115" s="24" t="n"/>
-      <c r="W115" s="26" t="n"/>
-      <c r="X115" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V115" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W115" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X115" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y115" s="25" t="n"/>
-      <c r="Z115" s="26" t="n"/>
-      <c r="AA115" s="28" t="n"/>
-      <c r="AB115" s="28" t="n"/>
-      <c r="AC115" s="30" t="n"/>
-      <c r="AD115" s="24" t="n"/>
+      <c r="Z115" s="26" t="n">
+        <v>-900</v>
+      </c>
+      <c r="AA115" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB115" s="28" t="n">
+        <v>0.309836</v>
+      </c>
+      <c r="AC115" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:05:14.355704Z</t>
+        </is>
+      </c>
       <c r="AE115" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-hul-ch-2026-10-06).</t>
@@ -37929,7 +37973,7 @@
       </c>
       <c r="AG115" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH115" s="24" t="n"/>
@@ -38059,8 +38103,12 @@
       <c r="BN115" s="28" t="n"/>
       <c r="BO115" s="28" t="n"/>
       <c r="BP115" s="25" t="n"/>
-      <c r="BQ115" s="27" t="n"/>
-      <c r="BR115" s="28" t="n"/>
+      <c r="BQ115" s="27" t="n">
+        <v>1.111111</v>
+      </c>
+      <c r="BR115" s="28" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BS115" s="28" t="n"/>
       <c r="BT115" s="28" t="n"/>
       <c r="BU115" s="25" t="n"/>
@@ -38124,12 +38172,12 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>01e1af3dedca4d71</t>
+          <t>fd1c05e7e1ce4b8f</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05T22:25:55.486296Z</t>
+          <t>2026-10-06T10:51:23.725681Z</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
@@ -38183,11 +38231,11 @@
         <v>0.45045</v>
       </c>
       <c r="O116" s="28" t="n">
-        <v>0.587048</v>
+        <v>0.586581</v>
       </c>
       <c r="P116" s="28" t="n"/>
       <c r="Q116" s="28" t="n">
-        <v>0.136598</v>
+        <v>0.136131</v>
       </c>
       <c r="R116" s="26" t="n">
         <v>88</v>
@@ -38202,18 +38250,38 @@
       </c>
       <c r="U116" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V116" s="24" t="n"/>
-      <c r="W116" s="26" t="n"/>
-      <c r="X116" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V116" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W116" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y116" s="25" t="n"/>
-      <c r="Z116" s="26" t="n"/>
-      <c r="AA116" s="28" t="n"/>
-      <c r="AB116" s="28" t="n"/>
-      <c r="AC116" s="30" t="n"/>
-      <c r="AD116" s="24" t="n"/>
+      <c r="Z116" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA116" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB116" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC116" s="30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD116" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:05:25.356164Z</t>
+        </is>
+      </c>
       <c r="AE116" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tsea-yes-2026-10-06).</t>
@@ -38300,7 +38368,7 @@
       </c>
       <c r="BA116" s="24" t="inlineStr">
         <is>
-          <t>8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92</t>
+          <t>6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d</t>
         </is>
       </c>
       <c r="BB116" s="24" t="inlineStr">
@@ -38315,7 +38383,7 @@
       </c>
       <c r="BD116" s="24" t="inlineStr">
         <is>
-          <t>8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92</t>
+          <t>6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d</t>
         </is>
       </c>
       <c r="BE116" s="24" t="inlineStr">
@@ -38335,7 +38403,7 @@
       </c>
       <c r="BH116" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05T22:25:44.939151Z</t>
+          <t>2026-10-06T10:51:03.361802Z</t>
         </is>
       </c>
       <c r="BI116" s="24" t="inlineStr">
@@ -38356,8 +38424,12 @@
       <c r="BN116" s="28" t="n"/>
       <c r="BO116" s="28" t="n"/>
       <c r="BP116" s="25" t="n"/>
-      <c r="BQ116" s="27" t="n"/>
-      <c r="BR116" s="28" t="n"/>
+      <c r="BQ116" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR116" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS116" s="28" t="n"/>
       <c r="BT116" s="28" t="n"/>
       <c r="BU116" s="25" t="n"/>
@@ -38414,7 +38486,922 @@
       <c r="DP116" s="24" t="n"/>
       <c r="DQ116" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92", "away_team": "Yellow Submarine", "event_id": "143565", "event_start_utc": "2026-10-06T14:00:00Z", "features": {"away_elo": 1786.068317, "away_history_count": 285, "home_elo": 1855.48017, "home_history_count": 23}, "historical_source_observation_times_verified": false, "home_team": "Team Synapse", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 285, "bo3:4:25201": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-05T11:10:00Z", "bo3:4:25201": "2026-10-05T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.08103315066152637, "platt_slope": 0.8449481325411426, "ratings": {"bo3:4:16486": 1786.068317, "bo3:4:25201": 1855.48017}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-05T22:25:23.694580+00:00", "team_ids": ["bo3:4:25201", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-05T22:25:23.694580+00:00", "probabilities": {"away": 0.412952, "home": 0.587048}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "de1d70f15f33b8dcda068e21a4a94c374808390850c2e0df4df0409544cc1b27", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d", "away_team": "Yellow Submarine", "event_id": "143565", "event_start_utc": "2026-10-06T14:00:00Z", "features": {"away_elo": 1786.028424, "away_history_count": 285, "home_elo": 1855.458017, "home_history_count": 23}, "historical_source_observation_times_verified": false, "home_team": "Team Synapse", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 285, "bo3:4:25201": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-05T11:10:00Z", "bo3:4:25201": "2026-10-05T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0806649303548175, "platt_slope": 0.8439015098774778, "ratings": {"bo3:4:16486": 1786.028424, "bo3:4:25201": 1855.458017}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T10:50:53.111088+00:00", "team_ids": ["bo3:4:25201", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T10:50:53.111088+00:00", "probabilities": {"away": 0.413419, "home": 0.586581}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2d95927cb9101c0d665d6d64969b5ac62cd066f6a48af941c35e0f56d54aa876", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="A117" s="24" t="inlineStr">
+        <is>
+          <t>120dd1ec1cd24c81</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:34:32.687894Z</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>144500</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="H117" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I117" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J117" s="25" t="n"/>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L117" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M117" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N117" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O117" s="28" t="n">
+        <v>0.552316</v>
+      </c>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="28" t="n">
+        <v>0.013145</v>
+      </c>
+      <c r="R117" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S117" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U117" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V117" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W117" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y117" s="25" t="n"/>
+      <c r="Z117" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA117" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB117" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC117" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD117" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:05:27.593158Z</t>
+        </is>
+      </c>
+      <c r="AE117" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-leg-mouz-2026-10-06).</t>
+        </is>
+      </c>
+      <c r="AF117" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG117" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH117" s="24" t="n"/>
+      <c r="AI117" s="31" t="n"/>
+      <c r="AJ117" s="31" t="n"/>
+      <c r="AK117" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL117" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM117" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN117" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO117" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP117" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AQ117" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AR117" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AS117" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AT117" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AU117" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AV117" s="24" t="n"/>
+      <c r="AW117" s="24" t="n"/>
+      <c r="AX117" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY117" s="24" t="n"/>
+      <c r="AZ117" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA117" s="24" t="inlineStr">
+        <is>
+          <t>4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee</t>
+        </is>
+      </c>
+      <c r="BB117" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC117" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD117" s="24" t="inlineStr">
+        <is>
+          <t>4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee</t>
+        </is>
+      </c>
+      <c r="BE117" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF117" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG117" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH117" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:34:12.398493Z</t>
+        </is>
+      </c>
+      <c r="BI117" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ117" s="25" t="n"/>
+      <c r="BK117" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL117" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM117" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN117" s="28" t="n"/>
+      <c r="BO117" s="28" t="n"/>
+      <c r="BP117" s="25" t="n"/>
+      <c r="BQ117" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR117" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS117" s="28" t="n"/>
+      <c r="BT117" s="28" t="n"/>
+      <c r="BU117" s="25" t="n"/>
+      <c r="BV117" s="29" t="n"/>
+      <c r="BW117" s="24" t="n"/>
+      <c r="BX117" s="30" t="n"/>
+      <c r="BY117" s="27" t="n"/>
+      <c r="BZ117" s="24" t="n"/>
+      <c r="CA117" s="31" t="n"/>
+      <c r="CB117" s="24" t="n"/>
+      <c r="CC117" s="24" t="n"/>
+      <c r="CD117" s="24" t="n"/>
+      <c r="CE117" s="24" t="n"/>
+      <c r="CF117" s="24" t="n"/>
+      <c r="CG117" s="24" t="n"/>
+      <c r="CH117" s="24" t="n"/>
+      <c r="CI117" s="24" t="n"/>
+      <c r="CJ117" s="24" t="n"/>
+      <c r="CK117" s="24" t="n"/>
+      <c r="CL117" s="24" t="n"/>
+      <c r="CM117" s="24" t="n"/>
+      <c r="CN117" s="24" t="n"/>
+      <c r="CO117" s="24" t="n"/>
+      <c r="CP117" s="24" t="n"/>
+      <c r="CQ117" s="24" t="n"/>
+      <c r="CR117" s="24" t="n"/>
+      <c r="CS117" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT117" s="24" t="n"/>
+      <c r="CU117" s="24" t="n"/>
+      <c r="CV117" s="24" t="n"/>
+      <c r="CW117" s="24" t="n"/>
+      <c r="CX117" s="24" t="n"/>
+      <c r="CY117" s="24" t="n"/>
+      <c r="CZ117" s="24" t="n"/>
+      <c r="DA117" s="24" t="n"/>
+      <c r="DB117" s="24" t="n"/>
+      <c r="DC117" s="24" t="n"/>
+      <c r="DD117" s="24" t="n"/>
+      <c r="DE117" s="24" t="n"/>
+      <c r="DF117" s="24" t="n"/>
+      <c r="DG117" s="24" t="n"/>
+      <c r="DH117" s="24" t="n"/>
+      <c r="DI117" s="24" t="n"/>
+      <c r="DJ117" s="24" t="n"/>
+      <c r="DK117" s="24" t="n"/>
+      <c r="DL117" s="24" t="n"/>
+      <c r="DM117" s="24" t="n"/>
+      <c r="DN117" s="24" t="n"/>
+      <c r="DO117" s="24" t="n"/>
+      <c r="DP117" s="24" t="n"/>
+      <c r="DQ117" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee", "away_team": "MOUZ", "event_id": "144500", "event_start_utc": "2026-10-06T17:00:00Z", "features": {"away_elo": 1644.197963, "away_history_count": 363, "home_elo": 1532.76, "home_history_count": 1}, "historical_source_observation_times_verified": false, "home_team": "LEGION", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15032": 363, "bo3:4:25401": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15032": "2026-10-05T18:00:00Z", "bo3:4:25401": "2026-10-05T14:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.08111949537955908, "platt_slope": 0.8418535477548365, "ratings": {"bo3:4:15032": 1644.197963, "bo3:4:25401": 1532.76}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T16:34:12.325280+00:00", "team_ids": ["bo3:4:25401", "bo3:4:15032"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T16:34:12.325280+00:00", "probabilities": {"away": 0.552316, "home": 0.447684}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d7ab51a4f880e3c1e54ff9e61bc180831b900208cf5f6dcb73682f2580b1dd3d", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>e78ebb127f8b4a80</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:56.390271Z</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>145226</t>
+        </is>
+      </c>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="H118" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I118" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J118" s="25" t="n"/>
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L118" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M118" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N118" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O118" s="28" t="n">
+        <v>0.550796</v>
+      </c>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="28" t="n">
+        <v>-0.148904</v>
+      </c>
+      <c r="R118" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U118" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V118" s="24" t="n"/>
+      <c r="W118" s="26" t="n"/>
+      <c r="X118" s="26" t="n"/>
+      <c r="Y118" s="25" t="n"/>
+      <c r="Z118" s="26" t="n"/>
+      <c r="AA118" s="28" t="n"/>
+      <c r="AB118" s="28" t="n"/>
+      <c r="AC118" s="30" t="n"/>
+      <c r="AD118" s="24" t="n"/>
+      <c r="AE118" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-db-y123-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF118" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG118" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH118" s="24" t="n"/>
+      <c r="AI118" s="31" t="n"/>
+      <c r="AJ118" s="31" t="n"/>
+      <c r="AK118" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL118" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM118" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN118" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO118" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP118" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AQ118" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AR118" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AS118" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AT118" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AU118" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AV118" s="24" t="n"/>
+      <c r="AW118" s="24" t="n"/>
+      <c r="AX118" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY118" s="24" t="n"/>
+      <c r="AZ118" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA118" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BB118" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC118" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD118" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BE118" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF118" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG118" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH118" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:25.556351Z</t>
+        </is>
+      </c>
+      <c r="BI118" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ118" s="25" t="n"/>
+      <c r="BK118" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL118" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM118" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN118" s="28" t="n"/>
+      <c r="BO118" s="28" t="n"/>
+      <c r="BP118" s="25" t="n"/>
+      <c r="BQ118" s="27" t="n"/>
+      <c r="BR118" s="28" t="n"/>
+      <c r="BS118" s="28" t="n"/>
+      <c r="BT118" s="28" t="n"/>
+      <c r="BU118" s="25" t="n"/>
+      <c r="BV118" s="29" t="n"/>
+      <c r="BW118" s="24" t="n"/>
+      <c r="BX118" s="30" t="n"/>
+      <c r="BY118" s="27" t="n"/>
+      <c r="BZ118" s="24" t="n"/>
+      <c r="CA118" s="31" t="n"/>
+      <c r="CB118" s="24" t="n"/>
+      <c r="CC118" s="24" t="n"/>
+      <c r="CD118" s="24" t="n"/>
+      <c r="CE118" s="24" t="n"/>
+      <c r="CF118" s="24" t="n"/>
+      <c r="CG118" s="24" t="n"/>
+      <c r="CH118" s="24" t="n"/>
+      <c r="CI118" s="24" t="n"/>
+      <c r="CJ118" s="24" t="n"/>
+      <c r="CK118" s="24" t="n"/>
+      <c r="CL118" s="24" t="n"/>
+      <c r="CM118" s="24" t="n"/>
+      <c r="CN118" s="24" t="n"/>
+      <c r="CO118" s="24" t="n"/>
+      <c r="CP118" s="24" t="n"/>
+      <c r="CQ118" s="24" t="n"/>
+      <c r="CR118" s="24" t="n"/>
+      <c r="CS118" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT118" s="24" t="n"/>
+      <c r="CU118" s="24" t="n"/>
+      <c r="CV118" s="24" t="n"/>
+      <c r="CW118" s="24" t="n"/>
+      <c r="CX118" s="24" t="n"/>
+      <c r="CY118" s="24" t="n"/>
+      <c r="CZ118" s="24" t="n"/>
+      <c r="DA118" s="24" t="n"/>
+      <c r="DB118" s="24" t="n"/>
+      <c r="DC118" s="24" t="n"/>
+      <c r="DD118" s="24" t="n"/>
+      <c r="DE118" s="24" t="n"/>
+      <c r="DF118" s="24" t="n"/>
+      <c r="DG118" s="24" t="n"/>
+      <c r="DH118" s="24" t="n"/>
+      <c r="DI118" s="24" t="n"/>
+      <c r="DJ118" s="24" t="n"/>
+      <c r="DK118" s="24" t="n"/>
+      <c r="DL118" s="24" t="n"/>
+      <c r="DM118" s="24" t="n"/>
+      <c r="DN118" s="24" t="n"/>
+      <c r="DO118" s="24" t="n"/>
+      <c r="DP118" s="24" t="n"/>
+      <c r="DQ118" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642", "away_team": "\u042f\u0427\u0401123", "event_id": "145226", "event_start_utc": "2026-10-07T03:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1584.551416, "home_history_count": 37}, "historical_source_observation_times_verified": false, "home_team": "Direborn", "inference_inputs": {"book_state": {"games_played": {"bo3:4:24344": 37}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:24344": "2026-10-06T06:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:24344": 1584.551416}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.483347+00:00", "team_ids": ["bo3:4:24344", "unknown:\u044f\u0447\u0435123"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.483347+00:00", "probabilities": {"away": 0.449204, "home": 0.550796}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "dc330291efd584143729f621ac5b58f7d873a090a9b0f169c927e0ebb9493b25", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="36" customHeight="1">
+      <c r="A119" s="24" t="inlineStr">
+        <is>
+          <t>ae99ce3a6fdb417f</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:56.390271Z</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>145796</t>
+        </is>
+      </c>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="H119" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I119" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J119" s="25" t="n"/>
+      <c r="K119" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L119" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M119" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N119" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O119" s="28" t="n">
+        <v>0.640253</v>
+      </c>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="28" t="n">
+        <v>0.030878</v>
+      </c>
+      <c r="R119" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S119" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U119" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V119" s="24" t="n"/>
+      <c r="W119" s="26" t="n"/>
+      <c r="X119" s="26" t="n"/>
+      <c r="Y119" s="25" t="n"/>
+      <c r="Z119" s="26" t="n"/>
+      <c r="AA119" s="28" t="n"/>
+      <c r="AB119" s="28" t="n"/>
+      <c r="AC119" s="30" t="n"/>
+      <c r="AD119" s="24" t="n"/>
+      <c r="AE119" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-bbl-yes-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF119" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG119" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH119" s="24" t="n"/>
+      <c r="AI119" s="31" t="n"/>
+      <c r="AJ119" s="31" t="n"/>
+      <c r="AK119" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL119" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM119" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN119" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO119" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP119" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AQ119" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AR119" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AS119" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AT119" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AU119" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AV119" s="24" t="n"/>
+      <c r="AW119" s="24" t="n"/>
+      <c r="AX119" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY119" s="24" t="n"/>
+      <c r="AZ119" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA119" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BB119" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC119" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD119" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BE119" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF119" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG119" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH119" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:25.683597Z</t>
+        </is>
+      </c>
+      <c r="BI119" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ119" s="25" t="n"/>
+      <c r="BK119" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL119" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM119" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN119" s="28" t="n"/>
+      <c r="BO119" s="28" t="n"/>
+      <c r="BP119" s="25" t="n"/>
+      <c r="BQ119" s="27" t="n"/>
+      <c r="BR119" s="28" t="n"/>
+      <c r="BS119" s="28" t="n"/>
+      <c r="BT119" s="28" t="n"/>
+      <c r="BU119" s="25" t="n"/>
+      <c r="BV119" s="29" t="n"/>
+      <c r="BW119" s="24" t="n"/>
+      <c r="BX119" s="30" t="n"/>
+      <c r="BY119" s="27" t="n"/>
+      <c r="BZ119" s="24" t="n"/>
+      <c r="CA119" s="31" t="n"/>
+      <c r="CB119" s="24" t="n"/>
+      <c r="CC119" s="24" t="n"/>
+      <c r="CD119" s="24" t="n"/>
+      <c r="CE119" s="24" t="n"/>
+      <c r="CF119" s="24" t="n"/>
+      <c r="CG119" s="24" t="n"/>
+      <c r="CH119" s="24" t="n"/>
+      <c r="CI119" s="24" t="n"/>
+      <c r="CJ119" s="24" t="n"/>
+      <c r="CK119" s="24" t="n"/>
+      <c r="CL119" s="24" t="n"/>
+      <c r="CM119" s="24" t="n"/>
+      <c r="CN119" s="24" t="n"/>
+      <c r="CO119" s="24" t="n"/>
+      <c r="CP119" s="24" t="n"/>
+      <c r="CQ119" s="24" t="n"/>
+      <c r="CR119" s="24" t="n"/>
+      <c r="CS119" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT119" s="24" t="n"/>
+      <c r="CU119" s="24" t="n"/>
+      <c r="CV119" s="24" t="n"/>
+      <c r="CW119" s="24" t="n"/>
+      <c r="CX119" s="24" t="n"/>
+      <c r="CY119" s="24" t="n"/>
+      <c r="CZ119" s="24" t="n"/>
+      <c r="DA119" s="24" t="n"/>
+      <c r="DB119" s="24" t="n"/>
+      <c r="DC119" s="24" t="n"/>
+      <c r="DD119" s="24" t="n"/>
+      <c r="DE119" s="24" t="n"/>
+      <c r="DF119" s="24" t="n"/>
+      <c r="DG119" s="24" t="n"/>
+      <c r="DH119" s="24" t="n"/>
+      <c r="DI119" s="24" t="n"/>
+      <c r="DJ119" s="24" t="n"/>
+      <c r="DK119" s="24" t="n"/>
+      <c r="DL119" s="24" t="n"/>
+      <c r="DM119" s="24" t="n"/>
+      <c r="DN119" s="24" t="n"/>
+      <c r="DO119" s="24" t="n"/>
+      <c r="DP119" s="24" t="n"/>
+      <c r="DQ119" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642", "away_team": "Yellow Submarine", "event_id": "145796", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1759.660919, "away_history_count": 286, "home_elo": 1497.898695, "home_history_count": 2}, "historical_source_observation_times_verified": false, "home_team": "Blasterbl", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 286, "bo3:4:23832": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-06T14:35:00Z", "bo3:4:23832": "2026-10-06T12:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:16486": 1759.660919, "bo3:4:23832": 1497.898695}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.483347+00:00", "team_ids": ["bo3:4:23832", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.483347+00:00", "probabilities": {"away": 0.640253, "home": 0.359747}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "72c0f4514c8da658b54751da2293583b1dca94c0c2906e7fcb514d3472bc5bc3", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/dota2/gated.xlsx
+++ b/data/sports/dota2/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ119" headerRowCount="1">
-  <autoFilter ref="A1:DQ119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ140" headerRowCount="1">
+  <autoFilter ref="A1:DQ140"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$119)</f>
+        <f>COUNTA('Picks'!$A$2:$A$140)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$119,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$140,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$119,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$140,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")+COUNTIFS('Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")+COUNTIFS('Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$119,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$140,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")/(COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"win")+COUNTIFS('Picks'!$BX$2:$BX$119,"&gt;0",'Picks'!$V$2:$V$119,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")/(COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")+COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$119)/SUM('Picks'!$BX$2:$BX$119),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$140)/SUM('Picks'!$BX$2:$BX$140),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$119)</f>
+        <f>SUM('Picks'!$BY$2:$BY$140)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$119,"&lt;&gt;",'Picks'!$AB$2:$AB$119),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$140,"&lt;&gt;",'Picks'!$AB$2:$AB$140),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$119,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$119,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$140,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$140,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$119,'Picks'!$AM$2:$AM$119,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$140,'Picks'!$AM$2:$AM$140,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A14,'Picks'!$U$2:$U$119,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A15,'Picks'!$U$2:$U$119,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled",'Picks'!$V$2:$V$119,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$119,'Picks'!$H$2:$H$119,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$119,'Picks'!$H$2:$H$119,$A16,'Picks'!$U$2:$U$119,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ119"/>
+  <dimension ref="A1:DQ140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -38892,18 +38892,38 @@
       </c>
       <c r="U118" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V118" s="24" t="n"/>
-      <c r="W118" s="26" t="n"/>
-      <c r="X118" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V118" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W118" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y118" s="25" t="n"/>
-      <c r="Z118" s="26" t="n"/>
-      <c r="AA118" s="28" t="n"/>
-      <c r="AB118" s="28" t="n"/>
-      <c r="AC118" s="30" t="n"/>
-      <c r="AD118" s="24" t="n"/>
+      <c r="Z118" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA118" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB118" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC118" s="30" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="AD118" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:05:40.667231Z</t>
+        </is>
+      </c>
       <c r="AE118" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-db-y123-2026-10-07).</t>
@@ -39046,8 +39066,12 @@
       <c r="BN118" s="28" t="n"/>
       <c r="BO118" s="28" t="n"/>
       <c r="BP118" s="25" t="n"/>
-      <c r="BQ118" s="27" t="n"/>
-      <c r="BR118" s="28" t="n"/>
+      <c r="BQ118" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR118" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS118" s="28" t="n"/>
       <c r="BT118" s="28" t="n"/>
       <c r="BU118" s="25" t="n"/>
@@ -39111,12 +39135,12 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="24" t="inlineStr">
         <is>
-          <t>ae99ce3a6fdb417f</t>
+          <t>b45edc68511c4231</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:56.390271Z</t>
+          <t>2026-10-07T05:29:10.726256Z</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
@@ -39161,23 +39185,23 @@
         </is>
       </c>
       <c r="L119" s="26" t="n">
-        <v>-156</v>
+        <v>-144</v>
       </c>
       <c r="M119" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.694444</v>
       </c>
       <c r="N119" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.590164</v>
       </c>
       <c r="O119" s="28" t="n">
-        <v>0.640253</v>
+        <v>0.639911</v>
       </c>
       <c r="P119" s="28" t="n"/>
       <c r="Q119" s="28" t="n">
-        <v>0.030878</v>
+        <v>0.049747</v>
       </c>
       <c r="R119" s="26" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="S119" s="29" t="n">
         <v>1</v>
@@ -39189,21 +39213,41 @@
       </c>
       <c r="U119" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V119" s="24" t="n"/>
-      <c r="W119" s="26" t="n"/>
-      <c r="X119" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V119" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W119" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y119" s="25" t="n"/>
-      <c r="Z119" s="26" t="n"/>
-      <c r="AA119" s="28" t="n"/>
-      <c r="AB119" s="28" t="n"/>
-      <c r="AC119" s="30" t="n"/>
-      <c r="AD119" s="24" t="n"/>
+      <c r="Z119" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA119" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB119" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC119" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD119" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:06:25.394851Z</t>
+        </is>
+      </c>
       <c r="AE119" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-bbl-yes-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-bbl-yes-2026-10-07).</t>
         </is>
       </c>
       <c r="AF119" s="31" t="inlineStr">
@@ -39213,7 +39257,7 @@
       </c>
       <c r="AG119" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH119" s="24" t="n"/>
@@ -39287,7 +39331,7 @@
       </c>
       <c r="BA119" s="24" t="inlineStr">
         <is>
-          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+          <t>00ed5147d0e0a43bf2db627ef55a5a1201c6979969e61e75b6a4a259a94f99a0</t>
         </is>
       </c>
       <c r="BB119" s="24" t="inlineStr">
@@ -39302,7 +39346,7 @@
       </c>
       <c r="BD119" s="24" t="inlineStr">
         <is>
-          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+          <t>00ed5147d0e0a43bf2db627ef55a5a1201c6979969e61e75b6a4a259a94f99a0</t>
         </is>
       </c>
       <c r="BE119" s="24" t="inlineStr">
@@ -39322,7 +39366,7 @@
       </c>
       <c r="BH119" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:25.683597Z</t>
+          <t>2026-10-07T05:28:49.757708Z</t>
         </is>
       </c>
       <c r="BI119" s="24" t="inlineStr">
@@ -39332,19 +39376,23 @@
       </c>
       <c r="BJ119" s="25" t="n"/>
       <c r="BK119" s="26" t="n">
-        <v>-156</v>
+        <v>-144</v>
       </c>
       <c r="BL119" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.694444</v>
       </c>
       <c r="BM119" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.590164</v>
       </c>
       <c r="BN119" s="28" t="n"/>
       <c r="BO119" s="28" t="n"/>
       <c r="BP119" s="25" t="n"/>
-      <c r="BQ119" s="27" t="n"/>
-      <c r="BR119" s="28" t="n"/>
+      <c r="BQ119" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR119" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS119" s="28" t="n"/>
       <c r="BT119" s="28" t="n"/>
       <c r="BU119" s="25" t="n"/>
@@ -39401,7 +39449,6586 @@
       <c r="DP119" s="24" t="n"/>
       <c r="DQ119" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642", "away_team": "Yellow Submarine", "event_id": "145796", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1759.660919, "away_history_count": 286, "home_elo": 1497.898695, "home_history_count": 2}, "historical_source_observation_times_verified": false, "home_team": "Blasterbl", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 286, "bo3:4:23832": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-06T14:35:00Z", "bo3:4:23832": "2026-10-06T12:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:16486": 1759.660919, "bo3:4:23832": 1497.898695}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.483347+00:00", "team_ids": ["bo3:4:23832", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.483347+00:00", "probabilities": {"away": 0.640253, "home": 0.359747}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "72c0f4514c8da658b54751da2293583b1dca94c0c2906e7fcb514d3472bc5bc3", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "00ed5147d0e0a43bf2db627ef55a5a1201c6979969e61e75b6a4a259a94f99a0", "away_team": "Yellow Submarine", "event_id": "145796", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1759.660919, "away_history_count": 286, "home_elo": 1497.898695, "home_history_count": 2}, "historical_source_observation_times_verified": false, "home_team": "Blasterbl", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 286, "bo3:4:23832": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-06T14:35:00Z", "bo3:4:23832": "2026-10-06T12:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:16486": 1759.660919, "bo3:4:23832": 1497.898695}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T05:28:49.648258+00:00", "team_ids": ["bo3:4:23832", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T05:28:49.648258+00:00", "probabilities": {"away": 0.639911, "home": 0.360089}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "8a7fc04bcf06afcbba6bf364eb12482398a8f0fcc2bcc06755a2c1074e81fe44", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="A120" s="24" t="inlineStr">
+        <is>
+          <t>5d975ad0beb743a5</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:23:30.086549Z</t>
+        </is>
+      </c>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>146207</t>
+        </is>
+      </c>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="H120" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I120" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J120" s="25" t="n"/>
+      <c r="K120" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L120" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M120" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N120" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O120" s="28" t="n">
+        <v>0.533946</v>
+      </c>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="28" t="n">
+        <v>-0.005225</v>
+      </c>
+      <c r="R120" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S120" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U120" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V120" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W120" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" s="25" t="n"/>
+      <c r="Z120" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA120" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB120" s="28" t="n">
+        <v>0.010829</v>
+      </c>
+      <c r="AC120" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD120" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:06:26.565290Z</t>
+        </is>
+      </c>
+      <c r="AE120" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-ch-mouz-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF120" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG120" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH120" s="24" t="n"/>
+      <c r="AI120" s="31" t="n"/>
+      <c r="AJ120" s="31" t="n"/>
+      <c r="AK120" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL120" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM120" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN120" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO120" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP120" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AQ120" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AR120" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AS120" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AT120" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AU120" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AV120" s="24" t="n"/>
+      <c r="AW120" s="24" t="n"/>
+      <c r="AX120" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY120" s="24" t="n"/>
+      <c r="AZ120" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA120" s="24" t="inlineStr">
+        <is>
+          <t>8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177</t>
+        </is>
+      </c>
+      <c r="BB120" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC120" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD120" s="24" t="inlineStr">
+        <is>
+          <t>8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177</t>
+        </is>
+      </c>
+      <c r="BE120" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF120" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG120" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH120" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:23:09.270676Z</t>
+        </is>
+      </c>
+      <c r="BI120" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ120" s="25" t="n"/>
+      <c r="BK120" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL120" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM120" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN120" s="28" t="n"/>
+      <c r="BO120" s="28" t="n"/>
+      <c r="BP120" s="25" t="n"/>
+      <c r="BQ120" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR120" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BS120" s="28" t="n"/>
+      <c r="BT120" s="28" t="n"/>
+      <c r="BU120" s="25" t="n"/>
+      <c r="BV120" s="29" t="n"/>
+      <c r="BW120" s="24" t="n"/>
+      <c r="BX120" s="30" t="n"/>
+      <c r="BY120" s="27" t="n"/>
+      <c r="BZ120" s="24" t="n"/>
+      <c r="CA120" s="31" t="n"/>
+      <c r="CB120" s="24" t="n"/>
+      <c r="CC120" s="24" t="n"/>
+      <c r="CD120" s="24" t="n"/>
+      <c r="CE120" s="24" t="n"/>
+      <c r="CF120" s="24" t="n"/>
+      <c r="CG120" s="24" t="n"/>
+      <c r="CH120" s="24" t="n"/>
+      <c r="CI120" s="24" t="n"/>
+      <c r="CJ120" s="24" t="n"/>
+      <c r="CK120" s="24" t="n"/>
+      <c r="CL120" s="24" t="n"/>
+      <c r="CM120" s="24" t="n"/>
+      <c r="CN120" s="24" t="n"/>
+      <c r="CO120" s="24" t="n"/>
+      <c r="CP120" s="24" t="n"/>
+      <c r="CQ120" s="24" t="n"/>
+      <c r="CR120" s="24" t="n"/>
+      <c r="CS120" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT120" s="24" t="n"/>
+      <c r="CU120" s="24" t="n"/>
+      <c r="CV120" s="24" t="n"/>
+      <c r="CW120" s="24" t="n"/>
+      <c r="CX120" s="24" t="n"/>
+      <c r="CY120" s="24" t="n"/>
+      <c r="CZ120" s="24" t="n"/>
+      <c r="DA120" s="24" t="n"/>
+      <c r="DB120" s="24" t="n"/>
+      <c r="DC120" s="24" t="n"/>
+      <c r="DD120" s="24" t="n"/>
+      <c r="DE120" s="24" t="n"/>
+      <c r="DF120" s="24" t="n"/>
+      <c r="DG120" s="24" t="n"/>
+      <c r="DH120" s="24" t="n"/>
+      <c r="DI120" s="24" t="n"/>
+      <c r="DJ120" s="24" t="n"/>
+      <c r="DK120" s="24" t="n"/>
+      <c r="DL120" s="24" t="n"/>
+      <c r="DM120" s="24" t="n"/>
+      <c r="DN120" s="24" t="n"/>
+      <c r="DO120" s="24" t="n"/>
+      <c r="DP120" s="24" t="n"/>
+      <c r="DQ120" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177", "away_team": "MOUZ", "event_id": "146207", "event_start_utc": "2026-10-07T12:00:00Z", "features": {"away_elo": 1601.278288, "away_history_count": 364, "home_elo": 1530.437849, "home_history_count": 2}, "historical_source_observation_times_verified": false, "home_team": "CyberHero", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15032": 364, "bo3:4:25398": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15032": "2026-10-06T17:20:00Z", "bo3:4:25398": "2026-10-06T08:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07656940144871896, "platt_slope": 0.849720404615883, "ratings": {"bo3:4:15032": 1601.278288, "bo3:4:25398": 1530.437849}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T10:23:09.218675+00:00", "team_ids": ["bo3:4:25398", "bo3:4:15032"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T10:23:09.218675+00:00", "probabilities": {"away": 0.533946, "home": 0.466054}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4646121ff359ae6c5ec0687780aa2d1878fdb09c65bd920cb1d15daf0b498a38", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="24" t="inlineStr">
+        <is>
+          <t>788b9c35de5b4367</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:23:30.086549Z</t>
+        </is>
+      </c>
+      <c r="C121" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr">
+        <is>
+          <t>146208</t>
+        </is>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="inlineStr">
+        <is>
+          <t>Team Synapse</t>
+        </is>
+      </c>
+      <c r="H121" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I121" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J121" s="25" t="n"/>
+      <c r="K121" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L121" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M121" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N121" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O121" s="28" t="n">
+        <v>0.673769</v>
+      </c>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="28" t="n">
+        <v>0.083605</v>
+      </c>
+      <c r="R121" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S121" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T121" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U121" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V121" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W121" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="25" t="n"/>
+      <c r="Z121" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA121" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB121" s="28" t="n">
+        <v>-0.040164</v>
+      </c>
+      <c r="AC121" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD121" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:04:54.335391Z</t>
+        </is>
+      </c>
+      <c r="AE121" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-tsea-leg-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF121" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG121" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH121" s="24" t="n"/>
+      <c r="AI121" s="31" t="n"/>
+      <c r="AJ121" s="31" t="n"/>
+      <c r="AK121" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL121" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM121" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN121" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO121" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP121" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AQ121" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AR121" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AS121" s="24" t="inlineStr">
+        <is>
+          <t>Team Synapse</t>
+        </is>
+      </c>
+      <c r="AT121" s="24" t="inlineStr">
+        <is>
+          <t>Team Synapse</t>
+        </is>
+      </c>
+      <c r="AU121" s="24" t="inlineStr">
+        <is>
+          <t>Team Synapse</t>
+        </is>
+      </c>
+      <c r="AV121" s="24" t="n"/>
+      <c r="AW121" s="24" t="n"/>
+      <c r="AX121" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY121" s="24" t="n"/>
+      <c r="AZ121" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA121" s="24" t="inlineStr">
+        <is>
+          <t>8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177</t>
+        </is>
+      </c>
+      <c r="BB121" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC121" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD121" s="24" t="inlineStr">
+        <is>
+          <t>8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177</t>
+        </is>
+      </c>
+      <c r="BE121" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF121" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG121" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH121" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:23:09.332235Z</t>
+        </is>
+      </c>
+      <c r="BI121" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ121" s="25" t="n"/>
+      <c r="BK121" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL121" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM121" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN121" s="28" t="n"/>
+      <c r="BO121" s="28" t="n"/>
+      <c r="BP121" s="25" t="n"/>
+      <c r="BQ121" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR121" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BS121" s="28" t="n"/>
+      <c r="BT121" s="28" t="n"/>
+      <c r="BU121" s="25" t="n"/>
+      <c r="BV121" s="29" t="n"/>
+      <c r="BW121" s="24" t="n"/>
+      <c r="BX121" s="30" t="n"/>
+      <c r="BY121" s="27" t="n"/>
+      <c r="BZ121" s="24" t="n"/>
+      <c r="CA121" s="31" t="n"/>
+      <c r="CB121" s="24" t="n"/>
+      <c r="CC121" s="24" t="n"/>
+      <c r="CD121" s="24" t="n"/>
+      <c r="CE121" s="24" t="n"/>
+      <c r="CF121" s="24" t="n"/>
+      <c r="CG121" s="24" t="n"/>
+      <c r="CH121" s="24" t="n"/>
+      <c r="CI121" s="24" t="n"/>
+      <c r="CJ121" s="24" t="n"/>
+      <c r="CK121" s="24" t="n"/>
+      <c r="CL121" s="24" t="n"/>
+      <c r="CM121" s="24" t="n"/>
+      <c r="CN121" s="24" t="n"/>
+      <c r="CO121" s="24" t="n"/>
+      <c r="CP121" s="24" t="n"/>
+      <c r="CQ121" s="24" t="n"/>
+      <c r="CR121" s="24" t="n"/>
+      <c r="CS121" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT121" s="24" t="n"/>
+      <c r="CU121" s="24" t="n"/>
+      <c r="CV121" s="24" t="n"/>
+      <c r="CW121" s="24" t="n"/>
+      <c r="CX121" s="24" t="n"/>
+      <c r="CY121" s="24" t="n"/>
+      <c r="CZ121" s="24" t="n"/>
+      <c r="DA121" s="24" t="n"/>
+      <c r="DB121" s="24" t="n"/>
+      <c r="DC121" s="24" t="n"/>
+      <c r="DD121" s="24" t="n"/>
+      <c r="DE121" s="24" t="n"/>
+      <c r="DF121" s="24" t="n"/>
+      <c r="DG121" s="24" t="n"/>
+      <c r="DH121" s="24" t="n"/>
+      <c r="DI121" s="24" t="n"/>
+      <c r="DJ121" s="24" t="n"/>
+      <c r="DK121" s="24" t="n"/>
+      <c r="DL121" s="24" t="n"/>
+      <c r="DM121" s="24" t="n"/>
+      <c r="DN121" s="24" t="n"/>
+      <c r="DO121" s="24" t="n"/>
+      <c r="DP121" s="24" t="n"/>
+      <c r="DQ121" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "8f4a6f5ae78633bea4c7b21d6e2903f4d5a628c17b4db8222ef6d4549d50f177", "away_team": "LEGION", "event_id": "146208", "event_start_utc": "2026-10-07T15:00:00Z", "features": {"away_elo": 1575.629058, "away_history_count": 2, "home_elo": 1881.437986, "home_history_count": 24}, "historical_source_observation_times_verified": false, "home_team": "Team Synapse", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25201": 24, "bo3:4:25401": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25201": "2026-10-06T14:35:00Z", "bo3:4:25401": "2026-10-06T17:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07656940144871896, "platt_slope": 0.849720404615883, "ratings": {"bo3:4:25201": 1881.437986, "bo3:4:25401": 1575.629058}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T10:23:09.218675+00:00", "team_ids": ["bo3:4:25201", "bo3:4:25401"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T10:23:09.218675+00:00", "probabilities": {"away": 0.326231, "home": 0.673769}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "c988e0bfb2734b187c99c9c45d600ba856d037d2016dfe738b6843af5d964537", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="24" t="inlineStr">
+        <is>
+          <t>8409de11415246a2</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:32:44.972195Z</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>147363</t>
+        </is>
+      </c>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="H122" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I122" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J122" s="25" t="n"/>
+      <c r="K122" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L122" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M122" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N122" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O122" s="28" t="n">
+        <v>0.502246</v>
+      </c>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="28" t="n">
+        <v>0.122018</v>
+      </c>
+      <c r="R122" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S122" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T122" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U122" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V122" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W122" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y122" s="25" t="n"/>
+      <c r="Z122" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA122" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB122" s="28" t="n">
+        <v>0.029772</v>
+      </c>
+      <c r="AC122" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD122" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:04:55.499144Z</t>
+        </is>
+      </c>
+      <c r="AE122" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-bbl-ch-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF122" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG122" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH122" s="24" t="n"/>
+      <c r="AI122" s="31" t="n"/>
+      <c r="AJ122" s="31" t="n"/>
+      <c r="AK122" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL122" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM122" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN122" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO122" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP122" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AQ122" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AR122" s="24" t="inlineStr">
+        <is>
+          <t>CyberHero</t>
+        </is>
+      </c>
+      <c r="AS122" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AT122" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AU122" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AV122" s="24" t="n"/>
+      <c r="AW122" s="24" t="n"/>
+      <c r="AX122" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY122" s="24" t="n"/>
+      <c r="AZ122" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA122" s="24" t="inlineStr">
+        <is>
+          <t>77804c68a4a17976e73de5a127cd27afaab30de3f32a7869f2309315b9e3f416</t>
+        </is>
+      </c>
+      <c r="BB122" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC122" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD122" s="24" t="inlineStr">
+        <is>
+          <t>77804c68a4a17976e73de5a127cd27afaab30de3f32a7869f2309315b9e3f416</t>
+        </is>
+      </c>
+      <c r="BE122" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF122" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG122" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH122" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:32:25.394431Z</t>
+        </is>
+      </c>
+      <c r="BI122" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ122" s="25" t="n"/>
+      <c r="BK122" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL122" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM122" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN122" s="28" t="n"/>
+      <c r="BO122" s="28" t="n"/>
+      <c r="BP122" s="25" t="n"/>
+      <c r="BQ122" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR122" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BS122" s="28" t="n"/>
+      <c r="BT122" s="28" t="n"/>
+      <c r="BU122" s="25" t="n"/>
+      <c r="BV122" s="29" t="n"/>
+      <c r="BW122" s="24" t="n"/>
+      <c r="BX122" s="30" t="n"/>
+      <c r="BY122" s="27" t="n"/>
+      <c r="BZ122" s="24" t="n"/>
+      <c r="CA122" s="31" t="n"/>
+      <c r="CB122" s="24" t="n"/>
+      <c r="CC122" s="24" t="n"/>
+      <c r="CD122" s="24" t="n"/>
+      <c r="CE122" s="24" t="n"/>
+      <c r="CF122" s="24" t="n"/>
+      <c r="CG122" s="24" t="n"/>
+      <c r="CH122" s="24" t="n"/>
+      <c r="CI122" s="24" t="n"/>
+      <c r="CJ122" s="24" t="n"/>
+      <c r="CK122" s="24" t="n"/>
+      <c r="CL122" s="24" t="n"/>
+      <c r="CM122" s="24" t="n"/>
+      <c r="CN122" s="24" t="n"/>
+      <c r="CO122" s="24" t="n"/>
+      <c r="CP122" s="24" t="n"/>
+      <c r="CQ122" s="24" t="n"/>
+      <c r="CR122" s="24" t="n"/>
+      <c r="CS122" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT122" s="24" t="n"/>
+      <c r="CU122" s="24" t="n"/>
+      <c r="CV122" s="24" t="n"/>
+      <c r="CW122" s="24" t="n"/>
+      <c r="CX122" s="24" t="n"/>
+      <c r="CY122" s="24" t="n"/>
+      <c r="CZ122" s="24" t="n"/>
+      <c r="DA122" s="24" t="n"/>
+      <c r="DB122" s="24" t="n"/>
+      <c r="DC122" s="24" t="n"/>
+      <c r="DD122" s="24" t="n"/>
+      <c r="DE122" s="24" t="n"/>
+      <c r="DF122" s="24" t="n"/>
+      <c r="DG122" s="24" t="n"/>
+      <c r="DH122" s="24" t="n"/>
+      <c r="DI122" s="24" t="n"/>
+      <c r="DJ122" s="24" t="n"/>
+      <c r="DK122" s="24" t="n"/>
+      <c r="DL122" s="24" t="n"/>
+      <c r="DM122" s="24" t="n"/>
+      <c r="DN122" s="24" t="n"/>
+      <c r="DO122" s="24" t="n"/>
+      <c r="DP122" s="24" t="n"/>
+      <c r="DQ122" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "77804c68a4a17976e73de5a127cd27afaab30de3f32a7869f2309315b9e3f416", "away_team": "CyberHero", "event_id": "147363", "event_start_utc": "2026-10-07T18:00:00Z", "features": {"away_elo": 1569.735616, "away_history_count": 3, "home_elo": 1551.480983, "home_history_count": 3}, "historical_source_observation_times_verified": false, "home_team": "Blasterbl", "inference_inputs": {"book_state": {"games_played": {"bo3:4:23832": 3, "bo3:4:25398": 3}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:23832": "2026-10-07T09:00:00Z", "bo3:4:25398": "2026-10-07T12:50:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07340728322508241, "platt_slope": 0.8514773257097051, "ratings": {"bo3:4:23832": 1551.480983, "bo3:4:25398": 1569.735616}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T16:32:25.298285+00:00", "team_ids": ["bo3:4:23832", "bo3:4:25398"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T16:32:25.298285+00:00", "probabilities": {"away": 0.502246, "home": 0.497754}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "8154548b6b33dee97f9700772469ce7ac6a57a577ee13aca6c4fed8410f500ec", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="24" t="inlineStr">
+        <is>
+          <t>f855d5cf44034bdc</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.225451Z</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr">
+        <is>
+          <t>147220</t>
+        </is>
+      </c>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="G123" s="24" t="inlineStr">
+        <is>
+          <t>InterActive Philippines</t>
+        </is>
+      </c>
+      <c r="H123" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I123" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J123" s="25" t="n"/>
+      <c r="K123" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L123" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M123" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N123" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O123" s="28" t="n">
+        <v>0.526899</v>
+      </c>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="28" t="n">
+        <v>-0.012272</v>
+      </c>
+      <c r="R123" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S123" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U123" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V123" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W123" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" s="25" t="n"/>
+      <c r="Z123" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA123" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB123" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC123" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD123" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:11.722429Z</t>
+        </is>
+      </c>
+      <c r="AE123" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-iac-db-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF123" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG123" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH123" s="24" t="n"/>
+      <c r="AI123" s="31" t="n"/>
+      <c r="AJ123" s="31" t="n"/>
+      <c r="AK123" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL123" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM123" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN123" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO123" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP123" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AQ123" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AR123" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AS123" s="24" t="inlineStr">
+        <is>
+          <t>InterActive Philippines</t>
+        </is>
+      </c>
+      <c r="AT123" s="24" t="inlineStr">
+        <is>
+          <t>InterActive Philippines</t>
+        </is>
+      </c>
+      <c r="AU123" s="24" t="inlineStr">
+        <is>
+          <t>InterActive Philippines</t>
+        </is>
+      </c>
+      <c r="AV123" s="24" t="n"/>
+      <c r="AW123" s="24" t="n"/>
+      <c r="AX123" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY123" s="24" t="n"/>
+      <c r="AZ123" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA123" s="24" t="inlineStr">
+        <is>
+          <t>baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51</t>
+        </is>
+      </c>
+      <c r="BB123" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC123" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD123" s="24" t="inlineStr">
+        <is>
+          <t>baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51</t>
+        </is>
+      </c>
+      <c r="BE123" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF123" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG123" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH123" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:21.735215Z</t>
+        </is>
+      </c>
+      <c r="BI123" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ123" s="25" t="n"/>
+      <c r="BK123" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL123" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM123" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN123" s="28" t="n"/>
+      <c r="BO123" s="28" t="n"/>
+      <c r="BP123" s="25" t="n"/>
+      <c r="BQ123" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR123" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS123" s="28" t="n"/>
+      <c r="BT123" s="28" t="n"/>
+      <c r="BU123" s="25" t="n"/>
+      <c r="BV123" s="29" t="n"/>
+      <c r="BW123" s="24" t="n"/>
+      <c r="BX123" s="30" t="n"/>
+      <c r="BY123" s="27" t="n"/>
+      <c r="BZ123" s="24" t="n"/>
+      <c r="CA123" s="31" t="n"/>
+      <c r="CB123" s="24" t="n"/>
+      <c r="CC123" s="24" t="n"/>
+      <c r="CD123" s="24" t="n"/>
+      <c r="CE123" s="24" t="n"/>
+      <c r="CF123" s="24" t="n"/>
+      <c r="CG123" s="24" t="n"/>
+      <c r="CH123" s="24" t="n"/>
+      <c r="CI123" s="24" t="n"/>
+      <c r="CJ123" s="24" t="n"/>
+      <c r="CK123" s="24" t="n"/>
+      <c r="CL123" s="24" t="n"/>
+      <c r="CM123" s="24" t="n"/>
+      <c r="CN123" s="24" t="n"/>
+      <c r="CO123" s="24" t="n"/>
+      <c r="CP123" s="24" t="n"/>
+      <c r="CQ123" s="24" t="n"/>
+      <c r="CR123" s="24" t="n"/>
+      <c r="CS123" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT123" s="24" t="n"/>
+      <c r="CU123" s="24" t="n"/>
+      <c r="CV123" s="24" t="n"/>
+      <c r="CW123" s="24" t="n"/>
+      <c r="CX123" s="24" t="n"/>
+      <c r="CY123" s="24" t="n"/>
+      <c r="CZ123" s="24" t="n"/>
+      <c r="DA123" s="24" t="n"/>
+      <c r="DB123" s="24" t="n"/>
+      <c r="DC123" s="24" t="n"/>
+      <c r="DD123" s="24" t="n"/>
+      <c r="DE123" s="24" t="n"/>
+      <c r="DF123" s="24" t="n"/>
+      <c r="DG123" s="24" t="n"/>
+      <c r="DH123" s="24" t="n"/>
+      <c r="DI123" s="24" t="n"/>
+      <c r="DJ123" s="24" t="n"/>
+      <c r="DK123" s="24" t="n"/>
+      <c r="DL123" s="24" t="n"/>
+      <c r="DM123" s="24" t="n"/>
+      <c r="DN123" s="24" t="n"/>
+      <c r="DO123" s="24" t="n"/>
+      <c r="DP123" s="24" t="n"/>
+      <c r="DQ123" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51", "away_team": "Direborn", "event_id": "147220", "event_start_utc": "2026-10-08T03:00:00Z", "features": {"away_elo": 1632.37521, "away_history_count": 39, "home_elo": 1591.369706, "home_history_count": 196}, "historical_source_observation_times_verified": false, "home_team": "InterActive Philippines", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15612": 196, "bo3:4:24344": 39}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15612": "2026-10-07T06:00:00Z", "bo3:4:24344": "2026-10-07T09:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07332109494800931, "platt_slope": 0.8507054355364946, "ratings": {"bo3:4:15612": 1591.369706, "bo3:4:24344": 1632.37521}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.585394+00:00", "team_ids": ["bo3:4:15612", "bo3:4:24344"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.585394+00:00", "probabilities": {"away": 0.526899, "home": 0.473101}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4c1cfbb6ee62a8dc4553a30cd7340239d2f33b5b1a6c3cde191076da88ad8a8c", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="A124" s="24" t="inlineStr">
+        <is>
+          <t>8a86e1e889754786</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.225451Z</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:30:00Z</t>
+        </is>
+      </c>
+      <c r="D124" s="24" t="inlineStr">
+        <is>
+          <t>143501</t>
+        </is>
+      </c>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="G124" s="24" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="H124" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I124" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J124" s="25" t="n"/>
+      <c r="K124" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L124" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M124" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N124" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O124" s="28" t="n">
+        <v>0.580766</v>
+      </c>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="28" t="n">
+        <v>0.041595</v>
+      </c>
+      <c r="R124" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S124" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U124" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V124" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W124" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y124" s="25" t="n"/>
+      <c r="Z124" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA124" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB124" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC124" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD124" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:13.160120Z</t>
+        </is>
+      </c>
+      <c r="AE124" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-aur-1win-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF124" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG124" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH124" s="24" t="n"/>
+      <c r="AI124" s="31" t="n"/>
+      <c r="AJ124" s="31" t="n"/>
+      <c r="AK124" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL124" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM124" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN124" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO124" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP124" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AQ124" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AR124" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AS124" s="24" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="AT124" s="24" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="AU124" s="24" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="AV124" s="24" t="n"/>
+      <c r="AW124" s="24" t="n"/>
+      <c r="AX124" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY124" s="24" t="n"/>
+      <c r="AZ124" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA124" s="24" t="inlineStr">
+        <is>
+          <t>baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51</t>
+        </is>
+      </c>
+      <c r="BB124" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC124" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD124" s="24" t="inlineStr">
+        <is>
+          <t>baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51</t>
+        </is>
+      </c>
+      <c r="BE124" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF124" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG124" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH124" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.208675Z</t>
+        </is>
+      </c>
+      <c r="BI124" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ124" s="25" t="n"/>
+      <c r="BK124" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL124" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM124" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN124" s="28" t="n"/>
+      <c r="BO124" s="28" t="n"/>
+      <c r="BP124" s="25" t="n"/>
+      <c r="BQ124" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR124" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS124" s="28" t="n"/>
+      <c r="BT124" s="28" t="n"/>
+      <c r="BU124" s="25" t="n"/>
+      <c r="BV124" s="29" t="n"/>
+      <c r="BW124" s="24" t="n"/>
+      <c r="BX124" s="30" t="n"/>
+      <c r="BY124" s="27" t="n"/>
+      <c r="BZ124" s="24" t="n"/>
+      <c r="CA124" s="31" t="n"/>
+      <c r="CB124" s="24" t="n"/>
+      <c r="CC124" s="24" t="n"/>
+      <c r="CD124" s="24" t="n"/>
+      <c r="CE124" s="24" t="n"/>
+      <c r="CF124" s="24" t="n"/>
+      <c r="CG124" s="24" t="n"/>
+      <c r="CH124" s="24" t="n"/>
+      <c r="CI124" s="24" t="n"/>
+      <c r="CJ124" s="24" t="n"/>
+      <c r="CK124" s="24" t="n"/>
+      <c r="CL124" s="24" t="n"/>
+      <c r="CM124" s="24" t="n"/>
+      <c r="CN124" s="24" t="n"/>
+      <c r="CO124" s="24" t="n"/>
+      <c r="CP124" s="24" t="n"/>
+      <c r="CQ124" s="24" t="n"/>
+      <c r="CR124" s="24" t="n"/>
+      <c r="CS124" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT124" s="24" t="n"/>
+      <c r="CU124" s="24" t="n"/>
+      <c r="CV124" s="24" t="n"/>
+      <c r="CW124" s="24" t="n"/>
+      <c r="CX124" s="24" t="n"/>
+      <c r="CY124" s="24" t="n"/>
+      <c r="CZ124" s="24" t="n"/>
+      <c r="DA124" s="24" t="n"/>
+      <c r="DB124" s="24" t="n"/>
+      <c r="DC124" s="24" t="n"/>
+      <c r="DD124" s="24" t="n"/>
+      <c r="DE124" s="24" t="n"/>
+      <c r="DF124" s="24" t="n"/>
+      <c r="DG124" s="24" t="n"/>
+      <c r="DH124" s="24" t="n"/>
+      <c r="DI124" s="24" t="n"/>
+      <c r="DJ124" s="24" t="n"/>
+      <c r="DK124" s="24" t="n"/>
+      <c r="DL124" s="24" t="n"/>
+      <c r="DM124" s="24" t="n"/>
+      <c r="DN124" s="24" t="n"/>
+      <c r="DO124" s="24" t="n"/>
+      <c r="DP124" s="24" t="n"/>
+      <c r="DQ124" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "baf9ccaa8f54c8de00adf9d2925d470d4e11611a62506fe2d568ed997460bb51", "away_team": "1win", "event_id": "143501", "event_start_utc": "2026-10-08T12:30:00Z", "features": {"away_elo": 1984.178977, "away_history_count": 317, "home_elo": 2050.731038, "home_history_count": 317}, "historical_source_observation_times_verified": false, "home_team": "Aurora", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15038": 317, "bo3:4:15143": 317}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15038": "2026-10-03T15:10:00Z", "bo3:4:15143": "2026-10-03T13:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07332109494800931, "platt_slope": 0.8507054355364946, "ratings": {"bo3:4:15038": 1984.178977, "bo3:4:15143": 2050.731038}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.585394+00:00", "team_ids": ["bo3:4:15143", "bo3:4:15038"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.585394+00:00", "probabilities": {"away": 0.419234, "home": 0.580766}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "0f8b095d31179e3a3017b2e93e816387139bd015f2830d12b6c2902f254875b1", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="24" t="inlineStr">
+        <is>
+          <t>7fe2e467c0c34f5a</t>
+        </is>
+      </c>
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:26:10.574372Z</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D125" s="24" t="inlineStr">
+        <is>
+          <t>153110</t>
+        </is>
+      </c>
+      <c r="E125" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F125" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="G125" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="H125" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I125" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J125" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K125" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L125" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M125" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N125" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O125" s="28" t="n">
+        <v>0.501559</v>
+      </c>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="28" t="n">
+        <v>-0.057912</v>
+      </c>
+      <c r="R125" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U125" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V125" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W125" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X125" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y125" s="25" t="n"/>
+      <c r="Z125" s="26" t="n"/>
+      <c r="AA125" s="28" t="n"/>
+      <c r="AB125" s="28" t="n"/>
+      <c r="AC125" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD125" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:04:53.300343Z</t>
+        </is>
+      </c>
+      <c r="AE125" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-dota2-ts-pari-2026-10-11-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF125" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG125" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH125" s="24" t="n"/>
+      <c r="AI125" s="31" t="n"/>
+      <c r="AJ125" s="31" t="n"/>
+      <c r="AK125" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL125" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM125" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN125" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO125" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP125" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AQ125" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AR125" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AS125" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AT125" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AU125" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AV125" s="24" t="n"/>
+      <c r="AW125" s="24" t="n"/>
+      <c r="AX125" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY125" s="24" t="n"/>
+      <c r="AZ125" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA125" s="24" t="inlineStr">
+        <is>
+          <t>e6ad89a5d5cd9c957bca5c6f529924ed1cad0a73c03e4b728aadeb70a4c6c573</t>
+        </is>
+      </c>
+      <c r="BB125" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC125" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD125" s="24" t="inlineStr">
+        <is>
+          <t>e6ad89a5d5cd9c957bca5c6f529924ed1cad0a73c03e4b728aadeb70a4c6c573</t>
+        </is>
+      </c>
+      <c r="BE125" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF125" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG125" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH125" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:29.357917Z</t>
+        </is>
+      </c>
+      <c r="BI125" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ125" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK125" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL125" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM125" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN125" s="28" t="n"/>
+      <c r="BO125" s="28" t="n"/>
+      <c r="BP125" s="25" t="n"/>
+      <c r="BQ125" s="27" t="n"/>
+      <c r="BR125" s="28" t="n"/>
+      <c r="BS125" s="28" t="n"/>
+      <c r="BT125" s="28" t="n"/>
+      <c r="BU125" s="25" t="n"/>
+      <c r="BV125" s="29" t="n"/>
+      <c r="BW125" s="24" t="n"/>
+      <c r="BX125" s="30" t="n"/>
+      <c r="BY125" s="27" t="n"/>
+      <c r="BZ125" s="24" t="n"/>
+      <c r="CA125" s="31" t="n"/>
+      <c r="CB125" s="24" t="n"/>
+      <c r="CC125" s="24" t="n"/>
+      <c r="CD125" s="24" t="n"/>
+      <c r="CE125" s="24" t="n"/>
+      <c r="CF125" s="24" t="n"/>
+      <c r="CG125" s="24" t="n"/>
+      <c r="CH125" s="24" t="n"/>
+      <c r="CI125" s="24" t="n"/>
+      <c r="CJ125" s="24" t="n"/>
+      <c r="CK125" s="24" t="n"/>
+      <c r="CL125" s="24" t="n"/>
+      <c r="CM125" s="24" t="n"/>
+      <c r="CN125" s="24" t="n"/>
+      <c r="CO125" s="24" t="n"/>
+      <c r="CP125" s="24" t="n"/>
+      <c r="CQ125" s="24" t="n"/>
+      <c r="CR125" s="24" t="n"/>
+      <c r="CS125" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT125" s="24" t="n"/>
+      <c r="CU125" s="24" t="n"/>
+      <c r="CV125" s="24" t="n"/>
+      <c r="CW125" s="24" t="n"/>
+      <c r="CX125" s="24" t="n"/>
+      <c r="CY125" s="24" t="n"/>
+      <c r="CZ125" s="24" t="n"/>
+      <c r="DA125" s="24" t="n"/>
+      <c r="DB125" s="24" t="n"/>
+      <c r="DC125" s="24" t="n"/>
+      <c r="DD125" s="24" t="n"/>
+      <c r="DE125" s="24" t="n"/>
+      <c r="DF125" s="24" t="n"/>
+      <c r="DG125" s="24" t="n"/>
+      <c r="DH125" s="24" t="n"/>
+      <c r="DI125" s="24" t="n"/>
+      <c r="DJ125" s="24" t="n"/>
+      <c r="DK125" s="24" t="n"/>
+      <c r="DL125" s="24" t="n"/>
+      <c r="DM125" s="24" t="n"/>
+      <c r="DN125" s="24" t="n"/>
+      <c r="DO125" s="24" t="n"/>
+      <c r="DP125" s="24" t="n"/>
+      <c r="DQ125" s="24" t="n"/>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="24" t="inlineStr">
+        <is>
+          <t>40042593c5ec4508</t>
+        </is>
+      </c>
+      <c r="B126" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:26:10.574372Z</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D126" s="24" t="inlineStr">
+        <is>
+          <t>153110</t>
+        </is>
+      </c>
+      <c r="E126" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F126" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="H126" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I126" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J126" s="25" t="n"/>
+      <c r="K126" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L126" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M126" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N126" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O126" s="28" t="n">
+        <v>0.54183</v>
+      </c>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="28" t="n">
+        <v>-0.15787</v>
+      </c>
+      <c r="R126" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U126" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V126" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W126" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y126" s="25" t="n"/>
+      <c r="Z126" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA126" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB126" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC126" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD126" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:04:54.481278Z</t>
+        </is>
+      </c>
+      <c r="AE126" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-ts-pari-2026-10-11).</t>
+        </is>
+      </c>
+      <c r="AF126" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG126" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH126" s="24" t="n"/>
+      <c r="AI126" s="31" t="n"/>
+      <c r="AJ126" s="31" t="n"/>
+      <c r="AK126" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL126" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM126" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN126" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO126" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP126" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AQ126" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AR126" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AS126" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AT126" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AU126" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AV126" s="24" t="n"/>
+      <c r="AW126" s="24" t="n"/>
+      <c r="AX126" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY126" s="24" t="n"/>
+      <c r="AZ126" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA126" s="24" t="inlineStr">
+        <is>
+          <t>e6ad89a5d5cd9c957bca5c6f529924ed1cad0a73c03e4b728aadeb70a4c6c573</t>
+        </is>
+      </c>
+      <c r="BB126" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC126" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD126" s="24" t="inlineStr">
+        <is>
+          <t>e6ad89a5d5cd9c957bca5c6f529924ed1cad0a73c03e4b728aadeb70a4c6c573</t>
+        </is>
+      </c>
+      <c r="BE126" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF126" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG126" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH126" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:39.511900Z</t>
+        </is>
+      </c>
+      <c r="BI126" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ126" s="25" t="n"/>
+      <c r="BK126" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL126" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM126" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN126" s="28" t="n"/>
+      <c r="BO126" s="28" t="n"/>
+      <c r="BP126" s="25" t="n"/>
+      <c r="BQ126" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR126" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS126" s="28" t="n"/>
+      <c r="BT126" s="28" t="n"/>
+      <c r="BU126" s="25" t="n"/>
+      <c r="BV126" s="29" t="n"/>
+      <c r="BW126" s="24" t="n"/>
+      <c r="BX126" s="30" t="n"/>
+      <c r="BY126" s="27" t="n"/>
+      <c r="BZ126" s="24" t="n"/>
+      <c r="CA126" s="31" t="n"/>
+      <c r="CB126" s="24" t="n"/>
+      <c r="CC126" s="24" t="n"/>
+      <c r="CD126" s="24" t="n"/>
+      <c r="CE126" s="24" t="n"/>
+      <c r="CF126" s="24" t="n"/>
+      <c r="CG126" s="24" t="n"/>
+      <c r="CH126" s="24" t="n"/>
+      <c r="CI126" s="24" t="n"/>
+      <c r="CJ126" s="24" t="n"/>
+      <c r="CK126" s="24" t="n"/>
+      <c r="CL126" s="24" t="n"/>
+      <c r="CM126" s="24" t="n"/>
+      <c r="CN126" s="24" t="n"/>
+      <c r="CO126" s="24" t="n"/>
+      <c r="CP126" s="24" t="n"/>
+      <c r="CQ126" s="24" t="n"/>
+      <c r="CR126" s="24" t="n"/>
+      <c r="CS126" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT126" s="24" t="n"/>
+      <c r="CU126" s="24" t="n"/>
+      <c r="CV126" s="24" t="n"/>
+      <c r="CW126" s="24" t="n"/>
+      <c r="CX126" s="24" t="n"/>
+      <c r="CY126" s="24" t="n"/>
+      <c r="CZ126" s="24" t="n"/>
+      <c r="DA126" s="24" t="n"/>
+      <c r="DB126" s="24" t="n"/>
+      <c r="DC126" s="24" t="n"/>
+      <c r="DD126" s="24" t="n"/>
+      <c r="DE126" s="24" t="n"/>
+      <c r="DF126" s="24" t="n"/>
+      <c r="DG126" s="24" t="n"/>
+      <c r="DH126" s="24" t="n"/>
+      <c r="DI126" s="24" t="n"/>
+      <c r="DJ126" s="24" t="n"/>
+      <c r="DK126" s="24" t="n"/>
+      <c r="DL126" s="24" t="n"/>
+      <c r="DM126" s="24" t="n"/>
+      <c r="DN126" s="24" t="n"/>
+      <c r="DO126" s="24" t="n"/>
+      <c r="DP126" s="24" t="n"/>
+      <c r="DQ126" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e6ad89a5d5cd9c957bca5c6f529924ed1cad0a73c03e4b728aadeb70a4c6c573", "away_team": "PARIVISION", "event_id": "153110", "event_start_utc": "2026-10-11T09:00:00Z", "features": {"away_elo": 2325.396544, "away_history_count": 251, "home_elo": 2270.921466, "home_history_count": 344}, "historical_source_observation_times_verified": false, "home_team": "Team Spirit", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16704": 344, "bo3:4:18604": 251}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16704": "2026-10-10T10:30:00Z", "bo3:4:18604": "2026-10-10T13:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06964891143172529, "platt_slope": 0.8461580414660153, "ratings": {"bo3:4:16704": 2270.921466, "bo3:4:18604": 2325.396544}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-11T07:25:19.138673+00:00", "team_ids": ["bo3:4:16704", "bo3:4:18604"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-11T07:25:19.138673+00:00", "probabilities": {"away": 0.54183, "home": 0.45817}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "7ef12b2318ffb4a13595ab212d3c9d59bb0fcf17abd3a4bcbdeff288b0edcf16", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="24" t="inlineStr">
+        <is>
+          <t>bf9f8308f6b74fe6</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:56:44.892731Z</t>
+        </is>
+      </c>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="D127" s="24" t="inlineStr">
+        <is>
+          <t>156703</t>
+        </is>
+      </c>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G127" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H127" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I127" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J127" s="25" t="n"/>
+      <c r="K127" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L127" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M127" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N127" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O127" s="28" t="n">
+        <v>0.652763</v>
+      </c>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="28" t="n">
+        <v>0.052763</v>
+      </c>
+      <c r="R127" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S127" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U127" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V127" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W127" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y127" s="25" t="n"/>
+      <c r="Z127" s="26" t="n"/>
+      <c r="AA127" s="28" t="n"/>
+      <c r="AB127" s="28" t="n"/>
+      <c r="AC127" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD127" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:26.524901Z</t>
+        </is>
+      </c>
+      <c r="AE127" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-lynx-z10-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF127" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG127" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH127" s="24" t="n"/>
+      <c r="AI127" s="31" t="n"/>
+      <c r="AJ127" s="31" t="n"/>
+      <c r="AK127" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL127" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM127" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN127" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO127" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP127" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ127" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR127" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS127" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT127" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU127" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV127" s="24" t="n"/>
+      <c r="AW127" s="24" t="n"/>
+      <c r="AX127" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY127" s="24" t="n"/>
+      <c r="AZ127" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA127" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BB127" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC127" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD127" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BE127" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF127" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG127" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH127" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:50:34.514198Z</t>
+        </is>
+      </c>
+      <c r="BI127" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ127" s="25" t="n"/>
+      <c r="BK127" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL127" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM127" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN127" s="28" t="n"/>
+      <c r="BO127" s="28" t="n"/>
+      <c r="BP127" s="25" t="n"/>
+      <c r="BQ127" s="27" t="n"/>
+      <c r="BR127" s="28" t="n"/>
+      <c r="BS127" s="28" t="n"/>
+      <c r="BT127" s="28" t="n"/>
+      <c r="BU127" s="25" t="n"/>
+      <c r="BV127" s="29" t="n"/>
+      <c r="BW127" s="24" t="n"/>
+      <c r="BX127" s="30" t="n"/>
+      <c r="BY127" s="27" t="n"/>
+      <c r="BZ127" s="24" t="n"/>
+      <c r="CA127" s="31" t="n"/>
+      <c r="CB127" s="24" t="n"/>
+      <c r="CC127" s="24" t="n"/>
+      <c r="CD127" s="24" t="n"/>
+      <c r="CE127" s="24" t="n"/>
+      <c r="CF127" s="24" t="n"/>
+      <c r="CG127" s="24" t="n"/>
+      <c r="CH127" s="24" t="n"/>
+      <c r="CI127" s="24" t="n"/>
+      <c r="CJ127" s="24" t="n"/>
+      <c r="CK127" s="24" t="n"/>
+      <c r="CL127" s="24" t="n"/>
+      <c r="CM127" s="24" t="n"/>
+      <c r="CN127" s="24" t="n"/>
+      <c r="CO127" s="24" t="n"/>
+      <c r="CP127" s="24" t="n"/>
+      <c r="CQ127" s="24" t="n"/>
+      <c r="CR127" s="24" t="n"/>
+      <c r="CS127" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT127" s="24" t="n"/>
+      <c r="CU127" s="24" t="n"/>
+      <c r="CV127" s="24" t="n"/>
+      <c r="CW127" s="24" t="n"/>
+      <c r="CX127" s="24" t="n"/>
+      <c r="CY127" s="24" t="n"/>
+      <c r="CZ127" s="24" t="n"/>
+      <c r="DA127" s="24" t="n"/>
+      <c r="DB127" s="24" t="n"/>
+      <c r="DC127" s="24" t="n"/>
+      <c r="DD127" s="24" t="n"/>
+      <c r="DE127" s="24" t="n"/>
+      <c r="DF127" s="24" t="n"/>
+      <c r="DG127" s="24" t="n"/>
+      <c r="DH127" s="24" t="n"/>
+      <c r="DI127" s="24" t="n"/>
+      <c r="DJ127" s="24" t="n"/>
+      <c r="DK127" s="24" t="n"/>
+      <c r="DL127" s="24" t="n"/>
+      <c r="DM127" s="24" t="n"/>
+      <c r="DN127" s="24" t="n"/>
+      <c r="DO127" s="24" t="n"/>
+      <c r="DP127" s="24" t="n"/>
+      <c r="DQ127" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f", "away_team": "Zero Tenacity", "event_id": "156703", "event_start_utc": "2026-10-13T07:00:00Z", "features": {"away_elo": 1583.870909, "away_history_count": 349, "home_elo": 1720.880148, "home_history_count": 185}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:18713": 349, "bo3:4:19913": 185}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:18713": "2026-10-09T16:25:00Z", "bo3:4:19913": "2026-10-12T16:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06660293057110224, "platt_slope": 0.8502014663873206, "ratings": {"bo3:4:18713": 1583.870909, "bo3:4:19913": 1720.880148}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T05:50:34.431410+00:00", "team_ids": ["bo3:4:19913", "bo3:4:18713"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T05:50:34.431410+00:00", "probabilities": {"away": 0.347237, "home": 0.652763}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a76a3bddcb7e8437baf8b35cd3af51cda6bb163aaaf843d281e21e8ee20c5ba1", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="24" t="inlineStr">
+        <is>
+          <t>14c624b263394f44</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:56:44.892731Z</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="D128" s="24" t="inlineStr">
+        <is>
+          <t>156703</t>
+        </is>
+      </c>
+      <c r="E128" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G128" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H128" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I128" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J128" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K128" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L128" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M128" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N128" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O128" s="28" t="n">
+        <v>0.521347</v>
+      </c>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="28" t="n">
+        <v>-0.028203</v>
+      </c>
+      <c r="R128" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S128" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U128" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V128" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W128" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X128" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y128" s="25" t="n"/>
+      <c r="Z128" s="26" t="n"/>
+      <c r="AA128" s="28" t="n"/>
+      <c r="AB128" s="28" t="n"/>
+      <c r="AC128" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD128" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T10:09:01.017706Z</t>
+        </is>
+      </c>
+      <c r="AE128" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=tsc-dota2-lynx-z10-2026-10-13-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF128" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG128" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH128" s="24" t="n"/>
+      <c r="AI128" s="31" t="n"/>
+      <c r="AJ128" s="31" t="n"/>
+      <c r="AK128" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL128" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM128" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN128" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO128" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP128" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ128" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR128" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS128" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT128" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU128" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV128" s="24" t="n"/>
+      <c r="AW128" s="24" t="n"/>
+      <c r="AX128" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY128" s="24" t="n"/>
+      <c r="AZ128" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA128" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BB128" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC128" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD128" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BE128" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF128" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG128" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH128" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:51:15.148583Z</t>
+        </is>
+      </c>
+      <c r="BI128" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ128" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK128" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL128" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM128" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN128" s="28" t="n"/>
+      <c r="BO128" s="28" t="n"/>
+      <c r="BP128" s="25" t="n"/>
+      <c r="BQ128" s="27" t="n"/>
+      <c r="BR128" s="28" t="n"/>
+      <c r="BS128" s="28" t="n"/>
+      <c r="BT128" s="28" t="n"/>
+      <c r="BU128" s="25" t="n"/>
+      <c r="BV128" s="29" t="n"/>
+      <c r="BW128" s="24" t="n"/>
+      <c r="BX128" s="30" t="n"/>
+      <c r="BY128" s="27" t="n"/>
+      <c r="BZ128" s="24" t="n"/>
+      <c r="CA128" s="31" t="n"/>
+      <c r="CB128" s="24" t="n"/>
+      <c r="CC128" s="24" t="n"/>
+      <c r="CD128" s="24" t="n"/>
+      <c r="CE128" s="24" t="n"/>
+      <c r="CF128" s="24" t="n"/>
+      <c r="CG128" s="24" t="n"/>
+      <c r="CH128" s="24" t="n"/>
+      <c r="CI128" s="24" t="n"/>
+      <c r="CJ128" s="24" t="n"/>
+      <c r="CK128" s="24" t="n"/>
+      <c r="CL128" s="24" t="n"/>
+      <c r="CM128" s="24" t="n"/>
+      <c r="CN128" s="24" t="n"/>
+      <c r="CO128" s="24" t="n"/>
+      <c r="CP128" s="24" t="n"/>
+      <c r="CQ128" s="24" t="n"/>
+      <c r="CR128" s="24" t="n"/>
+      <c r="CS128" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT128" s="24" t="n"/>
+      <c r="CU128" s="24" t="n"/>
+      <c r="CV128" s="24" t="n"/>
+      <c r="CW128" s="24" t="n"/>
+      <c r="CX128" s="24" t="n"/>
+      <c r="CY128" s="24" t="n"/>
+      <c r="CZ128" s="24" t="n"/>
+      <c r="DA128" s="24" t="n"/>
+      <c r="DB128" s="24" t="n"/>
+      <c r="DC128" s="24" t="n"/>
+      <c r="DD128" s="24" t="n"/>
+      <c r="DE128" s="24" t="n"/>
+      <c r="DF128" s="24" t="n"/>
+      <c r="DG128" s="24" t="n"/>
+      <c r="DH128" s="24" t="n"/>
+      <c r="DI128" s="24" t="n"/>
+      <c r="DJ128" s="24" t="n"/>
+      <c r="DK128" s="24" t="n"/>
+      <c r="DL128" s="24" t="n"/>
+      <c r="DM128" s="24" t="n"/>
+      <c r="DN128" s="24" t="n"/>
+      <c r="DO128" s="24" t="n"/>
+      <c r="DP128" s="24" t="n"/>
+      <c r="DQ128" s="24" t="n"/>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="24" t="inlineStr">
+        <is>
+          <t>921d7a1a56e34fb3</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:56:44.892731Z</t>
+        </is>
+      </c>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D129" s="24" t="inlineStr">
+        <is>
+          <t>156968</t>
+        </is>
+      </c>
+      <c r="E129" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>The goal of all life is death</t>
+        </is>
+      </c>
+      <c r="G129" s="24" t="inlineStr">
+        <is>
+          <t>Resp Gaming</t>
+        </is>
+      </c>
+      <c r="H129" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I129" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J129" s="25" t="n"/>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M129" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N129" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O129" s="28" t="n">
+        <v>0.519271</v>
+      </c>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="28" t="n">
+        <v>-0.011245</v>
+      </c>
+      <c r="R129" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S129" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U129" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V129" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W129" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y129" s="25" t="n"/>
+      <c r="Z129" s="26" t="n"/>
+      <c r="AA129" s="28" t="n"/>
+      <c r="AB129" s="28" t="n"/>
+      <c r="AC129" s="30" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AD129" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:27.852835Z</t>
+        </is>
+      </c>
+      <c r="AE129" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-rg-tgoalid-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF129" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG129" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH129" s="24" t="n"/>
+      <c r="AI129" s="31" t="n"/>
+      <c r="AJ129" s="31" t="n"/>
+      <c r="AK129" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL129" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM129" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN129" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO129" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP129" s="24" t="inlineStr">
+        <is>
+          <t>The goal of all life is death</t>
+        </is>
+      </c>
+      <c r="AQ129" s="24" t="inlineStr">
+        <is>
+          <t>The goal of all life is death</t>
+        </is>
+      </c>
+      <c r="AR129" s="24" t="inlineStr">
+        <is>
+          <t>The goal of all life is death</t>
+        </is>
+      </c>
+      <c r="AS129" s="24" t="inlineStr">
+        <is>
+          <t>Resp Gaming</t>
+        </is>
+      </c>
+      <c r="AT129" s="24" t="inlineStr">
+        <is>
+          <t>Resp Gaming</t>
+        </is>
+      </c>
+      <c r="AU129" s="24" t="inlineStr">
+        <is>
+          <t>Resp Gaming</t>
+        </is>
+      </c>
+      <c r="AV129" s="24" t="n"/>
+      <c r="AW129" s="24" t="n"/>
+      <c r="AX129" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY129" s="24" t="n"/>
+      <c r="AZ129" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA129" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BB129" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC129" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD129" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BE129" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF129" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG129" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH129" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:52:25.837911Z</t>
+        </is>
+      </c>
+      <c r="BI129" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ129" s="25" t="n"/>
+      <c r="BK129" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL129" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM129" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN129" s="28" t="n"/>
+      <c r="BO129" s="28" t="n"/>
+      <c r="BP129" s="25" t="n"/>
+      <c r="BQ129" s="27" t="n"/>
+      <c r="BR129" s="28" t="n"/>
+      <c r="BS129" s="28" t="n"/>
+      <c r="BT129" s="28" t="n"/>
+      <c r="BU129" s="25" t="n"/>
+      <c r="BV129" s="29" t="n"/>
+      <c r="BW129" s="24" t="n"/>
+      <c r="BX129" s="30" t="n"/>
+      <c r="BY129" s="27" t="n"/>
+      <c r="BZ129" s="24" t="n"/>
+      <c r="CA129" s="31" t="n"/>
+      <c r="CB129" s="24" t="n"/>
+      <c r="CC129" s="24" t="n"/>
+      <c r="CD129" s="24" t="n"/>
+      <c r="CE129" s="24" t="n"/>
+      <c r="CF129" s="24" t="n"/>
+      <c r="CG129" s="24" t="n"/>
+      <c r="CH129" s="24" t="n"/>
+      <c r="CI129" s="24" t="n"/>
+      <c r="CJ129" s="24" t="n"/>
+      <c r="CK129" s="24" t="n"/>
+      <c r="CL129" s="24" t="n"/>
+      <c r="CM129" s="24" t="n"/>
+      <c r="CN129" s="24" t="n"/>
+      <c r="CO129" s="24" t="n"/>
+      <c r="CP129" s="24" t="n"/>
+      <c r="CQ129" s="24" t="n"/>
+      <c r="CR129" s="24" t="n"/>
+      <c r="CS129" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT129" s="24" t="n"/>
+      <c r="CU129" s="24" t="n"/>
+      <c r="CV129" s="24" t="n"/>
+      <c r="CW129" s="24" t="n"/>
+      <c r="CX129" s="24" t="n"/>
+      <c r="CY129" s="24" t="n"/>
+      <c r="CZ129" s="24" t="n"/>
+      <c r="DA129" s="24" t="n"/>
+      <c r="DB129" s="24" t="n"/>
+      <c r="DC129" s="24" t="n"/>
+      <c r="DD129" s="24" t="n"/>
+      <c r="DE129" s="24" t="n"/>
+      <c r="DF129" s="24" t="n"/>
+      <c r="DG129" s="24" t="n"/>
+      <c r="DH129" s="24" t="n"/>
+      <c r="DI129" s="24" t="n"/>
+      <c r="DJ129" s="24" t="n"/>
+      <c r="DK129" s="24" t="n"/>
+      <c r="DL129" s="24" t="n"/>
+      <c r="DM129" s="24" t="n"/>
+      <c r="DN129" s="24" t="n"/>
+      <c r="DO129" s="24" t="n"/>
+      <c r="DP129" s="24" t="n"/>
+      <c r="DQ129" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f", "away_team": "The goal of all life is death", "event_id": "156968", "event_start_utc": "2026-10-13T08:00:00Z", "features": {"away_elo": 1466.255216, "away_history_count": 23, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "Resp Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15069": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15069": "2026-08-29T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06660293057110224, "platt_slope": 0.8502014663873206, "ratings": {"bo3:4:15069": 1466.255216}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T05:50:34.431410+00:00", "team_ids": ["unknown:respgaming", "bo3:4:15069"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T05:50:34.431410+00:00", "probabilities": {"away": 0.480729, "home": 0.519271}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "3b65f483251e622ee149930e14ede499ee4b55a8bb1f06123a073c275e3e6562", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="24" t="inlineStr">
+        <is>
+          <t>07b801af64c84863</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:56:44.892731Z</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D130" s="24" t="inlineStr">
+        <is>
+          <t>156670</t>
+        </is>
+      </c>
+      <c r="E130" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G130" s="24" t="inlineStr">
+        <is>
+          <t>HULIGANI</t>
+        </is>
+      </c>
+      <c r="H130" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I130" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J130" s="25" t="n"/>
+      <c r="K130" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M130" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N130" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O130" s="28" t="n">
+        <v>0.593184</v>
+      </c>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="28" t="n">
+        <v>0.033713</v>
+      </c>
+      <c r="R130" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S130" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U130" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V130" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W130" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" s="25" t="n"/>
+      <c r="Z130" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA130" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB130" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC130" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD130" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:29.277961Z</t>
+        </is>
+      </c>
+      <c r="AE130" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-hul-nemiga-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF130" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG130" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH130" s="24" t="n"/>
+      <c r="AI130" s="31" t="n"/>
+      <c r="AJ130" s="31" t="n"/>
+      <c r="AK130" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL130" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM130" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN130" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO130" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP130" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ130" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR130" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS130" s="24" t="inlineStr">
+        <is>
+          <t>HULIGANI</t>
+        </is>
+      </c>
+      <c r="AT130" s="24" t="inlineStr">
+        <is>
+          <t>HULIGANI</t>
+        </is>
+      </c>
+      <c r="AU130" s="24" t="inlineStr">
+        <is>
+          <t>HULIGANI</t>
+        </is>
+      </c>
+      <c r="AV130" s="24" t="n"/>
+      <c r="AW130" s="24" t="n"/>
+      <c r="AX130" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY130" s="24" t="n"/>
+      <c r="AZ130" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA130" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BB130" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC130" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD130" s="24" t="inlineStr">
+        <is>
+          <t>498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f</t>
+        </is>
+      </c>
+      <c r="BE130" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF130" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG130" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH130" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:52:36.540751Z</t>
+        </is>
+      </c>
+      <c r="BI130" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ130" s="25" t="n"/>
+      <c r="BK130" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL130" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM130" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN130" s="28" t="n"/>
+      <c r="BO130" s="28" t="n"/>
+      <c r="BP130" s="25" t="n"/>
+      <c r="BQ130" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR130" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BS130" s="28" t="n"/>
+      <c r="BT130" s="28" t="n"/>
+      <c r="BU130" s="25" t="n"/>
+      <c r="BV130" s="29" t="n"/>
+      <c r="BW130" s="24" t="n"/>
+      <c r="BX130" s="30" t="n"/>
+      <c r="BY130" s="27" t="n"/>
+      <c r="BZ130" s="24" t="n"/>
+      <c r="CA130" s="31" t="n"/>
+      <c r="CB130" s="24" t="n"/>
+      <c r="CC130" s="24" t="n"/>
+      <c r="CD130" s="24" t="n"/>
+      <c r="CE130" s="24" t="n"/>
+      <c r="CF130" s="24" t="n"/>
+      <c r="CG130" s="24" t="n"/>
+      <c r="CH130" s="24" t="n"/>
+      <c r="CI130" s="24" t="n"/>
+      <c r="CJ130" s="24" t="n"/>
+      <c r="CK130" s="24" t="n"/>
+      <c r="CL130" s="24" t="n"/>
+      <c r="CM130" s="24" t="n"/>
+      <c r="CN130" s="24" t="n"/>
+      <c r="CO130" s="24" t="n"/>
+      <c r="CP130" s="24" t="n"/>
+      <c r="CQ130" s="24" t="n"/>
+      <c r="CR130" s="24" t="n"/>
+      <c r="CS130" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT130" s="24" t="n"/>
+      <c r="CU130" s="24" t="n"/>
+      <c r="CV130" s="24" t="n"/>
+      <c r="CW130" s="24" t="n"/>
+      <c r="CX130" s="24" t="n"/>
+      <c r="CY130" s="24" t="n"/>
+      <c r="CZ130" s="24" t="n"/>
+      <c r="DA130" s="24" t="n"/>
+      <c r="DB130" s="24" t="n"/>
+      <c r="DC130" s="24" t="n"/>
+      <c r="DD130" s="24" t="n"/>
+      <c r="DE130" s="24" t="n"/>
+      <c r="DF130" s="24" t="n"/>
+      <c r="DG130" s="24" t="n"/>
+      <c r="DH130" s="24" t="n"/>
+      <c r="DI130" s="24" t="n"/>
+      <c r="DJ130" s="24" t="n"/>
+      <c r="DK130" s="24" t="n"/>
+      <c r="DL130" s="24" t="n"/>
+      <c r="DM130" s="24" t="n"/>
+      <c r="DN130" s="24" t="n"/>
+      <c r="DO130" s="24" t="n"/>
+      <c r="DP130" s="24" t="n"/>
+      <c r="DQ130" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "498068cbee0b727d651d5d989f095e8a43ce7662aad212f07b645d438261f98f", "away_team": "Nemiga Gaming", "event_id": "156670", "event_start_utc": "2026-10-13T09:00:00Z", "features": {"away_elo": 1464.093003, "away_history_count": 295, "home_elo": 1544.327209, "home_history_count": 337}, "historical_source_observation_times_verified": false, "home_team": "HULIGANI", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15098": 337, "bo3:4:16398": 295}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15098": "2026-10-06T08:10:00Z", "bo3:4:16398": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06660293057110224, "platt_slope": 0.8502014663873206, "ratings": {"bo3:4:15098": 1544.327209, "bo3:4:16398": 1464.093003}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T05:50:34.431410+00:00", "team_ids": ["bo3:4:15098", "bo3:4:16398"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T05:50:34.431410+00:00", "probabilities": {"away": 0.406816, "home": 0.593184}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1c8708fb5bbab32b607675cd051cb93a5e3de4c59fc3ccadd6eb3977bd7ceba2", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="24" t="inlineStr">
+        <is>
+          <t>fcd44b58014e4e0a</t>
+        </is>
+      </c>
+      <c r="B131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:23:20.635144Z</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D131" s="24" t="inlineStr">
+        <is>
+          <t>158060</t>
+        </is>
+      </c>
+      <c r="E131" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H131" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I131" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J131" s="25" t="n"/>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M131" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N131" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O131" s="28" t="n">
+        <v>0.585585</v>
+      </c>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="28" t="n">
+        <v>-0.114115</v>
+      </c>
+      <c r="R131" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U131" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W131" s="26" t="n"/>
+      <c r="X131" s="26" t="n"/>
+      <c r="Y131" s="25" t="n"/>
+      <c r="Z131" s="26" t="n"/>
+      <c r="AA131" s="28" t="n"/>
+      <c r="AB131" s="28" t="n"/>
+      <c r="AC131" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:40.843367Z</t>
+        </is>
+      </c>
+      <c r="AE131" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-tr-yb-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF131" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG131" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH131" s="24" t="n"/>
+      <c r="AI131" s="31" t="n"/>
+      <c r="AJ131" s="31" t="n"/>
+      <c r="AK131" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL131" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM131" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN131" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO131" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP131" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ131" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR131" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS131" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT131" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU131" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV131" s="24" t="n"/>
+      <c r="AW131" s="24" t="n"/>
+      <c r="AX131" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY131" s="24" t="n"/>
+      <c r="AZ131" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA131" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BB131" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC131" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD131" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BE131" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF131" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG131" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:18:19.188548Z</t>
+        </is>
+      </c>
+      <c r="BI131" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ131" s="25" t="n"/>
+      <c r="BK131" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL131" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM131" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN131" s="28" t="n"/>
+      <c r="BO131" s="28" t="n"/>
+      <c r="BP131" s="25" t="n"/>
+      <c r="BQ131" s="27" t="n"/>
+      <c r="BR131" s="28" t="n"/>
+      <c r="BS131" s="28" t="n"/>
+      <c r="BT131" s="28" t="n"/>
+      <c r="BU131" s="25" t="n"/>
+      <c r="BV131" s="29" t="n"/>
+      <c r="BW131" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {'Team Resilience': 0.66, 'Yakult Brothers': 0.34}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
+      <c r="BX131" s="30" t="n"/>
+      <c r="BY131" s="27" t="n"/>
+      <c r="BZ131" s="24" t="n"/>
+      <c r="CA131" s="31" t="n"/>
+      <c r="CB131" s="24" t="n"/>
+      <c r="CC131" s="24" t="n"/>
+      <c r="CD131" s="24" t="n"/>
+      <c r="CE131" s="24" t="n"/>
+      <c r="CF131" s="24" t="n"/>
+      <c r="CG131" s="24" t="n"/>
+      <c r="CH131" s="24" t="n"/>
+      <c r="CI131" s="24" t="n"/>
+      <c r="CJ131" s="24" t="n"/>
+      <c r="CK131" s="24" t="n"/>
+      <c r="CL131" s="24" t="n"/>
+      <c r="CM131" s="24" t="n"/>
+      <c r="CN131" s="24" t="n"/>
+      <c r="CO131" s="24" t="n"/>
+      <c r="CP131" s="24" t="n"/>
+      <c r="CQ131" s="24" t="n"/>
+      <c r="CR131" s="24" t="n"/>
+      <c r="CS131" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT131" s="24" t="n"/>
+      <c r="CU131" s="24" t="n"/>
+      <c r="CV131" s="24" t="n"/>
+      <c r="CW131" s="24" t="n"/>
+      <c r="CX131" s="24" t="n"/>
+      <c r="CY131" s="24" t="n"/>
+      <c r="CZ131" s="24" t="n"/>
+      <c r="DA131" s="24" t="n"/>
+      <c r="DB131" s="24" t="n"/>
+      <c r="DC131" s="24" t="n"/>
+      <c r="DD131" s="24" t="n"/>
+      <c r="DE131" s="24" t="n"/>
+      <c r="DF131" s="24" t="n"/>
+      <c r="DG131" s="24" t="n"/>
+      <c r="DH131" s="24" t="n"/>
+      <c r="DI131" s="24" t="n"/>
+      <c r="DJ131" s="24" t="n"/>
+      <c r="DK131" s="24" t="n"/>
+      <c r="DL131" s="24" t="n"/>
+      <c r="DM131" s="24" t="n"/>
+      <c r="DN131" s="24" t="n"/>
+      <c r="DO131" s="24" t="n"/>
+      <c r="DP131" s="24" t="n"/>
+      <c r="DQ131" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601", "away_team": "Yakult Brothers", "event_id": "158060", "event_start_utc": "2026-10-13T12:00:00Z", "features": {"away_elo": 1669.762098, "away_history_count": 187, "home_elo": 1740.091782, "home_history_count": 22}, "historical_source_observation_times_verified": false, "home_team": "Team Resilience", "inference_inputs": {"book_state": {"games_played": {"bo3:4:18586": 187, "bo3:4:23196": 22}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:18586": "2026-10-13T04:00:00Z", "bo3:4:23196": "2026-10-13T04:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06516991331836251, "platt_slope": 0.8491312027850109, "ratings": {"bo3:4:18586": 1669.762098, "bo3:4:23196": 1740.091782}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T11:18:19.094097+00:00", "team_ids": ["bo3:4:23196", "bo3:4:18586"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T11:18:19.094097+00:00", "probabilities": {"away": 0.414415, "home": 0.585585}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "30fb7e04208f443731ef0e51cde435c290820fa84f88e1026fadf40a9b4bf015", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="24" t="inlineStr">
+        <is>
+          <t>44985e069e194be8</t>
+        </is>
+      </c>
+      <c r="B132" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:23:20.635144Z</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D132" s="24" t="inlineStr">
+        <is>
+          <t>155060</t>
+        </is>
+      </c>
+      <c r="E132" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="G132" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H132" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I132" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J132" s="25" t="n"/>
+      <c r="K132" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M132" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N132" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O132" s="28" t="n">
+        <v>0.531826</v>
+      </c>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="28" t="n">
+        <v>-0.148685</v>
+      </c>
+      <c r="R132" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U132" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V132" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W132" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y132" s="25" t="n"/>
+      <c r="Z132" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA132" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB132" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC132" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD132" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:07:05.045625Z</t>
+        </is>
+      </c>
+      <c r="AE132" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-dota2-pr-twh-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF132" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG132" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH132" s="24" t="n"/>
+      <c r="AI132" s="31" t="n"/>
+      <c r="AJ132" s="31" t="n"/>
+      <c r="AK132" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL132" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM132" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN132" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO132" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP132" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AQ132" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AR132" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AS132" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT132" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU132" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV132" s="24" t="n"/>
+      <c r="AW132" s="24" t="n"/>
+      <c r="AX132" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY132" s="24" t="n"/>
+      <c r="AZ132" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA132" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BB132" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC132" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD132" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BE132" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF132" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG132" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH132" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:20:23.851640Z</t>
+        </is>
+      </c>
+      <c r="BI132" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ132" s="25" t="n"/>
+      <c r="BK132" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL132" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM132" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN132" s="28" t="n"/>
+      <c r="BO132" s="28" t="n"/>
+      <c r="BP132" s="25" t="n"/>
+      <c r="BQ132" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR132" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BS132" s="28" t="n"/>
+      <c r="BT132" s="28" t="n"/>
+      <c r="BU132" s="25" t="n"/>
+      <c r="BV132" s="29" t="n"/>
+      <c r="BW132" s="24" t="n"/>
+      <c r="BX132" s="30" t="n"/>
+      <c r="BY132" s="27" t="n"/>
+      <c r="BZ132" s="24" t="n"/>
+      <c r="CA132" s="31" t="n"/>
+      <c r="CB132" s="24" t="n"/>
+      <c r="CC132" s="24" t="n"/>
+      <c r="CD132" s="24" t="n"/>
+      <c r="CE132" s="24" t="n"/>
+      <c r="CF132" s="24" t="n"/>
+      <c r="CG132" s="24" t="n"/>
+      <c r="CH132" s="24" t="n"/>
+      <c r="CI132" s="24" t="n"/>
+      <c r="CJ132" s="24" t="n"/>
+      <c r="CK132" s="24" t="n"/>
+      <c r="CL132" s="24" t="n"/>
+      <c r="CM132" s="24" t="n"/>
+      <c r="CN132" s="24" t="n"/>
+      <c r="CO132" s="24" t="n"/>
+      <c r="CP132" s="24" t="n"/>
+      <c r="CQ132" s="24" t="n"/>
+      <c r="CR132" s="24" t="n"/>
+      <c r="CS132" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT132" s="24" t="n"/>
+      <c r="CU132" s="24" t="n"/>
+      <c r="CV132" s="24" t="n"/>
+      <c r="CW132" s="24" t="n"/>
+      <c r="CX132" s="24" t="n"/>
+      <c r="CY132" s="24" t="n"/>
+      <c r="CZ132" s="24" t="n"/>
+      <c r="DA132" s="24" t="n"/>
+      <c r="DB132" s="24" t="n"/>
+      <c r="DC132" s="24" t="n"/>
+      <c r="DD132" s="24" t="n"/>
+      <c r="DE132" s="24" t="n"/>
+      <c r="DF132" s="24" t="n"/>
+      <c r="DG132" s="24" t="n"/>
+      <c r="DH132" s="24" t="n"/>
+      <c r="DI132" s="24" t="n"/>
+      <c r="DJ132" s="24" t="n"/>
+      <c r="DK132" s="24" t="n"/>
+      <c r="DL132" s="24" t="n"/>
+      <c r="DM132" s="24" t="n"/>
+      <c r="DN132" s="24" t="n"/>
+      <c r="DO132" s="24" t="n"/>
+      <c r="DP132" s="24" t="n"/>
+      <c r="DQ132" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601", "away_team": "The Warriors", "event_id": "155060", "event_start_utc": "2026-10-13T13:00:00Z", "features": {"away_elo": 1573.452002, "away_history_count": 4, "home_elo": 1638.365225, "home_history_count": 93}, "historical_source_observation_times_verified": false, "home_team": "Power Rangers", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16653": 93, "bo3:4:25465": 4}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16653": "2026-09-08T09:00:00Z", "bo3:4:25465": "2026-10-12T19:25:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06516991331836251, "platt_slope": 0.8491312027850109, "ratings": {"bo3:4:16653": 1638.365225, "bo3:4:25465": 1573.452002}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T11:18:19.094097+00:00", "team_ids": ["bo3:4:16653", "bo3:4:25465"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T11:18:19.094097+00:00", "probabilities": {"away": 0.468174, "home": 0.531826}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "750d1ac2c44427d0341e3eb3cc2b85cb66e4553a14c56abf9b250e3ae4683337", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="24" t="inlineStr">
+        <is>
+          <t>bf6127e16a554ba4</t>
+        </is>
+      </c>
+      <c r="B133" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:23:20.635144Z</t>
+        </is>
+      </c>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D133" s="24" t="inlineStr">
+        <is>
+          <t>155060</t>
+        </is>
+      </c>
+      <c r="E133" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F133" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H133" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I133" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J133" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K133" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M133" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N133" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O133" s="28" t="n">
+        <v>0.500901</v>
+      </c>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="28" t="n">
+        <v>-0.078931</v>
+      </c>
+      <c r="R133" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U133" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V133" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W133" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X133" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y133" s="25" t="n"/>
+      <c r="Z133" s="26" t="n"/>
+      <c r="AA133" s="28" t="n"/>
+      <c r="AB133" s="28" t="n"/>
+      <c r="AC133" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD133" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:42.247257Z</t>
+        </is>
+      </c>
+      <c r="AE133" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=tsc-dota2-pr-twh-2026-10-13-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF133" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG133" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH133" s="24" t="n"/>
+      <c r="AI133" s="31" t="n"/>
+      <c r="AJ133" s="31" t="n"/>
+      <c r="AK133" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL133" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM133" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN133" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO133" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP133" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AQ133" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AR133" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AS133" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT133" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU133" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV133" s="24" t="n"/>
+      <c r="AW133" s="24" t="n"/>
+      <c r="AX133" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY133" s="24" t="n"/>
+      <c r="AZ133" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA133" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BB133" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC133" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD133" s="24" t="inlineStr">
+        <is>
+          <t>82eaf6866c5f8a33c82bd6297df9b8c17cc34456cc7a74fdcb602fb4705d7601</t>
+        </is>
+      </c>
+      <c r="BE133" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF133" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG133" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH133" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T11:20:23.925214Z</t>
+        </is>
+      </c>
+      <c r="BI133" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ133" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK133" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL133" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM133" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN133" s="28" t="n"/>
+      <c r="BO133" s="28" t="n"/>
+      <c r="BP133" s="25" t="n"/>
+      <c r="BQ133" s="27" t="n"/>
+      <c r="BR133" s="28" t="n"/>
+      <c r="BS133" s="28" t="n"/>
+      <c r="BT133" s="28" t="n"/>
+      <c r="BU133" s="25" t="n"/>
+      <c r="BV133" s="29" t="n"/>
+      <c r="BW133" s="24" t="n"/>
+      <c r="BX133" s="30" t="n"/>
+      <c r="BY133" s="27" t="n"/>
+      <c r="BZ133" s="24" t="n"/>
+      <c r="CA133" s="31" t="n"/>
+      <c r="CB133" s="24" t="n"/>
+      <c r="CC133" s="24" t="n"/>
+      <c r="CD133" s="24" t="n"/>
+      <c r="CE133" s="24" t="n"/>
+      <c r="CF133" s="24" t="n"/>
+      <c r="CG133" s="24" t="n"/>
+      <c r="CH133" s="24" t="n"/>
+      <c r="CI133" s="24" t="n"/>
+      <c r="CJ133" s="24" t="n"/>
+      <c r="CK133" s="24" t="n"/>
+      <c r="CL133" s="24" t="n"/>
+      <c r="CM133" s="24" t="n"/>
+      <c r="CN133" s="24" t="n"/>
+      <c r="CO133" s="24" t="n"/>
+      <c r="CP133" s="24" t="n"/>
+      <c r="CQ133" s="24" t="n"/>
+      <c r="CR133" s="24" t="n"/>
+      <c r="CS133" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT133" s="24" t="n"/>
+      <c r="CU133" s="24" t="n"/>
+      <c r="CV133" s="24" t="n"/>
+      <c r="CW133" s="24" t="n"/>
+      <c r="CX133" s="24" t="n"/>
+      <c r="CY133" s="24" t="n"/>
+      <c r="CZ133" s="24" t="n"/>
+      <c r="DA133" s="24" t="n"/>
+      <c r="DB133" s="24" t="n"/>
+      <c r="DC133" s="24" t="n"/>
+      <c r="DD133" s="24" t="n"/>
+      <c r="DE133" s="24" t="n"/>
+      <c r="DF133" s="24" t="n"/>
+      <c r="DG133" s="24" t="n"/>
+      <c r="DH133" s="24" t="n"/>
+      <c r="DI133" s="24" t="n"/>
+      <c r="DJ133" s="24" t="n"/>
+      <c r="DK133" s="24" t="n"/>
+      <c r="DL133" s="24" t="n"/>
+      <c r="DM133" s="24" t="n"/>
+      <c r="DN133" s="24" t="n"/>
+      <c r="DO133" s="24" t="n"/>
+      <c r="DP133" s="24" t="n"/>
+      <c r="DQ133" s="24" t="n"/>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="24" t="inlineStr">
+        <is>
+          <t>7112eb1a247f4f86</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:03:07.936006Z</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D134" s="24" t="inlineStr">
+        <is>
+          <t>156711</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G134" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="H134" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I134" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J134" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K134" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L134" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M134" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N134" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O134" s="28" t="n">
+        <v>0.50279</v>
+      </c>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="28" t="n">
+        <v>-0.068025</v>
+      </c>
+      <c r="R134" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U134" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V134" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W134" s="26" t="n"/>
+      <c r="X134" s="26" t="n"/>
+      <c r="Y134" s="25" t="n"/>
+      <c r="Z134" s="26" t="n"/>
+      <c r="AA134" s="28" t="n"/>
+      <c r="AB134" s="28" t="n"/>
+      <c r="AC134" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:07:11.470467Z</t>
+        </is>
+      </c>
+      <c r="AE134" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-dota2-twh-sala-2026-10-13-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF134" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG134" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH134" s="24" t="n"/>
+      <c r="AI134" s="31" t="n"/>
+      <c r="AJ134" s="31" t="n"/>
+      <c r="AK134" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL134" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM134" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN134" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO134" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP134" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ134" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR134" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS134" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AT134" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AU134" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AV134" s="24" t="n"/>
+      <c r="AW134" s="24" t="n"/>
+      <c r="AX134" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY134" s="24" t="n"/>
+      <c r="AZ134" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA134" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BB134" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC134" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD134" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BE134" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF134" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG134" s="24" t="inlineStr">
+        <is>
+          <t>dota2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH134" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:00:10.303927Z</t>
+        </is>
+      </c>
+      <c r="BI134" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ134" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK134" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL134" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM134" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN134" s="28" t="n"/>
+      <c r="BO134" s="28" t="n"/>
+      <c r="BP134" s="25" t="n"/>
+      <c r="BQ134" s="27" t="n"/>
+      <c r="BR134" s="28" t="n"/>
+      <c r="BS134" s="28" t="n"/>
+      <c r="BT134" s="28" t="n"/>
+      <c r="BU134" s="25" t="n"/>
+      <c r="BV134" s="29" t="n"/>
+      <c r="BW134" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
+      <c r="BX134" s="30" t="n"/>
+      <c r="BY134" s="27" t="n"/>
+      <c r="BZ134" s="24" t="n"/>
+      <c r="CA134" s="31" t="n"/>
+      <c r="CB134" s="24" t="n"/>
+      <c r="CC134" s="24" t="n"/>
+      <c r="CD134" s="24" t="n"/>
+      <c r="CE134" s="24" t="n"/>
+      <c r="CF134" s="24" t="n"/>
+      <c r="CG134" s="24" t="n"/>
+      <c r="CH134" s="24" t="n"/>
+      <c r="CI134" s="24" t="n"/>
+      <c r="CJ134" s="24" t="n"/>
+      <c r="CK134" s="24" t="n"/>
+      <c r="CL134" s="24" t="n"/>
+      <c r="CM134" s="24" t="n"/>
+      <c r="CN134" s="24" t="n"/>
+      <c r="CO134" s="24" t="n"/>
+      <c r="CP134" s="24" t="n"/>
+      <c r="CQ134" s="24" t="n"/>
+      <c r="CR134" s="24" t="n"/>
+      <c r="CS134" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT134" s="24" t="n"/>
+      <c r="CU134" s="24" t="n"/>
+      <c r="CV134" s="24" t="n"/>
+      <c r="CW134" s="24" t="n"/>
+      <c r="CX134" s="24" t="n"/>
+      <c r="CY134" s="24" t="n"/>
+      <c r="CZ134" s="24" t="n"/>
+      <c r="DA134" s="24" t="n"/>
+      <c r="DB134" s="24" t="n"/>
+      <c r="DC134" s="24" t="n"/>
+      <c r="DD134" s="24" t="n"/>
+      <c r="DE134" s="24" t="n"/>
+      <c r="DF134" s="24" t="n"/>
+      <c r="DG134" s="24" t="n"/>
+      <c r="DH134" s="24" t="n"/>
+      <c r="DI134" s="24" t="n"/>
+      <c r="DJ134" s="24" t="n"/>
+      <c r="DK134" s="24" t="n"/>
+      <c r="DL134" s="24" t="n"/>
+      <c r="DM134" s="24" t="n"/>
+      <c r="DN134" s="24" t="n"/>
+      <c r="DO134" s="24" t="n"/>
+      <c r="DP134" s="24" t="n"/>
+      <c r="DQ134" s="24" t="n"/>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="24" t="inlineStr">
+        <is>
+          <t>3c634e378d3c4ef4</t>
+        </is>
+      </c>
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:03:07.936006Z</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D135" s="24" t="inlineStr">
+        <is>
+          <t>156711</t>
+        </is>
+      </c>
+      <c r="E135" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F135" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G135" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="H135" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I135" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J135" s="25" t="n"/>
+      <c r="K135" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M135" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N135" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O135" s="28" t="n">
+        <v>0.555922</v>
+      </c>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="28" t="n">
+        <v>0.215786</v>
+      </c>
+      <c r="R135" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S135" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T135" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U135" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W135" s="26" t="n"/>
+      <c r="X135" s="26" t="n"/>
+      <c r="Y135" s="25" t="n"/>
+      <c r="Z135" s="26" t="n"/>
+      <c r="AA135" s="28" t="n"/>
+      <c r="AB135" s="28" t="n"/>
+      <c r="AC135" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:07:16.319688Z</t>
+        </is>
+      </c>
+      <c r="AE135" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-dota2-twh-sala-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF135" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG135" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH135" s="24" t="n"/>
+      <c r="AI135" s="31" t="n"/>
+      <c r="AJ135" s="31" t="n"/>
+      <c r="AK135" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL135" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM135" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN135" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO135" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP135" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ135" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR135" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS135" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AT135" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AU135" s="24" t="inlineStr">
+        <is>
+          <t>The Warriors</t>
+        </is>
+      </c>
+      <c r="AV135" s="24" t="n"/>
+      <c r="AW135" s="24" t="n"/>
+      <c r="AX135" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY135" s="24" t="n"/>
+      <c r="AZ135" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA135" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BB135" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC135" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD135" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BE135" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF135" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG135" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:00:20.578625Z</t>
+        </is>
+      </c>
+      <c r="BI135" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ135" s="25" t="n"/>
+      <c r="BK135" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL135" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM135" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN135" s="28" t="n"/>
+      <c r="BO135" s="28" t="n"/>
+      <c r="BP135" s="25" t="n"/>
+      <c r="BQ135" s="27" t="n"/>
+      <c r="BR135" s="28" t="n"/>
+      <c r="BS135" s="28" t="n"/>
+      <c r="BT135" s="28" t="n"/>
+      <c r="BU135" s="25" t="n"/>
+      <c r="BV135" s="29" t="n"/>
+      <c r="BW135" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
+      <c r="BX135" s="30" t="n"/>
+      <c r="BY135" s="27" t="n"/>
+      <c r="BZ135" s="24" t="n"/>
+      <c r="CA135" s="31" t="n"/>
+      <c r="CB135" s="24" t="n"/>
+      <c r="CC135" s="24" t="n"/>
+      <c r="CD135" s="24" t="n"/>
+      <c r="CE135" s="24" t="n"/>
+      <c r="CF135" s="24" t="n"/>
+      <c r="CG135" s="24" t="n"/>
+      <c r="CH135" s="24" t="n"/>
+      <c r="CI135" s="24" t="n"/>
+      <c r="CJ135" s="24" t="n"/>
+      <c r="CK135" s="24" t="n"/>
+      <c r="CL135" s="24" t="n"/>
+      <c r="CM135" s="24" t="n"/>
+      <c r="CN135" s="24" t="n"/>
+      <c r="CO135" s="24" t="n"/>
+      <c r="CP135" s="24" t="n"/>
+      <c r="CQ135" s="24" t="n"/>
+      <c r="CR135" s="24" t="n"/>
+      <c r="CS135" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT135" s="24" t="n"/>
+      <c r="CU135" s="24" t="n"/>
+      <c r="CV135" s="24" t="n"/>
+      <c r="CW135" s="24" t="n"/>
+      <c r="CX135" s="24" t="n"/>
+      <c r="CY135" s="24" t="n"/>
+      <c r="CZ135" s="24" t="n"/>
+      <c r="DA135" s="24" t="n"/>
+      <c r="DB135" s="24" t="n"/>
+      <c r="DC135" s="24" t="n"/>
+      <c r="DD135" s="24" t="n"/>
+      <c r="DE135" s="24" t="n"/>
+      <c r="DF135" s="24" t="n"/>
+      <c r="DG135" s="24" t="n"/>
+      <c r="DH135" s="24" t="n"/>
+      <c r="DI135" s="24" t="n"/>
+      <c r="DJ135" s="24" t="n"/>
+      <c r="DK135" s="24" t="n"/>
+      <c r="DL135" s="24" t="n"/>
+      <c r="DM135" s="24" t="n"/>
+      <c r="DN135" s="24" t="n"/>
+      <c r="DO135" s="24" t="n"/>
+      <c r="DP135" s="24" t="n"/>
+      <c r="DQ135" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3", "away_team": "salamit", "event_id": "156711", "event_start_utc": "2026-10-13T19:00:00Z", "features": {"away_elo": 1460.291035, "away_history_count": 1, "home_elo": 1546.705133, "home_history_count": 5}, "historical_source_observation_times_verified": false, "home_team": "The Warriors", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25465": 5, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25465": "2026-10-13T13:15:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0660951180882821, "platt_slope": 0.8503469876096356, "ratings": {"bo3:4:25465": 1546.705133, "bo3:4:25478": 1460.291035}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T16:58:36.903465+00:00", "team_ids": ["bo3:4:25465", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T16:58:36.903465+00:00", "probabilities": {"away": 0.444078, "home": 0.555922}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2f2a234e6a44119421ca10c14d5f4e4e09831bd4f160550721c7e4aaf1a169d4", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="24" t="inlineStr">
+        <is>
+          <t>5b7d9204e4244e2f</t>
+        </is>
+      </c>
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:03:07.936006Z</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D136" s="24" t="inlineStr">
+        <is>
+          <t>156778</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F136" s="24" t="inlineStr">
+        <is>
+          <t>Rottweilas Latam</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H136" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I136" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J136" s="25" t="n"/>
+      <c r="K136" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L136" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M136" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N136" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O136" s="28" t="n">
+        <v>0.522778</v>
+      </c>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="28" t="n">
+        <v>0.093593</v>
+      </c>
+      <c r="R136" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S136" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T136" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U136" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W136" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y136" s="25" t="n"/>
+      <c r="Z136" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="AA136" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB136" s="28" t="n">
+        <v>0.000815</v>
+      </c>
+      <c r="AC136" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:33:17.836664Z</t>
+        </is>
+      </c>
+      <c r="AE136" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-agm-rl-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF136" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG136" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH136" s="24" t="n"/>
+      <c r="AI136" s="31" t="n"/>
+      <c r="AJ136" s="31" t="n"/>
+      <c r="AK136" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL136" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM136" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN136" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO136" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP136" s="24" t="inlineStr">
+        <is>
+          <t>Rottweilas Latam</t>
+        </is>
+      </c>
+      <c r="AQ136" s="24" t="inlineStr">
+        <is>
+          <t>Rottweilas Latam</t>
+        </is>
+      </c>
+      <c r="AR136" s="24" t="inlineStr">
+        <is>
+          <t>Rottweilas Latam</t>
+        </is>
+      </c>
+      <c r="AS136" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT136" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU136" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV136" s="24" t="n"/>
+      <c r="AW136" s="24" t="n"/>
+      <c r="AX136" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY136" s="24" t="n"/>
+      <c r="AZ136" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA136" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BB136" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC136" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD136" s="24" t="inlineStr">
+        <is>
+          <t>dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3</t>
+        </is>
+      </c>
+      <c r="BE136" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF136" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG136" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:00:20.655668Z</t>
+        </is>
+      </c>
+      <c r="BI136" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ136" s="25" t="n"/>
+      <c r="BK136" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL136" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM136" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN136" s="28" t="n"/>
+      <c r="BO136" s="28" t="n"/>
+      <c r="BP136" s="25" t="n"/>
+      <c r="BQ136" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BR136" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BS136" s="28" t="n"/>
+      <c r="BT136" s="28" t="n"/>
+      <c r="BU136" s="25" t="n"/>
+      <c r="BV136" s="29" t="n"/>
+      <c r="BW136" s="24" t="n"/>
+      <c r="BX136" s="30" t="n"/>
+      <c r="BY136" s="27" t="n"/>
+      <c r="BZ136" s="24" t="n"/>
+      <c r="CA136" s="31" t="n"/>
+      <c r="CB136" s="24" t="n"/>
+      <c r="CC136" s="24" t="n"/>
+      <c r="CD136" s="24" t="n"/>
+      <c r="CE136" s="24" t="n"/>
+      <c r="CF136" s="24" t="n"/>
+      <c r="CG136" s="24" t="n"/>
+      <c r="CH136" s="24" t="n"/>
+      <c r="CI136" s="24" t="n"/>
+      <c r="CJ136" s="24" t="n"/>
+      <c r="CK136" s="24" t="n"/>
+      <c r="CL136" s="24" t="n"/>
+      <c r="CM136" s="24" t="n"/>
+      <c r="CN136" s="24" t="n"/>
+      <c r="CO136" s="24" t="n"/>
+      <c r="CP136" s="24" t="n"/>
+      <c r="CQ136" s="24" t="n"/>
+      <c r="CR136" s="24" t="n"/>
+      <c r="CS136" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT136" s="24" t="n"/>
+      <c r="CU136" s="24" t="n"/>
+      <c r="CV136" s="24" t="n"/>
+      <c r="CW136" s="24" t="n"/>
+      <c r="CX136" s="24" t="n"/>
+      <c r="CY136" s="24" t="n"/>
+      <c r="CZ136" s="24" t="n"/>
+      <c r="DA136" s="24" t="n"/>
+      <c r="DB136" s="24" t="n"/>
+      <c r="DC136" s="24" t="n"/>
+      <c r="DD136" s="24" t="n"/>
+      <c r="DE136" s="24" t="n"/>
+      <c r="DF136" s="24" t="n"/>
+      <c r="DG136" s="24" t="n"/>
+      <c r="DH136" s="24" t="n"/>
+      <c r="DI136" s="24" t="n"/>
+      <c r="DJ136" s="24" t="n"/>
+      <c r="DK136" s="24" t="n"/>
+      <c r="DL136" s="24" t="n"/>
+      <c r="DM136" s="24" t="n"/>
+      <c r="DN136" s="24" t="n"/>
+      <c r="DO136" s="24" t="n"/>
+      <c r="DP136" s="24" t="n"/>
+      <c r="DQ136" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dbdf8c3e3bd3daca22666c2f38605f226d67625f4460aace1c5df263d8fc71b3", "away_team": "Rottweilas Latam", "event_id": "156778", "event_start_utc": "2026-10-13T21:00:00Z", "features": {"away_elo": 1589.161828, "away_history_count": 14, "home_elo": 1583.277818, "home_history_count": 40}, "historical_source_observation_times_verified": false, "home_team": "Amaru Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:22157": 40, "bo3:4:22288": 14}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:22157": "2026-08-08T18:00:00Z", "bo3:4:22288": "2026-10-10T21:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0660951180882821, "platt_slope": 0.8503469876096356, "ratings": {"bo3:4:22157": 1583.277818, "bo3:4:22288": 1589.161828}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T16:58:36.903465+00:00", "team_ids": ["bo3:4:22157", "bo3:4:22288"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T16:58:36.903465+00:00", "probabilities": {"away": 0.522778, "home": 0.477222}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1a7c59420f60a97593d4329efa8097f5c696c3d97857d7a28977af1a5fb919e0", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="24" t="inlineStr">
+        <is>
+          <t>613423ba47604143</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:33:54.449023Z</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D137" s="24" t="inlineStr">
+        <is>
+          <t>158262</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>Cloud Dawning</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>Imperial Power</t>
+        </is>
+      </c>
+      <c r="H137" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I137" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J137" s="25" t="n"/>
+      <c r="K137" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N137" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O137" s="28" t="n">
+        <v>0.574536</v>
+      </c>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="28" t="n">
+        <v>0.183911</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S137" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W137" s="26" t="n"/>
+      <c r="X137" s="26" t="n"/>
+      <c r="Y137" s="25" t="n"/>
+      <c r="Z137" s="26" t="n"/>
+      <c r="AA137" s="28" t="n"/>
+      <c r="AB137" s="28" t="n"/>
+      <c r="AC137" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:33:24.028204Z</t>
+        </is>
+      </c>
+      <c r="AE137" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-ip-cd-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF137" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG137" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH137" s="24" t="n"/>
+      <c r="AI137" s="31" t="n"/>
+      <c r="AJ137" s="31" t="n"/>
+      <c r="AK137" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL137" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN137" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP137" s="24" t="inlineStr">
+        <is>
+          <t>Cloud Dawning</t>
+        </is>
+      </c>
+      <c r="AQ137" s="24" t="inlineStr">
+        <is>
+          <t>Cloud Dawning</t>
+        </is>
+      </c>
+      <c r="AR137" s="24" t="inlineStr">
+        <is>
+          <t>Cloud Dawning</t>
+        </is>
+      </c>
+      <c r="AS137" s="24" t="inlineStr">
+        <is>
+          <t>Imperial Power</t>
+        </is>
+      </c>
+      <c r="AT137" s="24" t="inlineStr">
+        <is>
+          <t>Imperial Power</t>
+        </is>
+      </c>
+      <c r="AU137" s="24" t="inlineStr">
+        <is>
+          <t>Imperial Power</t>
+        </is>
+      </c>
+      <c r="AV137" s="24" t="n"/>
+      <c r="AW137" s="24" t="n"/>
+      <c r="AX137" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY137" s="24" t="n"/>
+      <c r="AZ137" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA137" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BB137" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD137" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BE137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG137" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:29:18.434519Z</t>
+        </is>
+      </c>
+      <c r="BI137" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ137" s="25" t="n"/>
+      <c r="BK137" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL137" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM137" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN137" s="28" t="n"/>
+      <c r="BO137" s="28" t="n"/>
+      <c r="BP137" s="25" t="n"/>
+      <c r="BQ137" s="27" t="n"/>
+      <c r="BR137" s="28" t="n"/>
+      <c r="BS137" s="28" t="n"/>
+      <c r="BT137" s="28" t="n"/>
+      <c r="BU137" s="25" t="n"/>
+      <c r="BV137" s="29" t="n"/>
+      <c r="BW137" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
+      <c r="BX137" s="30" t="n"/>
+      <c r="BY137" s="27" t="n"/>
+      <c r="BZ137" s="24" t="n"/>
+      <c r="CA137" s="31" t="n"/>
+      <c r="CB137" s="24" t="n"/>
+      <c r="CC137" s="24" t="n"/>
+      <c r="CD137" s="24" t="n"/>
+      <c r="CE137" s="24" t="n"/>
+      <c r="CF137" s="24" t="n"/>
+      <c r="CG137" s="24" t="n"/>
+      <c r="CH137" s="24" t="n"/>
+      <c r="CI137" s="24" t="n"/>
+      <c r="CJ137" s="24" t="n"/>
+      <c r="CK137" s="24" t="n"/>
+      <c r="CL137" s="24" t="n"/>
+      <c r="CM137" s="24" t="n"/>
+      <c r="CN137" s="24" t="n"/>
+      <c r="CO137" s="24" t="n"/>
+      <c r="CP137" s="24" t="n"/>
+      <c r="CQ137" s="24" t="n"/>
+      <c r="CR137" s="24" t="n"/>
+      <c r="CS137" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT137" s="24" t="n"/>
+      <c r="CU137" s="24" t="n"/>
+      <c r="CV137" s="24" t="n"/>
+      <c r="CW137" s="24" t="n"/>
+      <c r="CX137" s="24" t="n"/>
+      <c r="CY137" s="24" t="n"/>
+      <c r="CZ137" s="24" t="n"/>
+      <c r="DA137" s="24" t="n"/>
+      <c r="DB137" s="24" t="n"/>
+      <c r="DC137" s="24" t="n"/>
+      <c r="DD137" s="24" t="n"/>
+      <c r="DE137" s="24" t="n"/>
+      <c r="DF137" s="24" t="n"/>
+      <c r="DG137" s="24" t="n"/>
+      <c r="DH137" s="24" t="n"/>
+      <c r="DI137" s="24" t="n"/>
+      <c r="DJ137" s="24" t="n"/>
+      <c r="DK137" s="24" t="n"/>
+      <c r="DL137" s="24" t="n"/>
+      <c r="DM137" s="24" t="n"/>
+      <c r="DN137" s="24" t="n"/>
+      <c r="DO137" s="24" t="n"/>
+      <c r="DP137" s="24" t="n"/>
+      <c r="DQ137" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "Cloud Dawning", "event_id": "158262", "event_start_utc": "2026-10-14T04:00:00Z", "features": {"away_elo": 1365.355637, "away_history_count": 37, "home_elo": 1485.9812, "home_history_count": 1}, "historical_source_observation_times_verified": false, "home_team": "Imperial Power", "inference_inputs": {"book_state": {"games_played": {"bo3:4:21875": 37, "bo3:4:25484": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:21875": "2026-10-13T08:10:00Z", "bo3:4:25484": "2026-10-13T04:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:21875": 1365.355637, "bo3:4:25484": 1485.9812}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:25484", "bo3:4:21875"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.425464, "home": 0.574536}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4ef0cf261aa1b84820c96fdd8c3f5ce33af807e3f098383a4fd68626aa144876", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="24" t="inlineStr">
+        <is>
+          <t>b263e4239cba4257</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:33:54.449023Z</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D138" s="24" t="inlineStr">
+        <is>
+          <t>158214</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>Kalmychata</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="H138" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I138" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J138" s="25" t="n"/>
+      <c r="K138" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M138" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N138" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O138" s="28" t="n">
+        <v>0.591647</v>
+      </c>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="28" t="n">
+        <v>-0.037983</v>
+      </c>
+      <c r="R138" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U138" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="n"/>
+      <c r="W138" s="26" t="n"/>
+      <c r="X138" s="26" t="n"/>
+      <c r="Y138" s="25" t="n"/>
+      <c r="Z138" s="26" t="n"/>
+      <c r="AA138" s="28" t="n"/>
+      <c r="AB138" s="28" t="n"/>
+      <c r="AC138" s="30" t="n"/>
+      <c r="AD138" s="24" t="n"/>
+      <c r="AE138" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF138" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG138" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH138" s="24" t="n"/>
+      <c r="AI138" s="31" t="n"/>
+      <c r="AJ138" s="31" t="n"/>
+      <c r="AK138" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL138" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM138" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN138" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO138" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP138" s="24" t="inlineStr">
+        <is>
+          <t>Kalmychata</t>
+        </is>
+      </c>
+      <c r="AQ138" s="24" t="inlineStr">
+        <is>
+          <t>Kalmychata</t>
+        </is>
+      </c>
+      <c r="AR138" s="24" t="inlineStr">
+        <is>
+          <t>Kalmychata</t>
+        </is>
+      </c>
+      <c r="AS138" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AT138" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AU138" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AV138" s="24" t="n"/>
+      <c r="AW138" s="24" t="n"/>
+      <c r="AX138" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY138" s="24" t="n"/>
+      <c r="AZ138" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA138" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BB138" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD138" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BE138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG138" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:29:58.800963Z</t>
+        </is>
+      </c>
+      <c r="BI138" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ138" s="25" t="n"/>
+      <c r="BK138" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL138" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM138" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN138" s="28" t="n"/>
+      <c r="BO138" s="28" t="n"/>
+      <c r="BP138" s="25" t="n"/>
+      <c r="BQ138" s="27" t="n"/>
+      <c r="BR138" s="28" t="n"/>
+      <c r="BS138" s="28" t="n"/>
+      <c r="BT138" s="28" t="n"/>
+      <c r="BU138" s="25" t="n"/>
+      <c r="BV138" s="29" t="n"/>
+      <c r="BW138" s="24" t="n"/>
+      <c r="BX138" s="30" t="n"/>
+      <c r="BY138" s="27" t="n"/>
+      <c r="BZ138" s="24" t="n"/>
+      <c r="CA138" s="31" t="n"/>
+      <c r="CB138" s="24" t="n"/>
+      <c r="CC138" s="24" t="n"/>
+      <c r="CD138" s="24" t="n"/>
+      <c r="CE138" s="24" t="n"/>
+      <c r="CF138" s="24" t="n"/>
+      <c r="CG138" s="24" t="n"/>
+      <c r="CH138" s="24" t="n"/>
+      <c r="CI138" s="24" t="n"/>
+      <c r="CJ138" s="24" t="n"/>
+      <c r="CK138" s="24" t="n"/>
+      <c r="CL138" s="24" t="n"/>
+      <c r="CM138" s="24" t="n"/>
+      <c r="CN138" s="24" t="n"/>
+      <c r="CO138" s="24" t="n"/>
+      <c r="CP138" s="24" t="n"/>
+      <c r="CQ138" s="24" t="n"/>
+      <c r="CR138" s="24" t="n"/>
+      <c r="CS138" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT138" s="24" t="n"/>
+      <c r="CU138" s="24" t="n"/>
+      <c r="CV138" s="24" t="n"/>
+      <c r="CW138" s="24" t="n"/>
+      <c r="CX138" s="24" t="n"/>
+      <c r="CY138" s="24" t="n"/>
+      <c r="CZ138" s="24" t="n"/>
+      <c r="DA138" s="24" t="n"/>
+      <c r="DB138" s="24" t="n"/>
+      <c r="DC138" s="24" t="n"/>
+      <c r="DD138" s="24" t="n"/>
+      <c r="DE138" s="24" t="n"/>
+      <c r="DF138" s="24" t="n"/>
+      <c r="DG138" s="24" t="n"/>
+      <c r="DH138" s="24" t="n"/>
+      <c r="DI138" s="24" t="n"/>
+      <c r="DJ138" s="24" t="n"/>
+      <c r="DK138" s="24" t="n"/>
+      <c r="DL138" s="24" t="n"/>
+      <c r="DM138" s="24" t="n"/>
+      <c r="DN138" s="24" t="n"/>
+      <c r="DO138" s="24" t="n"/>
+      <c r="DP138" s="24" t="n"/>
+      <c r="DQ138" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "Kalmychata", "event_id": "158214", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1592.500579, "away_history_count": 168, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15089": 168, "bo3:4:16398": 297}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15089": "2026-10-13T09:00:00Z", "bo3:4:16398": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:15089": 1592.500579, "bo3:4:16398": 1488.072875}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:15089"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.591647, "home": 0.408353}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2685a146ca3f8bb6364c69a072fbde4add522d53bd902c0ee0b3c9209ae30f73", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
+        <is>
+          <t>16c63b253b964377</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:33:54.449023Z</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D139" s="24" t="inlineStr">
+        <is>
+          <t>156718</t>
+        </is>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="H139" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I139" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J139" s="25" t="n"/>
+      <c r="K139" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L139" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M139" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N139" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O139" s="28" t="n">
+        <v>0.523645</v>
+      </c>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="28" t="n">
+        <v>0.13302</v>
+      </c>
+      <c r="R139" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S139" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T139" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U139" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="n"/>
+      <c r="W139" s="26" t="n"/>
+      <c r="X139" s="26" t="n"/>
+      <c r="Y139" s="25" t="n"/>
+      <c r="Z139" s="26" t="n"/>
+      <c r="AA139" s="28" t="n"/>
+      <c r="AB139" s="28" t="n"/>
+      <c r="AC139" s="30" t="n"/>
+      <c r="AD139" s="24" t="n"/>
+      <c r="AE139" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF139" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG139" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH139" s="24" t="n"/>
+      <c r="AI139" s="31" t="n"/>
+      <c r="AJ139" s="31" t="n"/>
+      <c r="AK139" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL139" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM139" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN139" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO139" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP139" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ139" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR139" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS139" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AT139" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AU139" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AV139" s="24" t="n"/>
+      <c r="AW139" s="24" t="n"/>
+      <c r="AX139" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY139" s="24" t="n"/>
+      <c r="AZ139" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA139" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BB139" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC139" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD139" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BE139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG139" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:32:02.017912Z</t>
+        </is>
+      </c>
+      <c r="BI139" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ139" s="25" t="n"/>
+      <c r="BK139" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL139" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM139" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN139" s="28" t="n"/>
+      <c r="BO139" s="28" t="n"/>
+      <c r="BP139" s="25" t="n"/>
+      <c r="BQ139" s="27" t="n"/>
+      <c r="BR139" s="28" t="n"/>
+      <c r="BS139" s="28" t="n"/>
+      <c r="BT139" s="28" t="n"/>
+      <c r="BU139" s="25" t="n"/>
+      <c r="BV139" s="29" t="n"/>
+      <c r="BW139" s="24" t="n"/>
+      <c r="BX139" s="30" t="n"/>
+      <c r="BY139" s="27" t="n"/>
+      <c r="BZ139" s="24" t="n"/>
+      <c r="CA139" s="31" t="n"/>
+      <c r="CB139" s="24" t="n"/>
+      <c r="CC139" s="24" t="n"/>
+      <c r="CD139" s="24" t="n"/>
+      <c r="CE139" s="24" t="n"/>
+      <c r="CF139" s="24" t="n"/>
+      <c r="CG139" s="24" t="n"/>
+      <c r="CH139" s="24" t="n"/>
+      <c r="CI139" s="24" t="n"/>
+      <c r="CJ139" s="24" t="n"/>
+      <c r="CK139" s="24" t="n"/>
+      <c r="CL139" s="24" t="n"/>
+      <c r="CM139" s="24" t="n"/>
+      <c r="CN139" s="24" t="n"/>
+      <c r="CO139" s="24" t="n"/>
+      <c r="CP139" s="24" t="n"/>
+      <c r="CQ139" s="24" t="n"/>
+      <c r="CR139" s="24" t="n"/>
+      <c r="CS139" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT139" s="24" t="n"/>
+      <c r="CU139" s="24" t="n"/>
+      <c r="CV139" s="24" t="n"/>
+      <c r="CW139" s="24" t="n"/>
+      <c r="CX139" s="24" t="n"/>
+      <c r="CY139" s="24" t="n"/>
+      <c r="CZ139" s="24" t="n"/>
+      <c r="DA139" s="24" t="n"/>
+      <c r="DB139" s="24" t="n"/>
+      <c r="DC139" s="24" t="n"/>
+      <c r="DD139" s="24" t="n"/>
+      <c r="DE139" s="24" t="n"/>
+      <c r="DF139" s="24" t="n"/>
+      <c r="DG139" s="24" t="n"/>
+      <c r="DH139" s="24" t="n"/>
+      <c r="DI139" s="24" t="n"/>
+      <c r="DJ139" s="24" t="n"/>
+      <c r="DK139" s="24" t="n"/>
+      <c r="DL139" s="24" t="n"/>
+      <c r="DM139" s="24" t="n"/>
+      <c r="DN139" s="24" t="n"/>
+      <c r="DO139" s="24" t="n"/>
+      <c r="DP139" s="24" t="n"/>
+      <c r="DQ139" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156718", "event_start_utc": "2026-10-14T16:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16398": 297, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16398": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:16398": 1488.072875, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.476355, "home": 0.523645}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fcd9e7bfaf0a7aef8cfe55b5174f307553eff49f6da840b15ce6cac7e8797e4a", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="24" t="inlineStr">
+        <is>
+          <t>af3588d76fc24e2d</t>
+        </is>
+      </c>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:33:54.449023Z</t>
+        </is>
+      </c>
+      <c r="C140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D140" s="24" t="inlineStr">
+        <is>
+          <t>156716</t>
+        </is>
+      </c>
+      <c r="E140" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F140" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G140" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="H140" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I140" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J140" s="25" t="n"/>
+      <c r="K140" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L140" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M140" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N140" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O140" s="28" t="n">
+        <v>0.5946399999999999</v>
+      </c>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="28" t="n">
+        <v>-0.095762</v>
+      </c>
+      <c r="R140" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U140" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V140" s="24" t="n"/>
+      <c r="W140" s="26" t="n"/>
+      <c r="X140" s="26" t="n"/>
+      <c r="Y140" s="25" t="n"/>
+      <c r="Z140" s="26" t="n"/>
+      <c r="AA140" s="28" t="n"/>
+      <c r="AB140" s="28" t="n"/>
+      <c r="AC140" s="30" t="n"/>
+      <c r="AD140" s="24" t="n"/>
+      <c r="AE140" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF140" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG140" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH140" s="24" t="n"/>
+      <c r="AI140" s="31" t="n"/>
+      <c r="AJ140" s="31" t="n"/>
+      <c r="AK140" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL140" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM140" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN140" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO140" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP140" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ140" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR140" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS140" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AT140" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AU140" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AV140" s="24" t="n"/>
+      <c r="AW140" s="24" t="n"/>
+      <c r="AX140" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY140" s="24" t="n"/>
+      <c r="AZ140" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA140" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BB140" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC140" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD140" s="24" t="inlineStr">
+        <is>
+          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+        </is>
+      </c>
+      <c r="BE140" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF140" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG140" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:33:23.747123Z</t>
+        </is>
+      </c>
+      <c r="BI140" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ140" s="25" t="n"/>
+      <c r="BK140" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL140" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM140" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN140" s="28" t="n"/>
+      <c r="BO140" s="28" t="n"/>
+      <c r="BP140" s="25" t="n"/>
+      <c r="BQ140" s="27" t="n"/>
+      <c r="BR140" s="28" t="n"/>
+      <c r="BS140" s="28" t="n"/>
+      <c r="BT140" s="28" t="n"/>
+      <c r="BU140" s="25" t="n"/>
+      <c r="BV140" s="29" t="n"/>
+      <c r="BW140" s="24" t="n"/>
+      <c r="BX140" s="30" t="n"/>
+      <c r="BY140" s="27" t="n"/>
+      <c r="BZ140" s="24" t="n"/>
+      <c r="CA140" s="31" t="n"/>
+      <c r="CB140" s="24" t="n"/>
+      <c r="CC140" s="24" t="n"/>
+      <c r="CD140" s="24" t="n"/>
+      <c r="CE140" s="24" t="n"/>
+      <c r="CF140" s="24" t="n"/>
+      <c r="CG140" s="24" t="n"/>
+      <c r="CH140" s="24" t="n"/>
+      <c r="CI140" s="24" t="n"/>
+      <c r="CJ140" s="24" t="n"/>
+      <c r="CK140" s="24" t="n"/>
+      <c r="CL140" s="24" t="n"/>
+      <c r="CM140" s="24" t="n"/>
+      <c r="CN140" s="24" t="n"/>
+      <c r="CO140" s="24" t="n"/>
+      <c r="CP140" s="24" t="n"/>
+      <c r="CQ140" s="24" t="n"/>
+      <c r="CR140" s="24" t="n"/>
+      <c r="CS140" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT140" s="24" t="n"/>
+      <c r="CU140" s="24" t="n"/>
+      <c r="CV140" s="24" t="n"/>
+      <c r="CW140" s="24" t="n"/>
+      <c r="CX140" s="24" t="n"/>
+      <c r="CY140" s="24" t="n"/>
+      <c r="CZ140" s="24" t="n"/>
+      <c r="DA140" s="24" t="n"/>
+      <c r="DB140" s="24" t="n"/>
+      <c r="DC140" s="24" t="n"/>
+      <c r="DD140" s="24" t="n"/>
+      <c r="DE140" s="24" t="n"/>
+      <c r="DF140" s="24" t="n"/>
+      <c r="DG140" s="24" t="n"/>
+      <c r="DH140" s="24" t="n"/>
+      <c r="DI140" s="24" t="n"/>
+      <c r="DJ140" s="24" t="n"/>
+      <c r="DK140" s="24" t="n"/>
+      <c r="DL140" s="24" t="n"/>
+      <c r="DM140" s="24" t="n"/>
+      <c r="DN140" s="24" t="n"/>
+      <c r="DO140" s="24" t="n"/>
+      <c r="DP140" s="24" t="n"/>
+      <c r="DQ140" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1620.120862, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:25301": 1620.120862, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.40536, "home": 0.59464}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2c88dd441710ecb8ad52dbe18df7d7bb9fa56f7788499bd04a0de2c69936ee26", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/dota2/gated.xlsx
+++ b/data/sports/dota2/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ140" headerRowCount="1">
-  <autoFilter ref="A1:DQ140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ143" headerRowCount="1">
+  <autoFilter ref="A1:DQ143"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$140)</f>
+        <f>COUNTA('Picks'!$A$2:$A$143)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$140,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$143,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$140,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")+COUNTIFS('Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$140,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$143,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")/(COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"win")+COUNTIFS('Picks'!$BX$2:$BX$140,"&gt;0",'Picks'!$V$2:$V$140,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")/(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$140)/SUM('Picks'!$BX$2:$BX$140),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$143)/SUM('Picks'!$BX$2:$BX$143),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$140)</f>
+        <f>SUM('Picks'!$BY$2:$BY$143)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$140,"&lt;&gt;",'Picks'!$AB$2:$AB$140),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$143,"&lt;&gt;",'Picks'!$AB$2:$AB$143),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$140,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$140,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$140,'Picks'!$AM$2:$AM$140,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$143,'Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A14,'Picks'!$U$2:$U$140,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A15,'Picks'!$U$2:$U$140,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled",'Picks'!$V$2:$V$140,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$140,'Picks'!$H$2:$H$140,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$140,'Picks'!$H$2:$H$140,$A16,'Picks'!$U$2:$U$140,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ140"/>
+  <dimension ref="A1:DQ143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45144,12 +45144,12 @@
     <row r="138" ht="36" customHeight="1">
       <c r="A138" s="24" t="inlineStr">
         <is>
-          <t>b263e4239cba4257</t>
+          <t>e5bb920605534850</t>
         </is>
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C138" s="24" t="inlineStr">
@@ -45179,45 +45179,47 @@
       </c>
       <c r="H138" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I138" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J138" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J138" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K138" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L138" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="M138" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="N138" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="O138" s="28" t="n">
-        <v>0.591647</v>
+        <v>0.507493</v>
       </c>
       <c r="P138" s="28" t="n"/>
       <c r="Q138" s="28" t="n">
-        <v>-0.037983</v>
+        <v>-0.063322</v>
       </c>
       <c r="R138" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S138" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T138" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U138" s="24" t="inlineStr">
@@ -45236,7 +45238,7 @@
       <c r="AD138" s="24" t="n"/>
       <c r="AE138" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-dota2-nemiga-kalmy-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF138" s="31" t="inlineStr">
@@ -45320,7 +45322,7 @@
       </c>
       <c r="BA138" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB138" s="24" t="inlineStr">
@@ -45330,12 +45332,12 @@
       </c>
       <c r="BC138" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD138" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE138" s="24" t="inlineStr">
@@ -45350,12 +45352,12 @@
       </c>
       <c r="BG138" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH138" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:29:58.800963Z</t>
+          <t>2026-10-14T05:52:44.375366Z</t>
         </is>
       </c>
       <c r="BI138" s="24" t="inlineStr">
@@ -45363,15 +45365,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ138" s="25" t="n"/>
+      <c r="BJ138" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK138" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="BL138" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="BM138" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="BN138" s="28" t="n"/>
       <c r="BO138" s="28" t="n"/>
@@ -45432,31 +45436,27 @@
       <c r="DN138" s="24" t="n"/>
       <c r="DO138" s="24" t="n"/>
       <c r="DP138" s="24" t="n"/>
-      <c r="DQ138" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "Kalmychata", "event_id": "158214", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1592.500579, "away_history_count": 168, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15089": 168, "bo3:4:16398": 297}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15089": "2026-10-13T09:00:00Z", "bo3:4:16398": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:15089": 1592.500579, "bo3:4:16398": 1488.072875}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:15089"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.591647, "home": 0.408353}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2685a146ca3f8bb6364c69a072fbde4add522d53bd902c0ee0b3c9209ae30f73", "sport": "DOTA2"}</t>
-        </is>
-      </c>
+      <c r="DQ138" s="24" t="n"/>
     </row>
     <row r="139" ht="36" customHeight="1">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>16c63b253b964377</t>
+          <t>bc081167fd014f36</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T16:00:00Z</t>
+          <t>2026-10-14T09:00:00Z</t>
         </is>
       </c>
       <c r="D139" s="24" t="inlineStr">
         <is>
-          <t>156718</t>
+          <t>158214</t>
         </is>
       </c>
       <c r="E139" s="24" t="inlineStr">
@@ -45466,7 +45466,7 @@
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="G139" s="24" t="inlineStr">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="I139" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J139" s="25" t="n"/>
@@ -45491,26 +45491,26 @@
         </is>
       </c>
       <c r="L139" s="26" t="n">
-        <v>156</v>
+        <v>-170</v>
       </c>
       <c r="M139" s="27" t="n">
-        <v>2.56</v>
+        <v>1.588235</v>
       </c>
       <c r="N139" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.62963</v>
       </c>
       <c r="O139" s="28" t="n">
-        <v>0.523645</v>
+        <v>0.591355</v>
       </c>
       <c r="P139" s="28" t="n"/>
       <c r="Q139" s="28" t="n">
-        <v>0.13302</v>
+        <v>-0.038275</v>
       </c>
       <c r="R139" s="26" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="S139" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T139" s="24" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
       <c r="AD139" s="24" t="n"/>
       <c r="AE139" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
         </is>
       </c>
       <c r="AF139" s="31" t="inlineStr">
@@ -45551,7 +45551,7 @@
       <c r="AJ139" s="31" t="n"/>
       <c r="AK139" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL139" s="26" t="n">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AM139" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN139" s="24" t="inlineStr">
@@ -45569,22 +45569,22 @@
       </c>
       <c r="AO139" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP139" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AQ139" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AR139" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AS139" s="24" t="inlineStr">
@@ -45617,7 +45617,7 @@
       </c>
       <c r="BA139" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB139" s="24" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="BD139" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE139" s="24" t="inlineStr">
@@ -45652,7 +45652,7 @@
       </c>
       <c r="BH139" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:32:02.017912Z</t>
+          <t>2026-10-14T05:53:14.998361Z</t>
         </is>
       </c>
       <c r="BI139" s="24" t="inlineStr">
@@ -45662,13 +45662,13 @@
       </c>
       <c r="BJ139" s="25" t="n"/>
       <c r="BK139" s="26" t="n">
-        <v>156</v>
+        <v>-170</v>
       </c>
       <c r="BL139" s="27" t="n">
-        <v>2.56</v>
+        <v>1.588235</v>
       </c>
       <c r="BM139" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.62963</v>
       </c>
       <c r="BN139" s="28" t="n"/>
       <c r="BO139" s="28" t="n"/>
@@ -45703,7 +45703,7 @@
       <c r="CR139" s="24" t="n"/>
       <c r="CS139" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT139" s="24" t="n"/>
@@ -45731,29 +45731,29 @@
       <c r="DP139" s="24" t="n"/>
       <c r="DQ139" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156718", "event_start_utc": "2026-10-14T16:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16398": 297, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16398": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:16398": 1488.072875, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.476355, "home": 0.523645}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fcd9e7bfaf0a7aef8cfe55b5174f307553eff49f6da840b15ce6cac7e8797e4a", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Kalmychata", "event_id": "158214", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1592.507792, "away_history_count": 168, "home_elo": 1488.080158, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15089": 168, "bo3:4:16398": 297}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15089": "2026-10-13T09:00:00Z", "bo3:4:16398": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:15089": 1592.507792, "bo3:4:16398": 1488.080158}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:16398", "bo3:4:15089"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.591355, "home": 0.408645}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "792be9ee076e5b22288cb5df758d4692b44c36a8a412c06212346b571186bdfc", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
     <row r="140" ht="36" customHeight="1">
       <c r="A140" s="24" t="inlineStr">
         <is>
-          <t>af3588d76fc24e2d</t>
+          <t>ad9e3a415f534f51</t>
         </is>
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T12:00:00Z</t>
         </is>
       </c>
       <c r="D140" s="24" t="inlineStr">
         <is>
-          <t>156716</t>
+          <t>158541</t>
         </is>
       </c>
       <c r="E140" s="24" t="inlineStr">
@@ -45763,12 +45763,12 @@
       </c>
       <c r="F140" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G140" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H140" s="24" t="inlineStr">
@@ -45778,7 +45778,7 @@
       </c>
       <c r="I140" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J140" s="25" t="n"/>
@@ -45788,20 +45788,20 @@
         </is>
       </c>
       <c r="L140" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="M140" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="N140" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="O140" s="28" t="n">
-        <v>0.5946399999999999</v>
+        <v>0.549683</v>
       </c>
       <c r="P140" s="28" t="n"/>
       <c r="Q140" s="28" t="n">
-        <v>-0.095762</v>
+        <v>-0.059692</v>
       </c>
       <c r="R140" s="26" t="n">
         <v>0</v>
@@ -45830,7 +45830,7 @@
       <c r="AD140" s="24" t="n"/>
       <c r="AE140" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-yb-tr-2026-10-14).</t>
         </is>
       </c>
       <c r="AF140" s="31" t="inlineStr">
@@ -45871,32 +45871,32 @@
       </c>
       <c r="AP140" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ140" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR140" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS140" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT140" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU140" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV140" s="24" t="n"/>
@@ -45914,7 +45914,7 @@
       </c>
       <c r="BA140" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB140" s="24" t="inlineStr">
@@ -45929,7 +45929,7 @@
       </c>
       <c r="BD140" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE140" s="24" t="inlineStr">
@@ -45949,7 +45949,7 @@
       </c>
       <c r="BH140" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:23.747123Z</t>
+          <t>2026-10-14T05:55:09.636207Z</t>
         </is>
       </c>
       <c r="BI140" s="24" t="inlineStr">
@@ -45959,13 +45959,13 @@
       </c>
       <c r="BJ140" s="25" t="n"/>
       <c r="BK140" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="BL140" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="BM140" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="BN140" s="28" t="n"/>
       <c r="BO140" s="28" t="n"/>
@@ -46028,7 +46028,898 @@
       <c r="DP140" s="24" t="n"/>
       <c r="DQ140" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1620.120862, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:25301": 1620.120862, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.40536, "home": 0.59464}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2c88dd441710ecb8ad52dbe18df7d7bb9fa56f7788499bd04a0de2c69936ee26", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Team Resilience", "event_id": "158541", "event_start_utc": "2026-10-14T12:00:00Z", "features": {"away_elo": 1752.912205, "away_history_count": 23, "home_elo": 1689.95539, "home_history_count": 188}, "historical_source_observation_times_verified": false, "home_team": "Yakult Brothers", "inference_inputs": {"book_state": {"games_played": {"bo3:4:18586": 188, "bo3:4:23196": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:18586": "2026-10-13T12:30:00Z", "bo3:4:23196": "2026-10-13T12:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:18586": 1689.95539, "bo3:4:23196": 1752.912205}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:18586", "bo3:4:23196"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.549683, "home": 0.450317}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b0e53c870d4a1380eb6f96e8b29b1badd097645f699610f6eb160a9e1dda942b", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="36" customHeight="1">
+      <c r="A141" s="24" t="inlineStr">
+        <is>
+          <t>b5c129fe23ee4513</t>
+        </is>
+      </c>
+      <c r="B141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D141" s="24" t="inlineStr">
+        <is>
+          <t>156718</t>
+        </is>
+      </c>
+      <c r="E141" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F141" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="H141" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I141" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J141" s="25" t="n"/>
+      <c r="K141" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M141" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N141" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O141" s="28" t="n">
+        <v>0.523655</v>
+      </c>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="28" t="n">
+        <v>0.123655</v>
+      </c>
+      <c r="R141" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S141" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T141" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U141" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="n"/>
+      <c r="W141" s="26" t="n"/>
+      <c r="X141" s="26" t="n"/>
+      <c r="Y141" s="25" t="n"/>
+      <c r="Z141" s="26" t="n"/>
+      <c r="AA141" s="28" t="n"/>
+      <c r="AB141" s="28" t="n"/>
+      <c r="AC141" s="30" t="n"/>
+      <c r="AD141" s="24" t="n"/>
+      <c r="AE141" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF141" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG141" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH141" s="24" t="n"/>
+      <c r="AI141" s="31" t="n"/>
+      <c r="AJ141" s="31" t="n"/>
+      <c r="AK141" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL141" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM141" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN141" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO141" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP141" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ141" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR141" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS141" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AT141" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AU141" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AV141" s="24" t="n"/>
+      <c r="AW141" s="24" t="n"/>
+      <c r="AX141" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY141" s="24" t="n"/>
+      <c r="AZ141" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA141" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB141" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC141" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD141" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE141" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF141" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG141" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:56:02.908549Z</t>
+        </is>
+      </c>
+      <c r="BI141" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ141" s="25" t="n"/>
+      <c r="BK141" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL141" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM141" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN141" s="28" t="n"/>
+      <c r="BO141" s="28" t="n"/>
+      <c r="BP141" s="25" t="n"/>
+      <c r="BQ141" s="27" t="n"/>
+      <c r="BR141" s="28" t="n"/>
+      <c r="BS141" s="28" t="n"/>
+      <c r="BT141" s="28" t="n"/>
+      <c r="BU141" s="25" t="n"/>
+      <c r="BV141" s="29" t="n"/>
+      <c r="BW141" s="24" t="n"/>
+      <c r="BX141" s="30" t="n"/>
+      <c r="BY141" s="27" t="n"/>
+      <c r="BZ141" s="24" t="n"/>
+      <c r="CA141" s="31" t="n"/>
+      <c r="CB141" s="24" t="n"/>
+      <c r="CC141" s="24" t="n"/>
+      <c r="CD141" s="24" t="n"/>
+      <c r="CE141" s="24" t="n"/>
+      <c r="CF141" s="24" t="n"/>
+      <c r="CG141" s="24" t="n"/>
+      <c r="CH141" s="24" t="n"/>
+      <c r="CI141" s="24" t="n"/>
+      <c r="CJ141" s="24" t="n"/>
+      <c r="CK141" s="24" t="n"/>
+      <c r="CL141" s="24" t="n"/>
+      <c r="CM141" s="24" t="n"/>
+      <c r="CN141" s="24" t="n"/>
+      <c r="CO141" s="24" t="n"/>
+      <c r="CP141" s="24" t="n"/>
+      <c r="CQ141" s="24" t="n"/>
+      <c r="CR141" s="24" t="n"/>
+      <c r="CS141" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT141" s="24" t="n"/>
+      <c r="CU141" s="24" t="n"/>
+      <c r="CV141" s="24" t="n"/>
+      <c r="CW141" s="24" t="n"/>
+      <c r="CX141" s="24" t="n"/>
+      <c r="CY141" s="24" t="n"/>
+      <c r="CZ141" s="24" t="n"/>
+      <c r="DA141" s="24" t="n"/>
+      <c r="DB141" s="24" t="n"/>
+      <c r="DC141" s="24" t="n"/>
+      <c r="DD141" s="24" t="n"/>
+      <c r="DE141" s="24" t="n"/>
+      <c r="DF141" s="24" t="n"/>
+      <c r="DG141" s="24" t="n"/>
+      <c r="DH141" s="24" t="n"/>
+      <c r="DI141" s="24" t="n"/>
+      <c r="DJ141" s="24" t="n"/>
+      <c r="DK141" s="24" t="n"/>
+      <c r="DL141" s="24" t="n"/>
+      <c r="DM141" s="24" t="n"/>
+      <c r="DN141" s="24" t="n"/>
+      <c r="DO141" s="24" t="n"/>
+      <c r="DP141" s="24" t="n"/>
+      <c r="DQ141" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156718", "event_start_utc": "2026-10-14T16:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1488.080158, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16398": 297, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16398": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:16398": 1488.080158, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:16398", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.476345, "home": 0.523655}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "24a5e4b74578f47f77b530c4eb469cecd5efa6c30b455019c70d475f291f4144", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="24" t="inlineStr">
+        <is>
+          <t>0202c808fd744b53</t>
+        </is>
+      </c>
+      <c r="B142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D142" s="24" t="inlineStr">
+        <is>
+          <t>156716</t>
+        </is>
+      </c>
+      <c r="E142" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F142" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G142" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="H142" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I142" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J142" s="25" t="n"/>
+      <c r="K142" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L142" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M142" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N142" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O142" s="28" t="n">
+        <v>0.59448</v>
+      </c>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="28" t="n">
+        <v>-0.09592199999999999</v>
+      </c>
+      <c r="R142" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U142" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="n"/>
+      <c r="W142" s="26" t="n"/>
+      <c r="X142" s="26" t="n"/>
+      <c r="Y142" s="25" t="n"/>
+      <c r="Z142" s="26" t="n"/>
+      <c r="AA142" s="28" t="n"/>
+      <c r="AB142" s="28" t="n"/>
+      <c r="AC142" s="30" t="n"/>
+      <c r="AD142" s="24" t="n"/>
+      <c r="AE142" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF142" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG142" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH142" s="24" t="n"/>
+      <c r="AI142" s="31" t="n"/>
+      <c r="AJ142" s="31" t="n"/>
+      <c r="AK142" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL142" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM142" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN142" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO142" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP142" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ142" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR142" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS142" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AT142" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AU142" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AV142" s="24" t="n"/>
+      <c r="AW142" s="24" t="n"/>
+      <c r="AX142" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY142" s="24" t="n"/>
+      <c r="AZ142" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA142" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB142" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC142" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD142" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE142" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF142" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG142" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:56:54.523031Z</t>
+        </is>
+      </c>
+      <c r="BI142" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ142" s="25" t="n"/>
+      <c r="BK142" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL142" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM142" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN142" s="28" t="n"/>
+      <c r="BO142" s="28" t="n"/>
+      <c r="BP142" s="25" t="n"/>
+      <c r="BQ142" s="27" t="n"/>
+      <c r="BR142" s="28" t="n"/>
+      <c r="BS142" s="28" t="n"/>
+      <c r="BT142" s="28" t="n"/>
+      <c r="BU142" s="25" t="n"/>
+      <c r="BV142" s="29" t="n"/>
+      <c r="BW142" s="24" t="n"/>
+      <c r="BX142" s="30" t="n"/>
+      <c r="BY142" s="27" t="n"/>
+      <c r="BZ142" s="24" t="n"/>
+      <c r="CA142" s="31" t="n"/>
+      <c r="CB142" s="24" t="n"/>
+      <c r="CC142" s="24" t="n"/>
+      <c r="CD142" s="24" t="n"/>
+      <c r="CE142" s="24" t="n"/>
+      <c r="CF142" s="24" t="n"/>
+      <c r="CG142" s="24" t="n"/>
+      <c r="CH142" s="24" t="n"/>
+      <c r="CI142" s="24" t="n"/>
+      <c r="CJ142" s="24" t="n"/>
+      <c r="CK142" s="24" t="n"/>
+      <c r="CL142" s="24" t="n"/>
+      <c r="CM142" s="24" t="n"/>
+      <c r="CN142" s="24" t="n"/>
+      <c r="CO142" s="24" t="n"/>
+      <c r="CP142" s="24" t="n"/>
+      <c r="CQ142" s="24" t="n"/>
+      <c r="CR142" s="24" t="n"/>
+      <c r="CS142" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT142" s="24" t="n"/>
+      <c r="CU142" s="24" t="n"/>
+      <c r="CV142" s="24" t="n"/>
+      <c r="CW142" s="24" t="n"/>
+      <c r="CX142" s="24" t="n"/>
+      <c r="CY142" s="24" t="n"/>
+      <c r="CZ142" s="24" t="n"/>
+      <c r="DA142" s="24" t="n"/>
+      <c r="DB142" s="24" t="n"/>
+      <c r="DC142" s="24" t="n"/>
+      <c r="DD142" s="24" t="n"/>
+      <c r="DE142" s="24" t="n"/>
+      <c r="DF142" s="24" t="n"/>
+      <c r="DG142" s="24" t="n"/>
+      <c r="DH142" s="24" t="n"/>
+      <c r="DI142" s="24" t="n"/>
+      <c r="DJ142" s="24" t="n"/>
+      <c r="DK142" s="24" t="n"/>
+      <c r="DL142" s="24" t="n"/>
+      <c r="DM142" s="24" t="n"/>
+      <c r="DN142" s="24" t="n"/>
+      <c r="DO142" s="24" t="n"/>
+      <c r="DP142" s="24" t="n"/>
+      <c r="DQ142" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1620.074907, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:25301": 1620.074907, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.40552, "home": 0.59448}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f63e7ddcb28fd5faf9bb7922cf0be61109ee48b76f676b6e8273dbe0a0179db", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="24" t="inlineStr">
+        <is>
+          <t>19baae4adbcc4759</t>
+        </is>
+      </c>
+      <c r="B143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D143" s="24" t="inlineStr">
+        <is>
+          <t>156803</t>
+        </is>
+      </c>
+      <c r="E143" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F143" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="G143" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H143" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I143" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J143" s="25" t="n"/>
+      <c r="K143" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M143" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N143" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O143" s="28" t="n">
+        <v>0.607537</v>
+      </c>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="28" t="n">
+        <v>0.157087</v>
+      </c>
+      <c r="R143" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S143" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T143" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U143" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="n"/>
+      <c r="W143" s="26" t="n"/>
+      <c r="X143" s="26" t="n"/>
+      <c r="Y143" s="25" t="n"/>
+      <c r="Z143" s="26" t="n"/>
+      <c r="AA143" s="28" t="n"/>
+      <c r="AB143" s="28" t="n"/>
+      <c r="AC143" s="30" t="n"/>
+      <c r="AD143" s="24" t="n"/>
+      <c r="AE143" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF143" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG143" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH143" s="24" t="n"/>
+      <c r="AI143" s="31" t="n"/>
+      <c r="AJ143" s="31" t="n"/>
+      <c r="AK143" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL143" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM143" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN143" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO143" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP143" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AQ143" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AR143" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AS143" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT143" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU143" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV143" s="24" t="n"/>
+      <c r="AW143" s="24" t="n"/>
+      <c r="AX143" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY143" s="24" t="n"/>
+      <c r="AZ143" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA143" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB143" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC143" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD143" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE143" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF143" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG143" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:16.995855Z</t>
+        </is>
+      </c>
+      <c r="BI143" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ143" s="25" t="n"/>
+      <c r="BK143" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL143" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM143" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN143" s="28" t="n"/>
+      <c r="BO143" s="28" t="n"/>
+      <c r="BP143" s="25" t="n"/>
+      <c r="BQ143" s="27" t="n"/>
+      <c r="BR143" s="28" t="n"/>
+      <c r="BS143" s="28" t="n"/>
+      <c r="BT143" s="28" t="n"/>
+      <c r="BU143" s="25" t="n"/>
+      <c r="BV143" s="29" t="n"/>
+      <c r="BW143" s="24" t="n"/>
+      <c r="BX143" s="30" t="n"/>
+      <c r="BY143" s="27" t="n"/>
+      <c r="BZ143" s="24" t="n"/>
+      <c r="CA143" s="31" t="n"/>
+      <c r="CB143" s="24" t="n"/>
+      <c r="CC143" s="24" t="n"/>
+      <c r="CD143" s="24" t="n"/>
+      <c r="CE143" s="24" t="n"/>
+      <c r="CF143" s="24" t="n"/>
+      <c r="CG143" s="24" t="n"/>
+      <c r="CH143" s="24" t="n"/>
+      <c r="CI143" s="24" t="n"/>
+      <c r="CJ143" s="24" t="n"/>
+      <c r="CK143" s="24" t="n"/>
+      <c r="CL143" s="24" t="n"/>
+      <c r="CM143" s="24" t="n"/>
+      <c r="CN143" s="24" t="n"/>
+      <c r="CO143" s="24" t="n"/>
+      <c r="CP143" s="24" t="n"/>
+      <c r="CQ143" s="24" t="n"/>
+      <c r="CR143" s="24" t="n"/>
+      <c r="CS143" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT143" s="24" t="n"/>
+      <c r="CU143" s="24" t="n"/>
+      <c r="CV143" s="24" t="n"/>
+      <c r="CW143" s="24" t="n"/>
+      <c r="CX143" s="24" t="n"/>
+      <c r="CY143" s="24" t="n"/>
+      <c r="CZ143" s="24" t="n"/>
+      <c r="DA143" s="24" t="n"/>
+      <c r="DB143" s="24" t="n"/>
+      <c r="DC143" s="24" t="n"/>
+      <c r="DD143" s="24" t="n"/>
+      <c r="DE143" s="24" t="n"/>
+      <c r="DF143" s="24" t="n"/>
+      <c r="DG143" s="24" t="n"/>
+      <c r="DH143" s="24" t="n"/>
+      <c r="DI143" s="24" t="n"/>
+      <c r="DJ143" s="24" t="n"/>
+      <c r="DK143" s="24" t="n"/>
+      <c r="DL143" s="24" t="n"/>
+      <c r="DM143" s="24" t="n"/>
+      <c r="DN143" s="24" t="n"/>
+      <c r="DO143" s="24" t="n"/>
+      <c r="DP143" s="24" t="n"/>
+      <c r="DQ143" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1620.074907, "away_history_count": 6, "home_elo": 1740.227749, "home_history_count": 186}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 186, "bo3:4:25301": 6}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-13T07:00:00Z", "bo3:4:25301": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:19913": 1740.227749, "bo3:4:25301": 1620.074907}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.392463, "home": 0.607537}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f91224b5f1040bd11c25b0422ef87b0b2899559b8a5d935ff122f45428a9806", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/dota2/gated.xlsx
+++ b/data/sports/dota2/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ143" headerRowCount="1">
-  <autoFilter ref="A1:DQ143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ148" headerRowCount="1">
+  <autoFilter ref="A1:DQ148"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$143)</f>
+        <f>COUNTA('Picks'!$A$2:$A$148)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$143,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$148,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")+COUNTIFS('Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$143,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$148,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")/(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")/(COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")+COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$143)/SUM('Picks'!$BX$2:$BX$143),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$148)/SUM('Picks'!$BX$2:$BX$148),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$143)</f>
+        <f>SUM('Picks'!$BY$2:$BY$148)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$143,"&lt;&gt;",'Picks'!$AB$2:$AB$143),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$148,"&lt;&gt;",'Picks'!$AB$2:$AB$148),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$148,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$143,'Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$148,'Picks'!$AM$2:$AM$148,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ143"/>
+  <dimension ref="A1:DQ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45224,18 +45224,32 @@
       </c>
       <c r="U138" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V138" s="24" t="n"/>
-      <c r="W138" s="26" t="n"/>
-      <c r="X138" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W138" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y138" s="25" t="n"/>
       <c r="Z138" s="26" t="n"/>
       <c r="AA138" s="28" t="n"/>
       <c r="AB138" s="28" t="n"/>
-      <c r="AC138" s="30" t="n"/>
-      <c r="AD138" s="24" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:17:42.530596Z</t>
+        </is>
+      </c>
       <c r="AE138" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-dota2-nemiga-kalmy-2026-10-14-tot-2pt5).</t>
@@ -45248,7 +45262,7 @@
       </c>
       <c r="AG138" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH138" s="24" t="n"/>
@@ -45519,18 +45533,38 @@
       </c>
       <c r="U139" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V139" s="24" t="n"/>
-      <c r="W139" s="26" t="n"/>
-      <c r="X139" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W139" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y139" s="25" t="n"/>
-      <c r="Z139" s="26" t="n"/>
-      <c r="AA139" s="28" t="n"/>
-      <c r="AB139" s="28" t="n"/>
-      <c r="AC139" s="30" t="n"/>
-      <c r="AD139" s="24" t="n"/>
+      <c r="Z139" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA139" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB139" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC139" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:17:45.398301Z</t>
+        </is>
+      </c>
       <c r="AE139" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
@@ -45673,8 +45707,12 @@
       <c r="BN139" s="28" t="n"/>
       <c r="BO139" s="28" t="n"/>
       <c r="BP139" s="25" t="n"/>
-      <c r="BQ139" s="27" t="n"/>
-      <c r="BR139" s="28" t="n"/>
+      <c r="BQ139" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR139" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS139" s="28" t="n"/>
       <c r="BT139" s="28" t="n"/>
       <c r="BU139" s="25" t="n"/>
@@ -45816,18 +45854,38 @@
       </c>
       <c r="U140" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V140" s="24" t="n"/>
-      <c r="W140" s="26" t="n"/>
-      <c r="X140" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V140" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W140" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y140" s="25" t="n"/>
-      <c r="Z140" s="26" t="n"/>
-      <c r="AA140" s="28" t="n"/>
-      <c r="AB140" s="28" t="n"/>
-      <c r="AC140" s="30" t="n"/>
-      <c r="AD140" s="24" t="n"/>
+      <c r="Z140" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA140" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB140" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC140" s="30" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AD140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:17:48.329322Z</t>
+        </is>
+      </c>
       <c r="AE140" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-yb-tr-2026-10-14).</t>
@@ -45970,8 +46028,12 @@
       <c r="BN140" s="28" t="n"/>
       <c r="BO140" s="28" t="n"/>
       <c r="BP140" s="25" t="n"/>
-      <c r="BQ140" s="27" t="n"/>
-      <c r="BR140" s="28" t="n"/>
+      <c r="BQ140" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR140" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS140" s="28" t="n"/>
       <c r="BT140" s="28" t="n"/>
       <c r="BU140" s="25" t="n"/>
@@ -46113,18 +46175,38 @@
       </c>
       <c r="U141" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V141" s="24" t="n"/>
-      <c r="W141" s="26" t="n"/>
-      <c r="X141" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W141" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y141" s="25" t="n"/>
-      <c r="Z141" s="26" t="n"/>
-      <c r="AA141" s="28" t="n"/>
-      <c r="AB141" s="28" t="n"/>
-      <c r="AC141" s="30" t="n"/>
-      <c r="AD141" s="24" t="n"/>
+      <c r="Z141" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA141" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB141" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:47.665739Z</t>
+        </is>
+      </c>
       <c r="AE141" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
@@ -46137,7 +46219,7 @@
       </c>
       <c r="AG141" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH141" s="24" t="n"/>
@@ -46267,8 +46349,12 @@
       <c r="BN141" s="28" t="n"/>
       <c r="BO141" s="28" t="n"/>
       <c r="BP141" s="25" t="n"/>
-      <c r="BQ141" s="27" t="n"/>
-      <c r="BR141" s="28" t="n"/>
+      <c r="BQ141" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR141" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS141" s="28" t="n"/>
       <c r="BT141" s="28" t="n"/>
       <c r="BU141" s="25" t="n"/>
@@ -46332,22 +46418,22 @@
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="24" t="inlineStr">
         <is>
-          <t>0202c808fd744b53</t>
+          <t>ebfc0857c86b4050</t>
         </is>
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:58.433878Z</t>
+          <t>2026-10-14T16:27:13.864206Z</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T17:00:00Z</t>
         </is>
       </c>
       <c r="D142" s="24" t="inlineStr">
         <is>
-          <t>156716</t>
+          <t>159104</t>
         </is>
       </c>
       <c r="E142" s="24" t="inlineStr">
@@ -46357,12 +46443,12 @@
       </c>
       <c r="F142" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="G142" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="H142" s="24" t="inlineStr">
@@ -46372,7 +46458,7 @@
       </c>
       <c r="I142" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J142" s="25" t="n"/>
@@ -46382,20 +46468,20 @@
         </is>
       </c>
       <c r="L142" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="M142" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="N142" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="O142" s="28" t="n">
-        <v>0.59448</v>
+        <v>0.562152</v>
       </c>
       <c r="P142" s="28" t="n"/>
       <c r="Q142" s="28" t="n">
-        <v>-0.09592199999999999</v>
+        <v>-0.137548</v>
       </c>
       <c r="R142" s="26" t="n">
         <v>0</v>
@@ -46410,21 +46496,41 @@
       </c>
       <c r="U142" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V142" s="24" t="n"/>
-      <c r="W142" s="26" t="n"/>
-      <c r="X142" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W142" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y142" s="25" t="n"/>
-      <c r="Z142" s="26" t="n"/>
-      <c r="AA142" s="28" t="n"/>
-      <c r="AB142" s="28" t="n"/>
-      <c r="AC142" s="30" t="n"/>
-      <c r="AD142" s="24" t="n"/>
+      <c r="Z142" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA142" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB142" s="28" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="AC142" s="30" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="AD142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:48.991943Z</t>
+        </is>
+      </c>
       <c r="AE142" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-nge-hkr-2026-10-14).</t>
         </is>
       </c>
       <c r="AF142" s="31" t="inlineStr">
@@ -46465,32 +46571,32 @@
       </c>
       <c r="AP142" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AQ142" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AR142" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AS142" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AT142" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AU142" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AV142" s="24" t="n"/>
@@ -46508,7 +46614,7 @@
       </c>
       <c r="BA142" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BB142" s="24" t="inlineStr">
@@ -46523,7 +46629,7 @@
       </c>
       <c r="BD142" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BE142" s="24" t="inlineStr">
@@ -46543,7 +46649,7 @@
       </c>
       <c r="BH142" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:56:54.523031Z</t>
+          <t>2026-10-14T16:25:51.391990Z</t>
         </is>
       </c>
       <c r="BI142" s="24" t="inlineStr">
@@ -46553,19 +46659,23 @@
       </c>
       <c r="BJ142" s="25" t="n"/>
       <c r="BK142" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="BL142" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="BM142" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="BN142" s="28" t="n"/>
       <c r="BO142" s="28" t="n"/>
       <c r="BP142" s="25" t="n"/>
-      <c r="BQ142" s="27" t="n"/>
-      <c r="BR142" s="28" t="n"/>
+      <c r="BQ142" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR142" s="28" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BS142" s="28" t="n"/>
       <c r="BT142" s="28" t="n"/>
       <c r="BU142" s="25" t="n"/>
@@ -46622,29 +46732,29 @@
       <c r="DP142" s="24" t="n"/>
       <c r="DQ142" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1620.074907, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:25301": 1620.074907, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.40552, "home": 0.59448}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f63e7ddcb28fd5faf9bb7922cf0be61109ee48b76f676b6e8273dbe0a0179db", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Hokori", "event_id": "159104", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1587.595589, "away_history_count": 93, "home_elo": 1511.739528, "home_history_count": 15}, "historical_source_observation_times_verified": false, "home_team": "New Growth", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15828": 93, "bo3:4:22378": 15}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15828": "2026-10-13T17:10:00Z", "bo3:4:22378": "2026-10-13T17:15:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:15828": 1587.595589, "bo3:4:22378": 1511.739528}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:22378", "bo3:4:15828"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.562152, "home": 0.437848}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d1c9ac18453b9cbab360dfe4e5be811f611b79e9b9bb5035e88ea7fe1674bfe0", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
     <row r="143" ht="36" customHeight="1">
       <c r="A143" s="24" t="inlineStr">
         <is>
-          <t>19baae4adbcc4759</t>
+          <t>e3fc10bbf8d4493c</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:58.433878Z</t>
+          <t>2026-10-14T16:27:13.864206Z</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
         <is>
-          <t>2026-10-15T10:00:00Z</t>
+          <t>2026-10-14T17:00:00Z</t>
         </is>
       </c>
       <c r="D143" s="24" t="inlineStr">
         <is>
-          <t>156803</t>
+          <t>159527</t>
         </is>
       </c>
       <c r="E143" s="24" t="inlineStr">
@@ -46654,12 +46764,12 @@
       </c>
       <c r="F143" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="G143" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="H143" s="24" t="inlineStr">
@@ -46669,7 +46779,7 @@
       </c>
       <c r="I143" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J143" s="25" t="n"/>
@@ -46679,26 +46789,26 @@
         </is>
       </c>
       <c r="L143" s="26" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="M143" s="27" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N143" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.4</v>
       </c>
       <c r="O143" s="28" t="n">
-        <v>0.607537</v>
+        <v>0.5145110000000001</v>
       </c>
       <c r="P143" s="28" t="n"/>
       <c r="Q143" s="28" t="n">
-        <v>0.157087</v>
+        <v>0.114511</v>
       </c>
       <c r="R143" s="26" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="S143" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T143" s="24" t="inlineStr">
         <is>
@@ -46707,21 +46817,41 @@
       </c>
       <c r="U143" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V143" s="24" t="n"/>
-      <c r="W143" s="26" t="n"/>
-      <c r="X143" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W143" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y143" s="25" t="n"/>
-      <c r="Z143" s="26" t="n"/>
-      <c r="AA143" s="28" t="n"/>
-      <c r="AB143" s="28" t="n"/>
-      <c r="AC143" s="30" t="n"/>
-      <c r="AD143" s="24" t="n"/>
+      <c r="Z143" s="26" t="n">
+        <v>-400</v>
+      </c>
+      <c r="AA143" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB143" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC143" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:50.222472Z</t>
+        </is>
+      </c>
       <c r="AE143" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-sky-rl-2026-10-14).</t>
         </is>
       </c>
       <c r="AF143" s="31" t="inlineStr">
@@ -46731,7 +46861,7 @@
       </c>
       <c r="AG143" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH143" s="24" t="n"/>
@@ -46762,32 +46892,32 @@
       </c>
       <c r="AP143" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AQ143" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AR143" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AS143" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AT143" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AU143" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AV143" s="24" t="n"/>
@@ -46805,7 +46935,7 @@
       </c>
       <c r="BA143" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BB143" s="24" t="inlineStr">
@@ -46820,7 +46950,7 @@
       </c>
       <c r="BD143" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BE143" s="24" t="inlineStr">
@@ -46840,7 +46970,7 @@
       </c>
       <c r="BH143" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:16.995855Z</t>
+          <t>2026-10-14T16:26:32.931088Z</t>
         </is>
       </c>
       <c r="BI143" s="24" t="inlineStr">
@@ -46850,19 +46980,23 @@
       </c>
       <c r="BJ143" s="25" t="n"/>
       <c r="BK143" s="26" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="BL143" s="27" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BM143" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.4</v>
       </c>
       <c r="BN143" s="28" t="n"/>
       <c r="BO143" s="28" t="n"/>
       <c r="BP143" s="25" t="n"/>
-      <c r="BQ143" s="27" t="n"/>
-      <c r="BR143" s="28" t="n"/>
+      <c r="BQ143" s="27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BR143" s="28" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BS143" s="28" t="n"/>
       <c r="BT143" s="28" t="n"/>
       <c r="BU143" s="25" t="n"/>
@@ -46919,7 +47053,1530 @@
       <c r="DP143" s="24" t="n"/>
       <c r="DQ143" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1620.074907, "away_history_count": 6, "home_elo": 1740.227749, "home_history_count": 186}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 186, "bo3:4:25301": 6}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-13T07:00:00Z", "bo3:4:25301": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:19913": 1740.227749, "bo3:4:25301": 1620.074907}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.392463, "home": 0.607537}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f91224b5f1040bd11c25b0422ef87b0b2899559b8a5d935ff122f45428a9806", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Rottweilas Latam", "event_id": "159527", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1555.776918, "away_history_count": 15, "home_elo": 1522.384807, "home_history_count": 5}, "historical_source_observation_times_verified": false, "home_team": "Skyreavers", "inference_inputs": {"book_state": {"games_played": {"bo3:4:22288": 15, "bo3:4:25468": 5}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:22288": "2026-10-13T21:00:00Z", "bo3:4:25468": "2026-10-13T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:22288": 1555.776918, "bo3:4:25468": 1522.384807}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:25468", "bo3:4:22288"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.514511, "home": 0.485489}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "53e21587e49ce07031479c6ea4c0f7d59d4a6641af182747482efe9dd33de1b1", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="24" t="inlineStr">
+        <is>
+          <t>c35f21d38e0e4415</t>
+        </is>
+      </c>
+      <c r="B144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:27:13.864206Z</t>
+        </is>
+      </c>
+      <c r="C144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D144" s="24" t="inlineStr">
+        <is>
+          <t>159889</t>
+        </is>
+      </c>
+      <c r="E144" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F144" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="G144" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="H144" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I144" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J144" s="25" t="n"/>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M144" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N144" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O144" s="28" t="n">
+        <v>0.56987</v>
+      </c>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="28" t="n">
+        <v>0.160034</v>
+      </c>
+      <c r="R144" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S144" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T144" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U144" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V144" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W144" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y144" s="25" t="n"/>
+      <c r="Z144" s="26" t="n"/>
+      <c r="AA144" s="28" t="n"/>
+      <c r="AB144" s="28" t="n"/>
+      <c r="AC144" s="30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:51.513326Z</t>
+        </is>
+      </c>
+      <c r="AE144" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-dota2-bot-kt-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF144" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG144" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH144" s="24" t="n"/>
+      <c r="AI144" s="31" t="n"/>
+      <c r="AJ144" s="31" t="n"/>
+      <c r="AK144" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL144" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM144" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN144" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO144" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP144" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AQ144" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AR144" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AS144" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AT144" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AU144" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AV144" s="24" t="n"/>
+      <c r="AW144" s="24" t="n"/>
+      <c r="AX144" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY144" s="24" t="n"/>
+      <c r="AZ144" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA144" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BB144" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC144" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD144" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BE144" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF144" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG144" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:26:33.015972Z</t>
+        </is>
+      </c>
+      <c r="BI144" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ144" s="25" t="n"/>
+      <c r="BK144" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL144" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM144" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN144" s="28" t="n"/>
+      <c r="BO144" s="28" t="n"/>
+      <c r="BP144" s="25" t="n"/>
+      <c r="BQ144" s="27" t="n"/>
+      <c r="BR144" s="28" t="n"/>
+      <c r="BS144" s="28" t="n"/>
+      <c r="BT144" s="28" t="n"/>
+      <c r="BU144" s="25" t="n"/>
+      <c r="BV144" s="29" t="n"/>
+      <c r="BW144" s="24" t="n"/>
+      <c r="BX144" s="30" t="n"/>
+      <c r="BY144" s="27" t="n"/>
+      <c r="BZ144" s="24" t="n"/>
+      <c r="CA144" s="31" t="n"/>
+      <c r="CB144" s="24" t="n"/>
+      <c r="CC144" s="24" t="n"/>
+      <c r="CD144" s="24" t="n"/>
+      <c r="CE144" s="24" t="n"/>
+      <c r="CF144" s="24" t="n"/>
+      <c r="CG144" s="24" t="n"/>
+      <c r="CH144" s="24" t="n"/>
+      <c r="CI144" s="24" t="n"/>
+      <c r="CJ144" s="24" t="n"/>
+      <c r="CK144" s="24" t="n"/>
+      <c r="CL144" s="24" t="n"/>
+      <c r="CM144" s="24" t="n"/>
+      <c r="CN144" s="24" t="n"/>
+      <c r="CO144" s="24" t="n"/>
+      <c r="CP144" s="24" t="n"/>
+      <c r="CQ144" s="24" t="n"/>
+      <c r="CR144" s="24" t="n"/>
+      <c r="CS144" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT144" s="24" t="n"/>
+      <c r="CU144" s="24" t="n"/>
+      <c r="CV144" s="24" t="n"/>
+      <c r="CW144" s="24" t="n"/>
+      <c r="CX144" s="24" t="n"/>
+      <c r="CY144" s="24" t="n"/>
+      <c r="CZ144" s="24" t="n"/>
+      <c r="DA144" s="24" t="n"/>
+      <c r="DB144" s="24" t="n"/>
+      <c r="DC144" s="24" t="n"/>
+      <c r="DD144" s="24" t="n"/>
+      <c r="DE144" s="24" t="n"/>
+      <c r="DF144" s="24" t="n"/>
+      <c r="DG144" s="24" t="n"/>
+      <c r="DH144" s="24" t="n"/>
+      <c r="DI144" s="24" t="n"/>
+      <c r="DJ144" s="24" t="n"/>
+      <c r="DK144" s="24" t="n"/>
+      <c r="DL144" s="24" t="n"/>
+      <c r="DM144" s="24" t="n"/>
+      <c r="DN144" s="24" t="n"/>
+      <c r="DO144" s="24" t="n"/>
+      <c r="DP144" s="24" t="n"/>
+      <c r="DQ144" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Korb3n Team", "event_id": "159889", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1413.038012, "away_history_count": 4, "home_elo": 1622.517552, "home_history_count": 15}, "historical_source_observation_times_verified": false, "home_team": "by Owl Team", "inference_inputs": {"book_state": {"games_played": {"bo3:4:20838": 4, "bo3:4:21660": 15}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:20838": "2025-06-05T18:15:00Z", "bo3:4:21660": "2025-11-30T14:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:20838": 1413.038012, "bo3:4:21660": 1622.517552}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:21660", "bo3:4:20838"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.43013, "home": 0.56987}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d4e2a64a9f5668351842c1563ecc563be1b30fa530535fc1eb116755d6aad808", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="24" t="inlineStr">
+        <is>
+          <t>57127c2b46684159</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:27:13.864206Z</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D145" s="24" t="inlineStr">
+        <is>
+          <t>156716</t>
+        </is>
+      </c>
+      <c r="E145" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F145" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="H145" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I145" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J145" s="25" t="n"/>
+      <c r="K145" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M145" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N145" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O145" s="28" t="n">
+        <v>0.5931959999999999</v>
+      </c>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="28" t="n">
+        <v>-0.097206</v>
+      </c>
+      <c r="R145" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U145" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V145" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W145" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" s="25" t="n"/>
+      <c r="Z145" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA145" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB145" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC145" s="30" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AD145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:52.766987Z</t>
+        </is>
+      </c>
+      <c r="AE145" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF145" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG145" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH145" s="24" t="n"/>
+      <c r="AI145" s="31" t="n"/>
+      <c r="AJ145" s="31" t="n"/>
+      <c r="AK145" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL145" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM145" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN145" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO145" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP145" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ145" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR145" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS145" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AT145" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AU145" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AV145" s="24" t="n"/>
+      <c r="AW145" s="24" t="n"/>
+      <c r="AX145" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY145" s="24" t="n"/>
+      <c r="AZ145" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA145" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BB145" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC145" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD145" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BE145" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF145" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG145" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:26:43.456466Z</t>
+        </is>
+      </c>
+      <c r="BI145" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ145" s="25" t="n"/>
+      <c r="BK145" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL145" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM145" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN145" s="28" t="n"/>
+      <c r="BO145" s="28" t="n"/>
+      <c r="BP145" s="25" t="n"/>
+      <c r="BQ145" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR145" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BS145" s="28" t="n"/>
+      <c r="BT145" s="28" t="n"/>
+      <c r="BU145" s="25" t="n"/>
+      <c r="BV145" s="29" t="n"/>
+      <c r="BW145" s="24" t="n"/>
+      <c r="BX145" s="30" t="n"/>
+      <c r="BY145" s="27" t="n"/>
+      <c r="BZ145" s="24" t="n"/>
+      <c r="CA145" s="31" t="n"/>
+      <c r="CB145" s="24" t="n"/>
+      <c r="CC145" s="24" t="n"/>
+      <c r="CD145" s="24" t="n"/>
+      <c r="CE145" s="24" t="n"/>
+      <c r="CF145" s="24" t="n"/>
+      <c r="CG145" s="24" t="n"/>
+      <c r="CH145" s="24" t="n"/>
+      <c r="CI145" s="24" t="n"/>
+      <c r="CJ145" s="24" t="n"/>
+      <c r="CK145" s="24" t="n"/>
+      <c r="CL145" s="24" t="n"/>
+      <c r="CM145" s="24" t="n"/>
+      <c r="CN145" s="24" t="n"/>
+      <c r="CO145" s="24" t="n"/>
+      <c r="CP145" s="24" t="n"/>
+      <c r="CQ145" s="24" t="n"/>
+      <c r="CR145" s="24" t="n"/>
+      <c r="CS145" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT145" s="24" t="n"/>
+      <c r="CU145" s="24" t="n"/>
+      <c r="CV145" s="24" t="n"/>
+      <c r="CW145" s="24" t="n"/>
+      <c r="CX145" s="24" t="n"/>
+      <c r="CY145" s="24" t="n"/>
+      <c r="CZ145" s="24" t="n"/>
+      <c r="DA145" s="24" t="n"/>
+      <c r="DB145" s="24" t="n"/>
+      <c r="DC145" s="24" t="n"/>
+      <c r="DD145" s="24" t="n"/>
+      <c r="DE145" s="24" t="n"/>
+      <c r="DF145" s="24" t="n"/>
+      <c r="DG145" s="24" t="n"/>
+      <c r="DH145" s="24" t="n"/>
+      <c r="DI145" s="24" t="n"/>
+      <c r="DJ145" s="24" t="n"/>
+      <c r="DK145" s="24" t="n"/>
+      <c r="DL145" s="24" t="n"/>
+      <c r="DM145" s="24" t="n"/>
+      <c r="DN145" s="24" t="n"/>
+      <c r="DO145" s="24" t="n"/>
+      <c r="DP145" s="24" t="n"/>
+      <c r="DQ145" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.359665, "away_history_count": 1, "home_elo": 1619.975066, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:25301": 1619.975066, "bo3:4:25478": 1460.359665}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.406804, "home": 0.593196}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "cabcc8a699a98345988ad0f64096ec22f1d9b9d311724c52f265d49816451015", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="24" t="inlineStr">
+        <is>
+          <t>03a648e87d274b84</t>
+        </is>
+      </c>
+      <c r="B146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t>156063</t>
+        </is>
+      </c>
+      <c r="E146" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F146" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="H146" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I146" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J146" s="25" t="n"/>
+      <c r="K146" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L146" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M146" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N146" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O146" s="28" t="n">
+        <v>0.527991</v>
+      </c>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="28" t="n">
+        <v>0.137366</v>
+      </c>
+      <c r="R146" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S146" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U146" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V146" s="24" t="n"/>
+      <c r="W146" s="26" t="n"/>
+      <c r="X146" s="26" t="n"/>
+      <c r="Y146" s="25" t="n"/>
+      <c r="Z146" s="26" t="n"/>
+      <c r="AA146" s="28" t="n"/>
+      <c r="AB146" s="28" t="n"/>
+      <c r="AC146" s="30" t="n"/>
+      <c r="AD146" s="24" t="n"/>
+      <c r="AE146" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-xctn-rb-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF146" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG146" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH146" s="24" t="n"/>
+      <c r="AI146" s="31" t="n"/>
+      <c r="AJ146" s="31" t="n"/>
+      <c r="AK146" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL146" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM146" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN146" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO146" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP146" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AQ146" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AR146" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AS146" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AT146" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AU146" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AV146" s="24" t="n"/>
+      <c r="AW146" s="24" t="n"/>
+      <c r="AX146" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY146" s="24" t="n"/>
+      <c r="AZ146" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA146" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB146" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD146" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE146" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF146" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.140829Z</t>
+        </is>
+      </c>
+      <c r="BI146" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ146" s="25" t="n"/>
+      <c r="BK146" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL146" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM146" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN146" s="28" t="n"/>
+      <c r="BO146" s="28" t="n"/>
+      <c r="BP146" s="25" t="n"/>
+      <c r="BQ146" s="27" t="n"/>
+      <c r="BR146" s="28" t="n"/>
+      <c r="BS146" s="28" t="n"/>
+      <c r="BT146" s="28" t="n"/>
+      <c r="BU146" s="25" t="n"/>
+      <c r="BV146" s="29" t="n"/>
+      <c r="BW146" s="24" t="n"/>
+      <c r="BX146" s="30" t="n"/>
+      <c r="BY146" s="27" t="n"/>
+      <c r="BZ146" s="24" t="n"/>
+      <c r="CA146" s="31" t="n"/>
+      <c r="CB146" s="24" t="n"/>
+      <c r="CC146" s="24" t="n"/>
+      <c r="CD146" s="24" t="n"/>
+      <c r="CE146" s="24" t="n"/>
+      <c r="CF146" s="24" t="n"/>
+      <c r="CG146" s="24" t="n"/>
+      <c r="CH146" s="24" t="n"/>
+      <c r="CI146" s="24" t="n"/>
+      <c r="CJ146" s="24" t="n"/>
+      <c r="CK146" s="24" t="n"/>
+      <c r="CL146" s="24" t="n"/>
+      <c r="CM146" s="24" t="n"/>
+      <c r="CN146" s="24" t="n"/>
+      <c r="CO146" s="24" t="n"/>
+      <c r="CP146" s="24" t="n"/>
+      <c r="CQ146" s="24" t="n"/>
+      <c r="CR146" s="24" t="n"/>
+      <c r="CS146" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT146" s="24" t="n"/>
+      <c r="CU146" s="24" t="n"/>
+      <c r="CV146" s="24" t="n"/>
+      <c r="CW146" s="24" t="n"/>
+      <c r="CX146" s="24" t="n"/>
+      <c r="CY146" s="24" t="n"/>
+      <c r="CZ146" s="24" t="n"/>
+      <c r="DA146" s="24" t="n"/>
+      <c r="DB146" s="24" t="n"/>
+      <c r="DC146" s="24" t="n"/>
+      <c r="DD146" s="24" t="n"/>
+      <c r="DE146" s="24" t="n"/>
+      <c r="DF146" s="24" t="n"/>
+      <c r="DG146" s="24" t="n"/>
+      <c r="DH146" s="24" t="n"/>
+      <c r="DI146" s="24" t="n"/>
+      <c r="DJ146" s="24" t="n"/>
+      <c r="DK146" s="24" t="n"/>
+      <c r="DL146" s="24" t="n"/>
+      <c r="DM146" s="24" t="n"/>
+      <c r="DN146" s="24" t="n"/>
+      <c r="DO146" s="24" t="n"/>
+      <c r="DP146" s="24" t="n"/>
+      <c r="DQ146" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Royal Bear", "event_id": "156063", "event_start_utc": "2026-10-15T04:00:00Z", "features": {"away_elo": 1565.005066, "away_history_count": 2, "home_elo": 1620.77125, "home_history_count": 232}, "historical_source_observation_times_verified": false, "home_team": "Execration", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16710": 232, "bo3:4:25439": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16710": "2026-09-13T05:45:00Z", "bo3:4:25439": "2026-10-10T08:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:16710": 1620.77125, "bo3:4:25439": 1565.005066}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:16710", "bo3:4:25439"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.472009, "home": 0.527991}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "21e684090db0fc15459d72e5adb631b9021f69f3e924847f36be1bc1730bee91", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="A147" s="24" t="inlineStr">
+        <is>
+          <t>723dfed0a2954c49</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t>156799</t>
+        </is>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="H147" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I147" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J147" s="25" t="n"/>
+      <c r="K147" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L147" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M147" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N147" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O147" s="28" t="n">
+        <v>0.6493910000000001</v>
+      </c>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="28" t="n">
+        <v>0.07857599999999999</v>
+      </c>
+      <c r="R147" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S147" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U147" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V147" s="24" t="n"/>
+      <c r="W147" s="26" t="n"/>
+      <c r="X147" s="26" t="n"/>
+      <c r="Y147" s="25" t="n"/>
+      <c r="Z147" s="26" t="n"/>
+      <c r="AA147" s="28" t="n"/>
+      <c r="AB147" s="28" t="n"/>
+      <c r="AC147" s="30" t="n"/>
+      <c r="AD147" s="24" t="n"/>
+      <c r="AE147" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-db-tke-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF147" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG147" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH147" s="24" t="n"/>
+      <c r="AI147" s="31" t="n"/>
+      <c r="AJ147" s="31" t="n"/>
+      <c r="AK147" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL147" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM147" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN147" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO147" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP147" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AQ147" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AR147" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AS147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AT147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AU147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AV147" s="24" t="n"/>
+      <c r="AW147" s="24" t="n"/>
+      <c r="AX147" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY147" s="24" t="n"/>
+      <c r="AZ147" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA147" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB147" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD147" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.205469Z</t>
+        </is>
+      </c>
+      <c r="BI147" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ147" s="25" t="n"/>
+      <c r="BK147" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL147" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM147" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN147" s="28" t="n"/>
+      <c r="BO147" s="28" t="n"/>
+      <c r="BP147" s="25" t="n"/>
+      <c r="BQ147" s="27" t="n"/>
+      <c r="BR147" s="28" t="n"/>
+      <c r="BS147" s="28" t="n"/>
+      <c r="BT147" s="28" t="n"/>
+      <c r="BU147" s="25" t="n"/>
+      <c r="BV147" s="29" t="n"/>
+      <c r="BW147" s="24" t="n"/>
+      <c r="BX147" s="30" t="n"/>
+      <c r="BY147" s="27" t="n"/>
+      <c r="BZ147" s="24" t="n"/>
+      <c r="CA147" s="31" t="n"/>
+      <c r="CB147" s="24" t="n"/>
+      <c r="CC147" s="24" t="n"/>
+      <c r="CD147" s="24" t="n"/>
+      <c r="CE147" s="24" t="n"/>
+      <c r="CF147" s="24" t="n"/>
+      <c r="CG147" s="24" t="n"/>
+      <c r="CH147" s="24" t="n"/>
+      <c r="CI147" s="24" t="n"/>
+      <c r="CJ147" s="24" t="n"/>
+      <c r="CK147" s="24" t="n"/>
+      <c r="CL147" s="24" t="n"/>
+      <c r="CM147" s="24" t="n"/>
+      <c r="CN147" s="24" t="n"/>
+      <c r="CO147" s="24" t="n"/>
+      <c r="CP147" s="24" t="n"/>
+      <c r="CQ147" s="24" t="n"/>
+      <c r="CR147" s="24" t="n"/>
+      <c r="CS147" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT147" s="24" t="n"/>
+      <c r="CU147" s="24" t="n"/>
+      <c r="CV147" s="24" t="n"/>
+      <c r="CW147" s="24" t="n"/>
+      <c r="CX147" s="24" t="n"/>
+      <c r="CY147" s="24" t="n"/>
+      <c r="CZ147" s="24" t="n"/>
+      <c r="DA147" s="24" t="n"/>
+      <c r="DB147" s="24" t="n"/>
+      <c r="DC147" s="24" t="n"/>
+      <c r="DD147" s="24" t="n"/>
+      <c r="DE147" s="24" t="n"/>
+      <c r="DF147" s="24" t="n"/>
+      <c r="DG147" s="24" t="n"/>
+      <c r="DH147" s="24" t="n"/>
+      <c r="DI147" s="24" t="n"/>
+      <c r="DJ147" s="24" t="n"/>
+      <c r="DK147" s="24" t="n"/>
+      <c r="DL147" s="24" t="n"/>
+      <c r="DM147" s="24" t="n"/>
+      <c r="DN147" s="24" t="n"/>
+      <c r="DO147" s="24" t="n"/>
+      <c r="DP147" s="24" t="n"/>
+      <c r="DQ147" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Team Kinetix", "event_id": "156799", "event_start_utc": "2026-10-15T04:00:00Z", "features": {"away_elo": 1454.932244, "away_history_count": 17, "home_elo": 1597.368763, "home_history_count": 40}, "historical_source_observation_times_verified": false, "home_team": "Direborn", "inference_inputs": {"book_state": {"games_played": {"bo3:4:24344": 40, "bo3:4:25225": 17}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:24344": "2026-10-08T03:10:00Z", "bo3:4:25225": "2026-10-12T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:24344": 1597.368763, "bo3:4:25225": 1454.932244}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:24344", "bo3:4:25225"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.350609, "home": 0.649391}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9aa03fcfb2d0ec6dca89faef6ba9ac3db646dcd5a3c5249be6a09f2755ed94cd", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="A148" s="24" t="inlineStr">
+        <is>
+          <t>3b689a3bb2fe46cc</t>
+        </is>
+      </c>
+      <c r="B148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t>156803</t>
+        </is>
+      </c>
+      <c r="E148" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="G148" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H148" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I148" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J148" s="25" t="n"/>
+      <c r="K148" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L148" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M148" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N148" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O148" s="28" t="n">
+        <v>0.612465</v>
+      </c>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="28" t="n">
+        <v>0.162015</v>
+      </c>
+      <c r="R148" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S148" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U148" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V148" s="24" t="n"/>
+      <c r="W148" s="26" t="n"/>
+      <c r="X148" s="26" t="n"/>
+      <c r="Y148" s="25" t="n"/>
+      <c r="Z148" s="26" t="n"/>
+      <c r="AA148" s="28" t="n"/>
+      <c r="AB148" s="28" t="n"/>
+      <c r="AC148" s="30" t="n"/>
+      <c r="AD148" s="24" t="n"/>
+      <c r="AE148" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF148" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG148" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH148" s="24" t="n"/>
+      <c r="AI148" s="31" t="n"/>
+      <c r="AJ148" s="31" t="n"/>
+      <c r="AK148" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL148" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM148" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN148" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO148" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP148" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AQ148" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AR148" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AS148" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT148" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU148" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV148" s="24" t="n"/>
+      <c r="AW148" s="24" t="n"/>
+      <c r="AX148" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY148" s="24" t="n"/>
+      <c r="AZ148" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA148" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB148" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD148" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:05.177623Z</t>
+        </is>
+      </c>
+      <c r="BI148" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ148" s="25" t="n"/>
+      <c r="BK148" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL148" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM148" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN148" s="28" t="n"/>
+      <c r="BO148" s="28" t="n"/>
+      <c r="BP148" s="25" t="n"/>
+      <c r="BQ148" s="27" t="n"/>
+      <c r="BR148" s="28" t="n"/>
+      <c r="BS148" s="28" t="n"/>
+      <c r="BT148" s="28" t="n"/>
+      <c r="BU148" s="25" t="n"/>
+      <c r="BV148" s="29" t="n"/>
+      <c r="BW148" s="24" t="n"/>
+      <c r="BX148" s="30" t="n"/>
+      <c r="BY148" s="27" t="n"/>
+      <c r="BZ148" s="24" t="n"/>
+      <c r="CA148" s="31" t="n"/>
+      <c r="CB148" s="24" t="n"/>
+      <c r="CC148" s="24" t="n"/>
+      <c r="CD148" s="24" t="n"/>
+      <c r="CE148" s="24" t="n"/>
+      <c r="CF148" s="24" t="n"/>
+      <c r="CG148" s="24" t="n"/>
+      <c r="CH148" s="24" t="n"/>
+      <c r="CI148" s="24" t="n"/>
+      <c r="CJ148" s="24" t="n"/>
+      <c r="CK148" s="24" t="n"/>
+      <c r="CL148" s="24" t="n"/>
+      <c r="CM148" s="24" t="n"/>
+      <c r="CN148" s="24" t="n"/>
+      <c r="CO148" s="24" t="n"/>
+      <c r="CP148" s="24" t="n"/>
+      <c r="CQ148" s="24" t="n"/>
+      <c r="CR148" s="24" t="n"/>
+      <c r="CS148" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT148" s="24" t="n"/>
+      <c r="CU148" s="24" t="n"/>
+      <c r="CV148" s="24" t="n"/>
+      <c r="CW148" s="24" t="n"/>
+      <c r="CX148" s="24" t="n"/>
+      <c r="CY148" s="24" t="n"/>
+      <c r="CZ148" s="24" t="n"/>
+      <c r="DA148" s="24" t="n"/>
+      <c r="DB148" s="24" t="n"/>
+      <c r="DC148" s="24" t="n"/>
+      <c r="DD148" s="24" t="n"/>
+      <c r="DE148" s="24" t="n"/>
+      <c r="DF148" s="24" t="n"/>
+      <c r="DG148" s="24" t="n"/>
+      <c r="DH148" s="24" t="n"/>
+      <c r="DI148" s="24" t="n"/>
+      <c r="DJ148" s="24" t="n"/>
+      <c r="DK148" s="24" t="n"/>
+      <c r="DL148" s="24" t="n"/>
+      <c r="DM148" s="24" t="n"/>
+      <c r="DN148" s="24" t="n"/>
+      <c r="DO148" s="24" t="n"/>
+      <c r="DP148" s="24" t="n"/>
+      <c r="DQ148" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1640.18007, "away_history_count": 7, "home_elo": 1758.623049, "home_history_count": 188}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 188, "bo3:4:25301": 7}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-14T10:00:00Z", "bo3:4:25301": "2026-10-14T19:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:19913": 1758.623049, "bo3:4:25301": 1640.18007}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.387535, "home": 0.612465}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "6f823458a4506198d775b496a2f575e24740130115de5ca82ae946e9b2b115a0", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
